--- a/MaestraPLU_FFVV.xlsx
+++ b/MaestraPLU_FFVV.xlsx
@@ -1173,7 +1173,7 @@
         <v>42041</v>
       </c>
       <c r="E39" t="str">
-        <v>1590</v>
+        <v>1690</v>
       </c>
       <c r="F39" t="str">
         <v>Por peso</v>

--- a/MaestraPLU_FFVV.xlsx
+++ b/MaestraPLU_FFVV.xlsx
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>741032</v>
+        <v>742011</v>
       </c>
       <c r="B2" t="str">
-        <v>JENGIBRE KG</v>
+        <v>LIMON KG</v>
       </c>
       <c r="C2" t="str">
         <v/>
       </c>
       <c r="D2" t="str">
-        <v>51032</v>
+        <v>42011</v>
       </c>
       <c r="E2" t="str">
-        <v>3560</v>
+        <v>1090</v>
       </c>
       <c r="F2" t="str">
         <v>Por peso</v>
@@ -441,19 +441,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>745146</v>
+        <v>742033</v>
       </c>
       <c r="B3" t="str">
-        <v>ALMENDRA KG FFVV</v>
+        <v>CIRUELA KG</v>
       </c>
       <c r="C3" t="str">
         <v/>
       </c>
       <c r="D3" t="str">
-        <v>45146</v>
+        <v>42033</v>
       </c>
       <c r="E3" t="str">
-        <v>16760</v>
+        <v>500</v>
       </c>
       <c r="F3" t="str">
         <v>Por peso</v>
@@ -461,19 +461,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>744023</v>
+        <v>742010</v>
       </c>
       <c r="B4" t="str">
-        <v>CHUCHOCA MOLIDA KG FFVV</v>
+        <v>KIWI KG</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
       <c r="D4" t="str">
-        <v>44023</v>
+        <v>42010</v>
       </c>
       <c r="E4" t="str">
-        <v>1960</v>
+        <v>990</v>
       </c>
       <c r="F4" t="str">
         <v>Por peso</v>
@@ -481,19 +481,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>743024</v>
+        <v>741042</v>
       </c>
       <c r="B5" t="str">
-        <v>PASAS MORENAS KG FFVV</v>
+        <v>ZANAHORIA KG</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5" t="str">
-        <v>43024</v>
+        <v>41042</v>
       </c>
       <c r="E5" t="str">
-        <v>5160</v>
+        <v>500</v>
       </c>
       <c r="F5" t="str">
         <v>Por peso</v>
@@ -501,19 +501,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>744019</v>
+        <v>741032</v>
       </c>
       <c r="B6" t="str">
-        <v>PASAS RUBIA KG FFVV</v>
+        <v>JENGIBRE KG</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
       <c r="D6" t="str">
-        <v>44019</v>
+        <v>51032</v>
       </c>
       <c r="E6" t="str">
-        <v>9960</v>
+        <v>3560</v>
       </c>
       <c r="F6" t="str">
         <v>Por peso</v>
@@ -521,19 +521,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>744160</v>
+        <v>745146</v>
       </c>
       <c r="B7" t="str">
-        <v>YUCA KG FFVV</v>
+        <v>ALMENDRA KG FFVV</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7" t="str">
-        <v>44160</v>
+        <v>45146</v>
       </c>
       <c r="E7" t="str">
-        <v>3490</v>
+        <v>16760</v>
       </c>
       <c r="F7" t="str">
         <v>Por peso</v>
@@ -541,19 +541,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>744153</v>
+        <v>744023</v>
       </c>
       <c r="B8" t="str">
-        <v>TUNAS LIQUIDACION KG</v>
+        <v>CHUCHOCA MOLIDA KG FFVV</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>44153</v>
+        <v>44023</v>
       </c>
       <c r="E8" t="str">
-        <v>9990</v>
+        <v>1960</v>
       </c>
       <c r="F8" t="str">
         <v>Por peso</v>
@@ -561,19 +561,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>744146</v>
+        <v>743024</v>
       </c>
       <c r="B9" t="str">
-        <v>FLOR DE JAMAICA KG FFVV</v>
+        <v>PASAS MORENAS KG FFVV</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9" t="str">
-        <v>44146</v>
+        <v>43024</v>
       </c>
       <c r="E9" t="str">
-        <v>27960</v>
+        <v>5160</v>
       </c>
       <c r="F9" t="str">
         <v>Por peso</v>
@@ -581,19 +581,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>745147</v>
+        <v>744019</v>
       </c>
       <c r="B10" t="str">
-        <v>HUESILLOS KG FFVV</v>
+        <v>PASAS RUBIA KG FFVV</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>45147</v>
+        <v>44019</v>
       </c>
       <c r="E10" t="str">
-        <v>9560</v>
+        <v>9960</v>
       </c>
       <c r="F10" t="str">
         <v>Por peso</v>
@@ -601,19 +601,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>742072</v>
+        <v>744160</v>
       </c>
       <c r="B11" t="str">
-        <v>SANDIA PRIMERA PP KG</v>
+        <v>YUCA KG FFVV</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>42072</v>
+        <v>44160</v>
       </c>
       <c r="E11" t="str">
-        <v>490</v>
+        <v>3490</v>
       </c>
       <c r="F11" t="str">
         <v>Por peso</v>
@@ -621,19 +621,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>742031</v>
+        <v>744153</v>
       </c>
       <c r="B12" t="str">
-        <v>PLATANO KG</v>
+        <v>TUNAS LIQUIDACION KG</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12" t="str">
-        <v>42031</v>
+        <v>44153</v>
       </c>
       <c r="E12" t="str">
-        <v>1690</v>
+        <v>9990</v>
       </c>
       <c r="F12" t="str">
         <v>Por peso</v>
@@ -641,19 +641,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>742025</v>
+        <v>744146</v>
       </c>
       <c r="B13" t="str">
-        <v>POMELO KG</v>
+        <v>FLOR DE JAMAICA KG FFVV</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13" t="str">
-        <v>42025</v>
+        <v>44146</v>
       </c>
       <c r="E13" t="str">
-        <v>890</v>
+        <v>27960</v>
       </c>
       <c r="F13" t="str">
         <v>Por peso</v>
@@ -661,19 +661,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>742049</v>
+        <v>745147</v>
       </c>
       <c r="B14" t="str">
-        <v>PERA SUMMER FAVORITA KG</v>
+        <v>HUESILLOS KG FFVV</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>42049</v>
+        <v>45147</v>
       </c>
       <c r="E14" t="str">
-        <v>990</v>
+        <v>9560</v>
       </c>
       <c r="F14" t="str">
         <v>Por peso</v>
@@ -681,19 +681,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>742045</v>
+        <v>742072</v>
       </c>
       <c r="B15" t="str">
-        <v>PERA PACKHAM KG</v>
+        <v>SANDIA PRIMERA PP KG</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>42045</v>
+        <v>42072</v>
       </c>
       <c r="E15" t="str">
-        <v>890</v>
+        <v>490</v>
       </c>
       <c r="F15" t="str">
         <v>Por peso</v>
@@ -701,19 +701,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>742024</v>
+        <v>742031</v>
       </c>
       <c r="B16" t="str">
-        <v>PERA WINTERNELLY KG</v>
+        <v>PLATANO KG</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>42024</v>
+        <v>42031</v>
       </c>
       <c r="E16" t="str">
-        <v>890</v>
+        <v>1690</v>
       </c>
       <c r="F16" t="str">
         <v>Por peso</v>
@@ -721,16 +721,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>742082</v>
+        <v>742025</v>
       </c>
       <c r="B17" t="str">
-        <v>PERA BERRY BOSC</v>
+        <v>POMELO KG</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>42082</v>
+        <v>42025</v>
       </c>
       <c r="E17" t="str">
         <v>890</v>
@@ -741,16 +741,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>742081</v>
+        <v>742049</v>
       </c>
       <c r="B18" t="str">
-        <v>PERA ASIATICA KG</v>
+        <v>PERA SUMMER FAVORITA KG</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>42081</v>
+        <v>42049</v>
       </c>
       <c r="E18" t="str">
         <v>990</v>
@@ -761,19 +761,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>742026</v>
+        <v>742045</v>
       </c>
       <c r="B19" t="str">
-        <v>PEPINO FRUTA KG</v>
+        <v>PERA PACKHAM KG</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>42026</v>
+        <v>42045</v>
       </c>
       <c r="E19" t="str">
-        <v>1790</v>
+        <v>890</v>
       </c>
       <c r="F19" t="str">
         <v>Por peso</v>
@@ -781,19 +781,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>742036</v>
+        <v>742024</v>
       </c>
       <c r="B20" t="str">
-        <v>PAPAYA KG</v>
+        <v>PERA WINTERNELLY KG</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>42036</v>
+        <v>42024</v>
       </c>
       <c r="E20" t="str">
-        <v>2990</v>
+        <v>890</v>
       </c>
       <c r="F20" t="str">
         <v>Por peso</v>
@@ -801,19 +801,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>742022</v>
+        <v>742082</v>
       </c>
       <c r="B21" t="str">
-        <v>NUECES KG FFVV</v>
+        <v>PERA BERRY BOSC</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>42022</v>
+        <v>42082</v>
       </c>
       <c r="E21" t="str">
-        <v>14760</v>
+        <v>890</v>
       </c>
       <c r="F21" t="str">
         <v>Por peso</v>
@@ -821,19 +821,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>742018</v>
+        <v>742081</v>
       </c>
       <c r="B22" t="str">
-        <v>NECTARIN AMARILLO KG</v>
+        <v>PERA ASIATICA KG</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>42018</v>
+        <v>42081</v>
       </c>
       <c r="E22" t="str">
-        <v>1290</v>
+        <v>990</v>
       </c>
       <c r="F22" t="str">
         <v>Por peso</v>
@@ -841,19 +841,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>742044</v>
+        <v>742026</v>
       </c>
       <c r="B23" t="str">
-        <v>MEMBRILLO KG</v>
+        <v>PEPINO FRUTA KG</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>42044</v>
+        <v>42026</v>
       </c>
       <c r="E23" t="str">
-        <v>990</v>
+        <v>1790</v>
       </c>
       <c r="F23" t="str">
         <v>Por peso</v>
@@ -861,19 +861,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>742015</v>
+        <v>742036</v>
       </c>
       <c r="B24" t="str">
-        <v>MANZANA VERDE KG</v>
+        <v>PAPAYA KG</v>
       </c>
       <c r="C24" t="str">
         <v/>
       </c>
       <c r="D24" t="str">
-        <v>42015</v>
+        <v>42036</v>
       </c>
       <c r="E24" t="str">
-        <v>990</v>
+        <v>2990</v>
       </c>
       <c r="F24" t="str">
         <v>Por peso</v>
@@ -881,19 +881,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>742013</v>
+        <v>742022</v>
       </c>
       <c r="B25" t="str">
-        <v>MANZANA ROJA KG</v>
+        <v>NUECES KG FFVV</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>42013</v>
+        <v>42022</v>
       </c>
       <c r="E25" t="str">
-        <v>990</v>
+        <v>14760</v>
       </c>
       <c r="F25" t="str">
         <v>Por peso</v>
@@ -901,19 +901,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>742066</v>
+        <v>742018</v>
       </c>
       <c r="B26" t="str">
-        <v>MANZANA ROYAL GALA KG</v>
+        <v>NECTARIN AMARILLO KG</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
       <c r="D26" t="str">
-        <v>42066</v>
+        <v>42018</v>
       </c>
       <c r="E26" t="str">
-        <v>990</v>
+        <v>1290</v>
       </c>
       <c r="F26" t="str">
         <v>Por peso</v>
@@ -921,16 +921,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>742067</v>
+        <v>742044</v>
       </c>
       <c r="B27" t="str">
-        <v>MANZANA FUJI KG</v>
+        <v>MEMBRILLO KG</v>
       </c>
       <c r="C27" t="str">
         <v/>
       </c>
       <c r="D27" t="str">
-        <v>42067</v>
+        <v>42044</v>
       </c>
       <c r="E27" t="str">
         <v>990</v>
@@ -941,19 +941,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>742102</v>
+        <v>742015</v>
       </c>
       <c r="B28" t="str">
-        <v>MANGOS KG</v>
+        <v>MANZANA VERDE KG</v>
       </c>
       <c r="C28" t="str">
         <v/>
       </c>
       <c r="D28" t="str">
-        <v>42102</v>
+        <v>42015</v>
       </c>
       <c r="E28" t="str">
-        <v>2690</v>
+        <v>990</v>
       </c>
       <c r="F28" t="str">
         <v>Por peso</v>
@@ -961,19 +961,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>742011</v>
+        <v>742013</v>
       </c>
       <c r="B29" t="str">
-        <v>LIMON KG</v>
+        <v>MANZANA ROJA KG</v>
       </c>
       <c r="C29" t="str">
         <v/>
       </c>
       <c r="D29" t="str">
-        <v>42011</v>
+        <v>42013</v>
       </c>
       <c r="E29" t="str">
-        <v>1290</v>
+        <v>990</v>
       </c>
       <c r="F29" t="str">
         <v>Por peso</v>
@@ -981,19 +981,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>742010</v>
+        <v>742066</v>
       </c>
       <c r="B30" t="str">
-        <v>KIWI KG</v>
+        <v>MANZANA ROYAL GALA KG</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30" t="str">
-        <v>42010</v>
+        <v>42066</v>
       </c>
       <c r="E30" t="str">
-        <v>1190</v>
+        <v>990</v>
       </c>
       <c r="F30" t="str">
         <v>Por peso</v>
@@ -1001,19 +1001,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>742051</v>
+        <v>742067</v>
       </c>
       <c r="B31" t="str">
-        <v>GRANADAS KG</v>
+        <v>MANZANA FUJI KG</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>42051</v>
+        <v>42067</v>
       </c>
       <c r="E31" t="str">
-        <v>1990</v>
+        <v>990</v>
       </c>
       <c r="F31" t="str">
         <v>Por peso</v>
@@ -1021,19 +1021,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>742012</v>
+        <v>742102</v>
       </c>
       <c r="B32" t="str">
-        <v>NECTARIN PLATANO KG</v>
+        <v>MANGOS KG</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>42012</v>
+        <v>42102</v>
       </c>
       <c r="E32" t="str">
-        <v>990</v>
+        <v>2690</v>
       </c>
       <c r="F32" t="str">
         <v>Por peso</v>
@@ -1041,19 +1041,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>742014</v>
+        <v>742051</v>
       </c>
       <c r="B33" t="str">
-        <v>DURAZNO CONSERVERO KG</v>
+        <v>GRANADAS KG</v>
       </c>
       <c r="C33" t="str">
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>42014</v>
+        <v>42051</v>
       </c>
       <c r="E33" t="str">
-        <v>1190</v>
+        <v>1990</v>
       </c>
       <c r="F33" t="str">
         <v>Por peso</v>
@@ -1061,16 +1061,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>742009</v>
+        <v>742012</v>
       </c>
       <c r="B34" t="str">
-        <v>DURAZNO AMARILLO KG</v>
+        <v>NECTARIN PLATANO KG</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>42009</v>
+        <v>42012</v>
       </c>
       <c r="E34" t="str">
         <v>990</v>
@@ -1081,19 +1081,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>742122</v>
+        <v>742014</v>
       </c>
       <c r="B35" t="str">
-        <v>DURAZNO BLANCO KG</v>
+        <v>DURAZNO CONSERVERO KG</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>42122</v>
+        <v>42014</v>
       </c>
       <c r="E35" t="str">
-        <v>990</v>
+        <v>1190</v>
       </c>
       <c r="F35" t="str">
         <v>Por peso</v>
@@ -1101,19 +1101,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>742033</v>
+        <v>742009</v>
       </c>
       <c r="B36" t="str">
-        <v>CIRUELA KG</v>
+        <v>DURAZNO AMARILLO KG</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>42033</v>
+        <v>42009</v>
       </c>
       <c r="E36" t="str">
-        <v>690</v>
+        <v>990</v>
       </c>
       <c r="F36" t="str">
         <v>Por peso</v>
@@ -1121,19 +1121,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>742040</v>
+        <v>742122</v>
       </c>
       <c r="B37" t="str">
-        <v>TUNAS KG</v>
+        <v>DURAZNO BLANCO KG</v>
       </c>
       <c r="C37" t="str">
         <v/>
       </c>
       <c r="D37" t="str">
-        <v>42040</v>
+        <v>42122</v>
       </c>
       <c r="E37" t="str">
-        <v>1190</v>
+        <v>990</v>
       </c>
       <c r="F37" t="str">
         <v>Por peso</v>
@@ -1141,16 +1141,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>742042</v>
+        <v>742040</v>
       </c>
       <c r="B38" t="str">
-        <v>UVA NEGRA KG</v>
+        <v>TUNAS KG</v>
       </c>
       <c r="C38" t="str">
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>42042</v>
+        <v>42040</v>
       </c>
       <c r="E38" t="str">
         <v>1190</v>
@@ -1161,19 +1161,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>742041</v>
+        <v>742042</v>
       </c>
       <c r="B39" t="str">
-        <v>TOMATE LARGA VIDA KG</v>
+        <v>UVA NEGRA KG</v>
       </c>
       <c r="C39" t="str">
         <v/>
       </c>
       <c r="D39" t="str">
-        <v>42041</v>
+        <v>42042</v>
       </c>
       <c r="E39" t="str">
-        <v>1690</v>
+        <v>1190</v>
       </c>
       <c r="F39" t="str">
         <v>Por peso</v>
@@ -1181,19 +1181,19 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>742166</v>
+        <v>742041</v>
       </c>
       <c r="B40" t="str">
-        <v>CACAO AMARGO KG FFVV</v>
+        <v>TOMATE LARGA VIDA KG</v>
       </c>
       <c r="C40" t="str">
         <v/>
       </c>
       <c r="D40" t="str">
-        <v>42166</v>
+        <v>42041</v>
       </c>
       <c r="E40" t="str">
-        <v>14760</v>
+        <v>1690</v>
       </c>
       <c r="F40" t="str">
         <v>Por peso</v>
@@ -1201,19 +1201,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>742135</v>
+        <v>742166</v>
       </c>
       <c r="B41" t="str">
-        <v>SANDIA EXTRA PP KG</v>
+        <v>CACAO AMARGO KG FFVV</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
       <c r="D41" t="str">
-        <v>42135</v>
+        <v>42166</v>
       </c>
       <c r="E41" t="str">
-        <v>490</v>
+        <v>14760</v>
       </c>
       <c r="F41" t="str">
         <v>Por peso</v>
@@ -1221,19 +1221,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>741835</v>
+        <v>742135</v>
       </c>
       <c r="B42" t="str">
-        <v>ANIS ESTRELLA KG FFVV</v>
+        <v>SANDIA EXTRA PP KG</v>
       </c>
       <c r="C42" t="str">
         <v/>
       </c>
       <c r="D42" t="str">
-        <v>41835</v>
+        <v>42135</v>
       </c>
       <c r="E42" t="str">
-        <v>27160</v>
+        <v>490</v>
       </c>
       <c r="F42" t="str">
         <v>Por peso</v>
@@ -1241,19 +1241,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>741828</v>
+        <v>741835</v>
       </c>
       <c r="B43" t="str">
-        <v>PEPINO FRUTA LIQUIDACION</v>
+        <v>ANIS ESTRELLA KG FFVV</v>
       </c>
       <c r="C43" t="str">
         <v/>
       </c>
       <c r="D43" t="str">
-        <v>41828</v>
+        <v>41835</v>
       </c>
       <c r="E43" t="str">
-        <v>9990</v>
+        <v>27160</v>
       </c>
       <c r="F43" t="str">
         <v>Por peso</v>
@@ -1261,19 +1261,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>741826</v>
+        <v>741828</v>
       </c>
       <c r="B44" t="str">
-        <v>TOMATE CHERRY KG FFVV</v>
+        <v>PEPINO FRUTA LIQUIDACION</v>
       </c>
       <c r="C44" t="str">
         <v/>
       </c>
       <c r="D44" t="str">
-        <v>41826</v>
+        <v>41828</v>
       </c>
       <c r="E44" t="str">
-        <v>4760</v>
+        <v>9990</v>
       </c>
       <c r="F44" t="str">
         <v>Por peso</v>
@@ -1281,19 +1281,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>741820</v>
+        <v>741826</v>
       </c>
       <c r="B45" t="str">
-        <v>MERKEN KG FFVV</v>
+        <v>TOMATE CHERRY KG FFVV</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45" t="str">
-        <v>41820</v>
+        <v>41826</v>
       </c>
       <c r="E45" t="str">
-        <v>12360</v>
+        <v>4760</v>
       </c>
       <c r="F45" t="str">
         <v>Por peso</v>
@@ -1301,19 +1301,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>745142</v>
+        <v>741820</v>
       </c>
       <c r="B46" t="str">
-        <v>CEBOLLA MORADA KG</v>
+        <v>MERKEN KG FFVV</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46" t="str">
-        <v>45142</v>
+        <v>41820</v>
       </c>
       <c r="E46" t="str">
-        <v>790</v>
+        <v>12360</v>
       </c>
       <c r="F46" t="str">
         <v>Por peso</v>
@@ -1321,19 +1321,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>742075</v>
+        <v>745142</v>
       </c>
       <c r="B47" t="str">
-        <v>PERA FORELLE KG</v>
+        <v>CEBOLLA MORADA KG</v>
       </c>
       <c r="C47" t="str">
         <v/>
       </c>
       <c r="D47" t="str">
-        <v>42075</v>
+        <v>45142</v>
       </c>
       <c r="E47" t="str">
-        <v>890</v>
+        <v>790</v>
       </c>
       <c r="F47" t="str">
         <v>Por peso</v>
@@ -1341,19 +1341,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>742118</v>
+        <v>742075</v>
       </c>
       <c r="B48" t="str">
-        <v>CLEMENTINA MANDARINA KG</v>
+        <v>PERA FORELLE KG</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>42118</v>
+        <v>42075</v>
       </c>
       <c r="E48" t="str">
-        <v>1590</v>
+        <v>890</v>
       </c>
       <c r="F48" t="str">
         <v>Por peso</v>
@@ -1361,19 +1361,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>742016</v>
+        <v>742118</v>
       </c>
       <c r="B49" t="str">
-        <v>CASTANAS KILO FFVV</v>
+        <v>CLEMENTINA MANDARINA KG</v>
       </c>
       <c r="C49" t="str">
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>42016</v>
+        <v>42118</v>
       </c>
       <c r="E49" t="str">
-        <v>1990</v>
+        <v>1590</v>
       </c>
       <c r="F49" t="str">
         <v>Por peso</v>
@@ -1381,19 +1381,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>742001</v>
+        <v>742016</v>
       </c>
       <c r="B50" t="str">
-        <v>FRUTA CONFITADA KG FFVV</v>
+        <v>CASTANAS KILO FFVV</v>
       </c>
       <c r="C50" t="str">
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>42001</v>
+        <v>42016</v>
       </c>
       <c r="E50" t="str">
-        <v>5560</v>
+        <v>1990</v>
       </c>
       <c r="F50" t="str">
         <v>Por peso</v>
@@ -1401,19 +1401,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>742158</v>
+        <v>742001</v>
       </c>
       <c r="B51" t="str">
-        <v>MANZANA CRISS PINK KG</v>
+        <v>FRUTA CONFITADA KG FFVV</v>
       </c>
       <c r="C51" t="str">
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>42158</v>
+        <v>42001</v>
       </c>
       <c r="E51" t="str">
-        <v>990</v>
+        <v>5560</v>
       </c>
       <c r="F51" t="str">
         <v>Por peso</v>
@@ -1421,19 +1421,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>741064</v>
+        <v>742158</v>
       </c>
       <c r="B52" t="str">
-        <v>ZAPALLO JAMBOREE SAMPSON PP KG</v>
+        <v>MANZANA CRISS PINK KG</v>
       </c>
       <c r="C52" t="str">
         <v/>
       </c>
       <c r="D52" t="str">
-        <v>41064</v>
+        <v>42158</v>
       </c>
       <c r="E52" t="str">
-        <v>790</v>
+        <v>990</v>
       </c>
       <c r="F52" t="str">
         <v>Por peso</v>
@@ -1441,16 +1441,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>741039</v>
+        <v>741064</v>
       </c>
       <c r="B53" t="str">
-        <v>ZAPALLO CAMOTE KG</v>
+        <v>ZAPALLO JAMBOREE SAMPSON PP KG</v>
       </c>
       <c r="C53" t="str">
         <v/>
       </c>
       <c r="D53" t="str">
-        <v>41039</v>
+        <v>41064</v>
       </c>
       <c r="E53" t="str">
         <v>790</v>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>741025</v>
+        <v>741039</v>
       </c>
       <c r="B54" t="str">
-        <v>POROTO VERDE KG</v>
+        <v>ZAPALLO CAMOTE KG</v>
       </c>
       <c r="C54" t="str">
         <v/>
       </c>
       <c r="D54" t="str">
-        <v>41025</v>
+        <v>41039</v>
       </c>
       <c r="E54" t="str">
-        <v>2290</v>
+        <v>790</v>
       </c>
       <c r="F54" t="str">
         <v>Por peso</v>
@@ -1481,16 +1481,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>741026</v>
+        <v>741025</v>
       </c>
       <c r="B55" t="str">
-        <v>POROTO GRANADO KG</v>
+        <v>POROTO VERDE KG</v>
       </c>
       <c r="C55" t="str">
         <v/>
       </c>
       <c r="D55" t="str">
-        <v>41026</v>
+        <v>41025</v>
       </c>
       <c r="E55" t="str">
         <v>2290</v>
@@ -1501,19 +1501,19 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>741051</v>
+        <v>741026</v>
       </c>
       <c r="B56" t="str">
-        <v>PAPA LAVADA KG</v>
+        <v>POROTO GRANADO KG</v>
       </c>
       <c r="C56" t="str">
         <v/>
       </c>
       <c r="D56" t="str">
-        <v>41051</v>
+        <v>41026</v>
       </c>
       <c r="E56" t="str">
-        <v>890</v>
+        <v>2290</v>
       </c>
       <c r="F56" t="str">
         <v>Por peso</v>
@@ -1521,19 +1521,19 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>741002</v>
+        <v>741051</v>
       </c>
       <c r="B57" t="str">
-        <v>AJI LIQUIDACION</v>
+        <v>PAPA LAVADA KG</v>
       </c>
       <c r="C57" t="str">
         <v/>
       </c>
       <c r="D57" t="str">
-        <v>41002</v>
+        <v>41051</v>
       </c>
       <c r="E57" t="str">
-        <v>9990</v>
+        <v>890</v>
       </c>
       <c r="F57" t="str">
         <v>Por peso</v>
@@ -1541,19 +1541,19 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>741021</v>
+        <v>741002</v>
       </c>
       <c r="B58" t="str">
-        <v>MOTE KG</v>
+        <v>AJI LIQUIDACION</v>
       </c>
       <c r="C58" t="str">
         <v/>
       </c>
       <c r="D58" t="str">
-        <v>41021</v>
+        <v>41002</v>
       </c>
       <c r="E58" t="str">
-        <v>1290</v>
+        <v>9990</v>
       </c>
       <c r="F58" t="str">
         <v>Por peso</v>
@@ -1561,19 +1561,19 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>741014</v>
+        <v>741021</v>
       </c>
       <c r="B59" t="str">
-        <v>HABAS KG</v>
+        <v>MOTE KG</v>
       </c>
       <c r="C59" t="str">
         <v/>
       </c>
       <c r="D59" t="str">
-        <v>41014</v>
+        <v>41021</v>
       </c>
       <c r="E59" t="str">
-        <v>990</v>
+        <v>1290</v>
       </c>
       <c r="F59" t="str">
         <v>Por peso</v>
@@ -1581,19 +1581,19 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>741046</v>
+        <v>741014</v>
       </c>
       <c r="B60" t="str">
-        <v>AJI CACHO CABRA SECO KG</v>
+        <v>HABAS KG</v>
       </c>
       <c r="C60" t="str">
         <v/>
       </c>
       <c r="D60" t="str">
-        <v>41046</v>
+        <v>41014</v>
       </c>
       <c r="E60" t="str">
-        <v>13160</v>
+        <v>990</v>
       </c>
       <c r="F60" t="str">
         <v>Por peso</v>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>741079</v>
+        <v>741046</v>
       </c>
       <c r="B61" t="str">
-        <v>CEBOLLA BLANCA CRISTAL KG</v>
+        <v>AJI CACHO CABRA SECO KG</v>
       </c>
       <c r="C61" t="str">
         <v/>
       </c>
       <c r="D61" t="str">
-        <v>41079</v>
+        <v>41046</v>
       </c>
       <c r="E61" t="str">
-        <v>790</v>
+        <v>13160</v>
       </c>
       <c r="F61" t="str">
         <v>Por peso</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>741080</v>
+        <v>741079</v>
       </c>
       <c r="B62" t="str">
-        <v>CEBOLLA CUGAT PP KG</v>
+        <v>CEBOLLA BLANCA CRISTAL KG</v>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
       <c r="D62" t="str">
-        <v>41080</v>
+        <v>41079</v>
       </c>
       <c r="E62" t="str">
-        <v>690</v>
+        <v>790</v>
       </c>
       <c r="F62" t="str">
         <v>Por peso</v>
@@ -1641,19 +1641,19 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>741055</v>
+        <v>741080</v>
       </c>
       <c r="B63" t="str">
-        <v>BRUSELAS KG</v>
+        <v>CEBOLLA CUGAT PP KG</v>
       </c>
       <c r="C63" t="str">
         <v/>
       </c>
       <c r="D63" t="str">
-        <v>41055</v>
+        <v>41080</v>
       </c>
       <c r="E63" t="str">
-        <v>2590</v>
+        <v>690</v>
       </c>
       <c r="F63" t="str">
         <v>Por peso</v>
@@ -1661,19 +1661,19 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>741129</v>
+        <v>741055</v>
       </c>
       <c r="B64" t="str">
-        <v>PAPA SURENA KILO</v>
+        <v>BRUSELAS KG</v>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64" t="str">
-        <v>41129</v>
+        <v>41055</v>
       </c>
       <c r="E64" t="str">
-        <v>690</v>
+        <v>2590</v>
       </c>
       <c r="F64" t="str">
         <v>Por peso</v>
@@ -1681,16 +1681,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>741042</v>
+        <v>741129</v>
       </c>
       <c r="B65" t="str">
-        <v>ZANAHORIA KG</v>
+        <v>PAPA SURENA KILO</v>
       </c>
       <c r="C65" t="str">
         <v/>
       </c>
       <c r="D65" t="str">
-        <v>41042</v>
+        <v>41129</v>
       </c>
       <c r="E65" t="str">
         <v>690</v>

--- a/MaestraPLU_FFVV.xlsx
+++ b/MaestraPLU_FFVV.xlsx
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>742011</v>
+        <v>741032</v>
       </c>
       <c r="B2" t="str">
-        <v>LIMON KG</v>
+        <v>JENGIBRE KG</v>
       </c>
       <c r="C2" t="str">
         <v/>
       </c>
       <c r="D2" t="str">
-        <v>42011</v>
+        <v>51032</v>
       </c>
       <c r="E2" t="str">
-        <v>1090</v>
+        <v>3560</v>
       </c>
       <c r="F2" t="str">
         <v>Por peso</v>
@@ -441,19 +441,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>742033</v>
+        <v>745146</v>
       </c>
       <c r="B3" t="str">
-        <v>CIRUELA KG</v>
+        <v>ALMENDRA KG FFVV</v>
       </c>
       <c r="C3" t="str">
         <v/>
       </c>
       <c r="D3" t="str">
-        <v>42033</v>
+        <v>45146</v>
       </c>
       <c r="E3" t="str">
-        <v>500</v>
+        <v>16760</v>
       </c>
       <c r="F3" t="str">
         <v>Por peso</v>
@@ -461,19 +461,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>742010</v>
+        <v>744023</v>
       </c>
       <c r="B4" t="str">
-        <v>KIWI KG</v>
+        <v>CHUCHOCA MOLIDA KG FFVV</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
       <c r="D4" t="str">
-        <v>42010</v>
+        <v>44023</v>
       </c>
       <c r="E4" t="str">
-        <v>990</v>
+        <v>1960</v>
       </c>
       <c r="F4" t="str">
         <v>Por peso</v>
@@ -481,19 +481,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>741042</v>
+        <v>743024</v>
       </c>
       <c r="B5" t="str">
-        <v>ZANAHORIA KG</v>
+        <v>PASAS MORENAS KG FFVV</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5" t="str">
-        <v>41042</v>
+        <v>43024</v>
       </c>
       <c r="E5" t="str">
-        <v>500</v>
+        <v>5160</v>
       </c>
       <c r="F5" t="str">
         <v>Por peso</v>
@@ -501,19 +501,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>741032</v>
+        <v>744019</v>
       </c>
       <c r="B6" t="str">
-        <v>JENGIBRE KG</v>
+        <v>PASAS RUBIA KG FFVV</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
       <c r="D6" t="str">
-        <v>51032</v>
+        <v>44019</v>
       </c>
       <c r="E6" t="str">
-        <v>3560</v>
+        <v>9960</v>
       </c>
       <c r="F6" t="str">
         <v>Por peso</v>
@@ -521,19 +521,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>745146</v>
+        <v>744160</v>
       </c>
       <c r="B7" t="str">
-        <v>ALMENDRA KG FFVV</v>
+        <v>YUCA KG FFVV</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7" t="str">
-        <v>45146</v>
+        <v>44160</v>
       </c>
       <c r="E7" t="str">
-        <v>16760</v>
+        <v>3490</v>
       </c>
       <c r="F7" t="str">
         <v>Por peso</v>
@@ -541,19 +541,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>744023</v>
+        <v>744153</v>
       </c>
       <c r="B8" t="str">
-        <v>CHUCHOCA MOLIDA KG FFVV</v>
+        <v>TUNAS LIQUIDACION KG</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>44023</v>
+        <v>44153</v>
       </c>
       <c r="E8" t="str">
-        <v>1960</v>
+        <v>9990</v>
       </c>
       <c r="F8" t="str">
         <v>Por peso</v>
@@ -561,19 +561,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>743024</v>
+        <v>744146</v>
       </c>
       <c r="B9" t="str">
-        <v>PASAS MORENAS KG FFVV</v>
+        <v>FLOR DE JAMAICA KG FFVV</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9" t="str">
-        <v>43024</v>
+        <v>44146</v>
       </c>
       <c r="E9" t="str">
-        <v>5160</v>
+        <v>27960</v>
       </c>
       <c r="F9" t="str">
         <v>Por peso</v>
@@ -581,19 +581,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>744019</v>
+        <v>745147</v>
       </c>
       <c r="B10" t="str">
-        <v>PASAS RUBIA KG FFVV</v>
+        <v>HUESILLOS KG FFVV</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>44019</v>
+        <v>45147</v>
       </c>
       <c r="E10" t="str">
-        <v>9960</v>
+        <v>9560</v>
       </c>
       <c r="F10" t="str">
         <v>Por peso</v>
@@ -601,19 +601,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>744160</v>
+        <v>742072</v>
       </c>
       <c r="B11" t="str">
-        <v>YUCA KG FFVV</v>
+        <v>SANDIA PRIMERA PP KG</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>44160</v>
+        <v>42072</v>
       </c>
       <c r="E11" t="str">
-        <v>3490</v>
+        <v>490</v>
       </c>
       <c r="F11" t="str">
         <v>Por peso</v>
@@ -621,19 +621,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>744153</v>
+        <v>742031</v>
       </c>
       <c r="B12" t="str">
-        <v>TUNAS LIQUIDACION KG</v>
+        <v>PLATANO KG</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12" t="str">
-        <v>44153</v>
+        <v>42031</v>
       </c>
       <c r="E12" t="str">
-        <v>9990</v>
+        <v>1690</v>
       </c>
       <c r="F12" t="str">
         <v>Por peso</v>
@@ -641,19 +641,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>744146</v>
+        <v>742025</v>
       </c>
       <c r="B13" t="str">
-        <v>FLOR DE JAMAICA KG FFVV</v>
+        <v>POMELO KG</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13" t="str">
-        <v>44146</v>
+        <v>42025</v>
       </c>
       <c r="E13" t="str">
-        <v>27960</v>
+        <v>890</v>
       </c>
       <c r="F13" t="str">
         <v>Por peso</v>
@@ -661,19 +661,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>745147</v>
+        <v>742045</v>
       </c>
       <c r="B14" t="str">
-        <v>HUESILLOS KG FFVV</v>
+        <v>PERA PACKHAM KG</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>45147</v>
+        <v>42045</v>
       </c>
       <c r="E14" t="str">
-        <v>9560</v>
+        <v>890</v>
       </c>
       <c r="F14" t="str">
         <v>Por peso</v>
@@ -681,19 +681,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>742072</v>
+        <v>742024</v>
       </c>
       <c r="B15" t="str">
-        <v>SANDIA PRIMERA PP KG</v>
+        <v>PERA WINTERNELLY KG</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>42072</v>
+        <v>42024</v>
       </c>
       <c r="E15" t="str">
-        <v>490</v>
+        <v>890</v>
       </c>
       <c r="F15" t="str">
         <v>Por peso</v>
@@ -701,19 +701,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>742031</v>
+        <v>742082</v>
       </c>
       <c r="B16" t="str">
-        <v>PLATANO KG</v>
+        <v>PERA BERRY BOSC</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>42031</v>
+        <v>42082</v>
       </c>
       <c r="E16" t="str">
-        <v>1690</v>
+        <v>890</v>
       </c>
       <c r="F16" t="str">
         <v>Por peso</v>
@@ -721,19 +721,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>742025</v>
+        <v>742081</v>
       </c>
       <c r="B17" t="str">
-        <v>POMELO KG</v>
+        <v>PERA ASIATICA KG</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>42025</v>
+        <v>42081</v>
       </c>
       <c r="E17" t="str">
-        <v>890</v>
+        <v>990</v>
       </c>
       <c r="F17" t="str">
         <v>Por peso</v>
@@ -741,19 +741,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>742049</v>
+        <v>742026</v>
       </c>
       <c r="B18" t="str">
-        <v>PERA SUMMER FAVORITA KG</v>
+        <v>PEPINO FRUTA KG</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>42049</v>
+        <v>42026</v>
       </c>
       <c r="E18" t="str">
-        <v>990</v>
+        <v>1790</v>
       </c>
       <c r="F18" t="str">
         <v>Por peso</v>
@@ -761,19 +761,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>742045</v>
+        <v>742036</v>
       </c>
       <c r="B19" t="str">
-        <v>PERA PACKHAM KG</v>
+        <v>PAPAYA KG</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>42045</v>
+        <v>42036</v>
       </c>
       <c r="E19" t="str">
-        <v>890</v>
+        <v>2990</v>
       </c>
       <c r="F19" t="str">
         <v>Por peso</v>
@@ -781,19 +781,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>742024</v>
+        <v>742022</v>
       </c>
       <c r="B20" t="str">
-        <v>PERA WINTERNELLY KG</v>
+        <v>NUECES KG FFVV</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>42024</v>
+        <v>42022</v>
       </c>
       <c r="E20" t="str">
-        <v>890</v>
+        <v>14760</v>
       </c>
       <c r="F20" t="str">
         <v>Por peso</v>
@@ -801,19 +801,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>742082</v>
+        <v>742018</v>
       </c>
       <c r="B21" t="str">
-        <v>PERA BERRY BOSC</v>
+        <v>NECTARIN AMARILLO KG</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>42082</v>
+        <v>42018</v>
       </c>
       <c r="E21" t="str">
-        <v>890</v>
+        <v>1290</v>
       </c>
       <c r="F21" t="str">
         <v>Por peso</v>
@@ -821,16 +821,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>742081</v>
+        <v>742044</v>
       </c>
       <c r="B22" t="str">
-        <v>PERA ASIATICA KG</v>
+        <v>MEMBRILLO KG</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>42081</v>
+        <v>42044</v>
       </c>
       <c r="E22" t="str">
         <v>990</v>
@@ -841,19 +841,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>742026</v>
+        <v>742015</v>
       </c>
       <c r="B23" t="str">
-        <v>PEPINO FRUTA KG</v>
+        <v>MANZANA VERDE KG</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>42026</v>
+        <v>42015</v>
       </c>
       <c r="E23" t="str">
-        <v>1790</v>
+        <v>990</v>
       </c>
       <c r="F23" t="str">
         <v>Por peso</v>
@@ -861,19 +861,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>742036</v>
+        <v>742013</v>
       </c>
       <c r="B24" t="str">
-        <v>PAPAYA KG</v>
+        <v>MANZANA ROJA KG</v>
       </c>
       <c r="C24" t="str">
         <v/>
       </c>
       <c r="D24" t="str">
-        <v>42036</v>
+        <v>42013</v>
       </c>
       <c r="E24" t="str">
-        <v>2990</v>
+        <v>990</v>
       </c>
       <c r="F24" t="str">
         <v>Por peso</v>
@@ -881,19 +881,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>742022</v>
+        <v>742066</v>
       </c>
       <c r="B25" t="str">
-        <v>NUECES KG FFVV</v>
+        <v>MANZANA ROYAL GALA KG</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>42022</v>
+        <v>42066</v>
       </c>
       <c r="E25" t="str">
-        <v>14760</v>
+        <v>990</v>
       </c>
       <c r="F25" t="str">
         <v>Por peso</v>
@@ -901,19 +901,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>742018</v>
+        <v>742067</v>
       </c>
       <c r="B26" t="str">
-        <v>NECTARIN AMARILLO KG</v>
+        <v>MANZANA FUJI KG</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
       <c r="D26" t="str">
-        <v>42018</v>
+        <v>42067</v>
       </c>
       <c r="E26" t="str">
-        <v>1290</v>
+        <v>990</v>
       </c>
       <c r="F26" t="str">
         <v>Por peso</v>
@@ -921,19 +921,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>742044</v>
+        <v>742102</v>
       </c>
       <c r="B27" t="str">
-        <v>MEMBRILLO KG</v>
+        <v>MANGOS KG</v>
       </c>
       <c r="C27" t="str">
         <v/>
       </c>
       <c r="D27" t="str">
-        <v>42044</v>
+        <v>42102</v>
       </c>
       <c r="E27" t="str">
-        <v>990</v>
+        <v>2890</v>
       </c>
       <c r="F27" t="str">
         <v>Por peso</v>
@@ -941,19 +941,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>742015</v>
+        <v>742011</v>
       </c>
       <c r="B28" t="str">
-        <v>MANZANA VERDE KG</v>
+        <v>LIMON KG</v>
       </c>
       <c r="C28" t="str">
         <v/>
       </c>
       <c r="D28" t="str">
-        <v>42015</v>
+        <v>42011</v>
       </c>
       <c r="E28" t="str">
-        <v>990</v>
+        <v>1290</v>
       </c>
       <c r="F28" t="str">
         <v>Por peso</v>
@@ -961,19 +961,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>742013</v>
+        <v>742010</v>
       </c>
       <c r="B29" t="str">
-        <v>MANZANA ROJA KG</v>
+        <v>KIWI KG</v>
       </c>
       <c r="C29" t="str">
         <v/>
       </c>
       <c r="D29" t="str">
-        <v>42013</v>
+        <v>42010</v>
       </c>
       <c r="E29" t="str">
-        <v>990</v>
+        <v>1190</v>
       </c>
       <c r="F29" t="str">
         <v>Por peso</v>
@@ -981,19 +981,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>742066</v>
+        <v>742051</v>
       </c>
       <c r="B30" t="str">
-        <v>MANZANA ROYAL GALA KG</v>
+        <v>GRANADAS KG</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30" t="str">
-        <v>42066</v>
+        <v>42051</v>
       </c>
       <c r="E30" t="str">
-        <v>990</v>
+        <v>1990</v>
       </c>
       <c r="F30" t="str">
         <v>Por peso</v>
@@ -1001,16 +1001,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>742067</v>
+        <v>742012</v>
       </c>
       <c r="B31" t="str">
-        <v>MANZANA FUJI KG</v>
+        <v>NECTARIN PLATANO KG</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>42067</v>
+        <v>42012</v>
       </c>
       <c r="E31" t="str">
         <v>990</v>
@@ -1021,19 +1021,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>742102</v>
+        <v>742014</v>
       </c>
       <c r="B32" t="str">
-        <v>MANGOS KG</v>
+        <v>DURAZNO CONSERVERO KG</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>42102</v>
+        <v>42014</v>
       </c>
       <c r="E32" t="str">
-        <v>2690</v>
+        <v>1190</v>
       </c>
       <c r="F32" t="str">
         <v>Por peso</v>
@@ -1041,19 +1041,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>742051</v>
+        <v>742009</v>
       </c>
       <c r="B33" t="str">
-        <v>GRANADAS KG</v>
+        <v>DURAZNO AMARILLO KG</v>
       </c>
       <c r="C33" t="str">
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>42051</v>
+        <v>42009</v>
       </c>
       <c r="E33" t="str">
-        <v>1990</v>
+        <v>990</v>
       </c>
       <c r="F33" t="str">
         <v>Por peso</v>
@@ -1061,16 +1061,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>742012</v>
+        <v>742122</v>
       </c>
       <c r="B34" t="str">
-        <v>NECTARIN PLATANO KG</v>
+        <v>DURAZNO BLANCO KG</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>42012</v>
+        <v>42122</v>
       </c>
       <c r="E34" t="str">
         <v>990</v>
@@ -1081,19 +1081,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>742014</v>
+        <v>742033</v>
       </c>
       <c r="B35" t="str">
-        <v>DURAZNO CONSERVERO KG</v>
+        <v>CIRUELA KG</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>42014</v>
+        <v>42033</v>
       </c>
       <c r="E35" t="str">
-        <v>1190</v>
+        <v>690</v>
       </c>
       <c r="F35" t="str">
         <v>Por peso</v>
@@ -1101,19 +1101,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>742009</v>
+        <v>742040</v>
       </c>
       <c r="B36" t="str">
-        <v>DURAZNO AMARILLO KG</v>
+        <v>TUNAS KG</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>42009</v>
+        <v>42040</v>
       </c>
       <c r="E36" t="str">
-        <v>990</v>
+        <v>1190</v>
       </c>
       <c r="F36" t="str">
         <v>Por peso</v>
@@ -1121,19 +1121,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>742122</v>
+        <v>742042</v>
       </c>
       <c r="B37" t="str">
-        <v>DURAZNO BLANCO KG</v>
+        <v>UVA NEGRA KG</v>
       </c>
       <c r="C37" t="str">
         <v/>
       </c>
       <c r="D37" t="str">
-        <v>42122</v>
+        <v>42042</v>
       </c>
       <c r="E37" t="str">
-        <v>990</v>
+        <v>1190</v>
       </c>
       <c r="F37" t="str">
         <v>Por peso</v>
@@ -1141,19 +1141,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>742040</v>
+        <v>742041</v>
       </c>
       <c r="B38" t="str">
-        <v>TUNAS KG</v>
+        <v>TOMATE LARGA VIDA KG</v>
       </c>
       <c r="C38" t="str">
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>42040</v>
+        <v>42041</v>
       </c>
       <c r="E38" t="str">
-        <v>1190</v>
+        <v>1690</v>
       </c>
       <c r="F38" t="str">
         <v>Por peso</v>
@@ -1161,19 +1161,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>742042</v>
+        <v>742166</v>
       </c>
       <c r="B39" t="str">
-        <v>UVA NEGRA KG</v>
+        <v>CACAO AMARGO KG FFVV</v>
       </c>
       <c r="C39" t="str">
         <v/>
       </c>
       <c r="D39" t="str">
-        <v>42042</v>
+        <v>42166</v>
       </c>
       <c r="E39" t="str">
-        <v>1190</v>
+        <v>14760</v>
       </c>
       <c r="F39" t="str">
         <v>Por peso</v>
@@ -1181,19 +1181,19 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>742041</v>
+        <v>742135</v>
       </c>
       <c r="B40" t="str">
-        <v>TOMATE LARGA VIDA KG</v>
+        <v>SANDIA EXTRA PP KG</v>
       </c>
       <c r="C40" t="str">
         <v/>
       </c>
       <c r="D40" t="str">
-        <v>42041</v>
+        <v>42135</v>
       </c>
       <c r="E40" t="str">
-        <v>1690</v>
+        <v>490</v>
       </c>
       <c r="F40" t="str">
         <v>Por peso</v>
@@ -1201,19 +1201,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>742166</v>
+        <v>741835</v>
       </c>
       <c r="B41" t="str">
-        <v>CACAO AMARGO KG FFVV</v>
+        <v>ANIS ESTRELLA KG FFVV</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
       <c r="D41" t="str">
-        <v>42166</v>
+        <v>41835</v>
       </c>
       <c r="E41" t="str">
-        <v>14760</v>
+        <v>27160</v>
       </c>
       <c r="F41" t="str">
         <v>Por peso</v>
@@ -1221,19 +1221,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>742135</v>
+        <v>741828</v>
       </c>
       <c r="B42" t="str">
-        <v>SANDIA EXTRA PP KG</v>
+        <v>PEPINO FRUTA LIQUIDACION</v>
       </c>
       <c r="C42" t="str">
         <v/>
       </c>
       <c r="D42" t="str">
-        <v>42135</v>
+        <v>41828</v>
       </c>
       <c r="E42" t="str">
-        <v>490</v>
+        <v>9990</v>
       </c>
       <c r="F42" t="str">
         <v>Por peso</v>
@@ -1241,19 +1241,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>741835</v>
+        <v>741826</v>
       </c>
       <c r="B43" t="str">
-        <v>ANIS ESTRELLA KG FFVV</v>
+        <v>TOMATE CHERRY KG FFVV</v>
       </c>
       <c r="C43" t="str">
         <v/>
       </c>
       <c r="D43" t="str">
-        <v>41835</v>
+        <v>41826</v>
       </c>
       <c r="E43" t="str">
-        <v>27160</v>
+        <v>4760</v>
       </c>
       <c r="F43" t="str">
         <v>Por peso</v>
@@ -1261,19 +1261,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>741828</v>
+        <v>741820</v>
       </c>
       <c r="B44" t="str">
-        <v>PEPINO FRUTA LIQUIDACION</v>
+        <v>MERKEN KG FFVV</v>
       </c>
       <c r="C44" t="str">
         <v/>
       </c>
       <c r="D44" t="str">
-        <v>41828</v>
+        <v>41820</v>
       </c>
       <c r="E44" t="str">
-        <v>9990</v>
+        <v>12360</v>
       </c>
       <c r="F44" t="str">
         <v>Por peso</v>
@@ -1281,19 +1281,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>741826</v>
+        <v>745142</v>
       </c>
       <c r="B45" t="str">
-        <v>TOMATE CHERRY KG FFVV</v>
+        <v>CEBOLLA MORADA KG</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45" t="str">
-        <v>41826</v>
+        <v>45142</v>
       </c>
       <c r="E45" t="str">
-        <v>4760</v>
+        <v>790</v>
       </c>
       <c r="F45" t="str">
         <v>Por peso</v>
@@ -1301,19 +1301,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>741820</v>
+        <v>742075</v>
       </c>
       <c r="B46" t="str">
-        <v>MERKEN KG FFVV</v>
+        <v>PERA FORELLE KG</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46" t="str">
-        <v>41820</v>
+        <v>42075</v>
       </c>
       <c r="E46" t="str">
-        <v>12360</v>
+        <v>890</v>
       </c>
       <c r="F46" t="str">
         <v>Por peso</v>
@@ -1321,19 +1321,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>745142</v>
+        <v>742118</v>
       </c>
       <c r="B47" t="str">
-        <v>CEBOLLA MORADA KG</v>
+        <v>CLEMENTINA MANDARINA KG</v>
       </c>
       <c r="C47" t="str">
         <v/>
       </c>
       <c r="D47" t="str">
-        <v>45142</v>
+        <v>42118</v>
       </c>
       <c r="E47" t="str">
-        <v>790</v>
+        <v>1490</v>
       </c>
       <c r="F47" t="str">
         <v>Por peso</v>
@@ -1341,19 +1341,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>742075</v>
+        <v>742016</v>
       </c>
       <c r="B48" t="str">
-        <v>PERA FORELLE KG</v>
+        <v>CASTANAS KILO FFVV</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>42075</v>
+        <v>42016</v>
       </c>
       <c r="E48" t="str">
-        <v>890</v>
+        <v>1990</v>
       </c>
       <c r="F48" t="str">
         <v>Por peso</v>
@@ -1361,19 +1361,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>742118</v>
+        <v>742001</v>
       </c>
       <c r="B49" t="str">
-        <v>CLEMENTINA MANDARINA KG</v>
+        <v>FRUTA CONFITADA KG FFVV</v>
       </c>
       <c r="C49" t="str">
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>42118</v>
+        <v>42001</v>
       </c>
       <c r="E49" t="str">
-        <v>1590</v>
+        <v>5560</v>
       </c>
       <c r="F49" t="str">
         <v>Por peso</v>
@@ -1381,19 +1381,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>742016</v>
+        <v>742158</v>
       </c>
       <c r="B50" t="str">
-        <v>CASTANAS KILO FFVV</v>
+        <v>MANZANA CRISS PINK KG</v>
       </c>
       <c r="C50" t="str">
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>42016</v>
+        <v>42158</v>
       </c>
       <c r="E50" t="str">
-        <v>1990</v>
+        <v>990</v>
       </c>
       <c r="F50" t="str">
         <v>Por peso</v>
@@ -1401,19 +1401,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>742001</v>
+        <v>741064</v>
       </c>
       <c r="B51" t="str">
-        <v>FRUTA CONFITADA KG FFVV</v>
+        <v>ZAPALLO JAMBOREE SAMPSON PP KG</v>
       </c>
       <c r="C51" t="str">
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>42001</v>
+        <v>41064</v>
       </c>
       <c r="E51" t="str">
-        <v>5560</v>
+        <v>790</v>
       </c>
       <c r="F51" t="str">
         <v>Por peso</v>
@@ -1421,19 +1421,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>742158</v>
+        <v>741039</v>
       </c>
       <c r="B52" t="str">
-        <v>MANZANA CRISS PINK KG</v>
+        <v>ZAPALLO CAMOTE KG</v>
       </c>
       <c r="C52" t="str">
         <v/>
       </c>
       <c r="D52" t="str">
-        <v>42158</v>
+        <v>41039</v>
       </c>
       <c r="E52" t="str">
-        <v>990</v>
+        <v>790</v>
       </c>
       <c r="F52" t="str">
         <v>Por peso</v>
@@ -1441,19 +1441,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>741064</v>
+        <v>741025</v>
       </c>
       <c r="B53" t="str">
-        <v>ZAPALLO JAMBOREE SAMPSON PP KG</v>
+        <v>POROTO VERDE KG</v>
       </c>
       <c r="C53" t="str">
         <v/>
       </c>
       <c r="D53" t="str">
-        <v>41064</v>
+        <v>41025</v>
       </c>
       <c r="E53" t="str">
-        <v>790</v>
+        <v>2290</v>
       </c>
       <c r="F53" t="str">
         <v>Por peso</v>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>741039</v>
+        <v>741026</v>
       </c>
       <c r="B54" t="str">
-        <v>ZAPALLO CAMOTE KG</v>
+        <v>POROTO GRANADO KG</v>
       </c>
       <c r="C54" t="str">
         <v/>
       </c>
       <c r="D54" t="str">
-        <v>41039</v>
+        <v>41026</v>
       </c>
       <c r="E54" t="str">
-        <v>790</v>
+        <v>2290</v>
       </c>
       <c r="F54" t="str">
         <v>Por peso</v>
@@ -1481,19 +1481,19 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>741025</v>
+        <v>741051</v>
       </c>
       <c r="B55" t="str">
-        <v>POROTO VERDE KG</v>
+        <v>PAPA LAVADA KG</v>
       </c>
       <c r="C55" t="str">
         <v/>
       </c>
       <c r="D55" t="str">
-        <v>41025</v>
+        <v>41051</v>
       </c>
       <c r="E55" t="str">
-        <v>2290</v>
+        <v>890</v>
       </c>
       <c r="F55" t="str">
         <v>Por peso</v>
@@ -1501,19 +1501,19 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>741026</v>
+        <v>741002</v>
       </c>
       <c r="B56" t="str">
-        <v>POROTO GRANADO KG</v>
+        <v>AJI LIQUIDACION</v>
       </c>
       <c r="C56" t="str">
         <v/>
       </c>
       <c r="D56" t="str">
-        <v>41026</v>
+        <v>41002</v>
       </c>
       <c r="E56" t="str">
-        <v>2290</v>
+        <v>9990</v>
       </c>
       <c r="F56" t="str">
         <v>Por peso</v>
@@ -1521,19 +1521,19 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>741051</v>
+        <v>741021</v>
       </c>
       <c r="B57" t="str">
-        <v>PAPA LAVADA KG</v>
+        <v>MOTE KG</v>
       </c>
       <c r="C57" t="str">
         <v/>
       </c>
       <c r="D57" t="str">
-        <v>41051</v>
+        <v>41021</v>
       </c>
       <c r="E57" t="str">
-        <v>890</v>
+        <v>1290</v>
       </c>
       <c r="F57" t="str">
         <v>Por peso</v>
@@ -1541,19 +1541,19 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>741002</v>
+        <v>741014</v>
       </c>
       <c r="B58" t="str">
-        <v>AJI LIQUIDACION</v>
+        <v>HABAS KG</v>
       </c>
       <c r="C58" t="str">
         <v/>
       </c>
       <c r="D58" t="str">
-        <v>41002</v>
+        <v>41014</v>
       </c>
       <c r="E58" t="str">
-        <v>9990</v>
+        <v>990</v>
       </c>
       <c r="F58" t="str">
         <v>Por peso</v>
@@ -1561,19 +1561,19 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>741021</v>
+        <v>741046</v>
       </c>
       <c r="B59" t="str">
-        <v>MOTE KG</v>
+        <v>AJI CACHO CABRA SECO KG</v>
       </c>
       <c r="C59" t="str">
         <v/>
       </c>
       <c r="D59" t="str">
-        <v>41021</v>
+        <v>41046</v>
       </c>
       <c r="E59" t="str">
-        <v>1290</v>
+        <v>13160</v>
       </c>
       <c r="F59" t="str">
         <v>Por peso</v>
@@ -1581,19 +1581,19 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>741014</v>
+        <v>741079</v>
       </c>
       <c r="B60" t="str">
-        <v>HABAS KG</v>
+        <v>CEBOLLA BLANCA CRISTAL KG</v>
       </c>
       <c r="C60" t="str">
         <v/>
       </c>
       <c r="D60" t="str">
-        <v>41014</v>
+        <v>41079</v>
       </c>
       <c r="E60" t="str">
-        <v>990</v>
+        <v>790</v>
       </c>
       <c r="F60" t="str">
         <v>Por peso</v>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>741046</v>
+        <v>741080</v>
       </c>
       <c r="B61" t="str">
-        <v>AJI CACHO CABRA SECO KG</v>
+        <v>CEBOLLA CUGAT PP KG</v>
       </c>
       <c r="C61" t="str">
         <v/>
       </c>
       <c r="D61" t="str">
-        <v>41046</v>
+        <v>41080</v>
       </c>
       <c r="E61" t="str">
-        <v>13160</v>
+        <v>690</v>
       </c>
       <c r="F61" t="str">
         <v>Por peso</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>741079</v>
+        <v>741055</v>
       </c>
       <c r="B62" t="str">
-        <v>CEBOLLA BLANCA CRISTAL KG</v>
+        <v>BRUSELAS KG</v>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
       <c r="D62" t="str">
-        <v>41079</v>
+        <v>41055</v>
       </c>
       <c r="E62" t="str">
-        <v>790</v>
+        <v>2590</v>
       </c>
       <c r="F62" t="str">
         <v>Por peso</v>
@@ -1641,16 +1641,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>741080</v>
+        <v>741129</v>
       </c>
       <c r="B63" t="str">
-        <v>CEBOLLA CUGAT PP KG</v>
+        <v>PAPA SURENA KILO</v>
       </c>
       <c r="C63" t="str">
         <v/>
       </c>
       <c r="D63" t="str">
-        <v>41080</v>
+        <v>41129</v>
       </c>
       <c r="E63" t="str">
         <v>690</v>
@@ -1661,19 +1661,19 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>741055</v>
+        <v>741042</v>
       </c>
       <c r="B64" t="str">
-        <v>BRUSELAS KG</v>
+        <v>ZANAHORIA KG</v>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64" t="str">
-        <v>41055</v>
+        <v>41042</v>
       </c>
       <c r="E64" t="str">
-        <v>2590</v>
+        <v>690</v>
       </c>
       <c r="F64" t="str">
         <v>Por peso</v>
@@ -1681,19 +1681,19 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>741129</v>
+        <v>741420</v>
       </c>
       <c r="B65" t="str">
-        <v>PAPA SURENA KILO</v>
+        <v>PAPA CAMOTE KG</v>
       </c>
       <c r="C65" t="str">
         <v/>
       </c>
       <c r="D65" t="str">
-        <v>41129</v>
+        <v>41420</v>
       </c>
       <c r="E65" t="str">
-        <v>690</v>
+        <v>1990</v>
       </c>
       <c r="F65" t="str">
         <v>Por peso</v>
@@ -1701,19 +1701,19 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>741420</v>
+        <v>741030</v>
       </c>
       <c r="B66" t="str">
-        <v>PAPA CAMOTE KG</v>
+        <v>PAPA KG</v>
       </c>
       <c r="C66" t="str">
         <v/>
       </c>
       <c r="D66" t="str">
-        <v>41420</v>
+        <v>41030</v>
       </c>
       <c r="E66" t="str">
-        <v>1990</v>
+        <v>790</v>
       </c>
       <c r="F66" t="str">
         <v>Por peso</v>
@@ -1721,19 +1721,19 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>741030</v>
+        <v>741107</v>
       </c>
       <c r="B67" t="str">
-        <v>PAPA KG</v>
+        <v>CRANBERRY KG FFVV</v>
       </c>
       <c r="C67" t="str">
         <v/>
       </c>
       <c r="D67" t="str">
-        <v>41030</v>
+        <v>41107</v>
       </c>
       <c r="E67" t="str">
-        <v>790</v>
+        <v>12360</v>
       </c>
       <c r="F67" t="str">
         <v>Por peso</v>
@@ -1741,19 +1741,19 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>741107</v>
+        <v>741180</v>
       </c>
       <c r="B68" t="str">
-        <v>CRANBERRY KG FFVV</v>
+        <v>PAPA BLANCA KG</v>
       </c>
       <c r="C68" t="str">
         <v/>
       </c>
       <c r="D68" t="str">
-        <v>41107</v>
+        <v>41180</v>
       </c>
       <c r="E68" t="str">
-        <v>12360</v>
+        <v>1190</v>
       </c>
       <c r="F68" t="str">
         <v>Por peso</v>
@@ -1761,19 +1761,19 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>741180</v>
+        <v>741043</v>
       </c>
       <c r="B69" t="str">
-        <v>PAPA BLANCA KG</v>
+        <v>SESAMO BLANCO KILO FFVV</v>
       </c>
       <c r="C69" t="str">
         <v/>
       </c>
       <c r="D69" t="str">
-        <v>41180</v>
+        <v>41043</v>
       </c>
       <c r="E69" t="str">
-        <v>1190</v>
+        <v>9960</v>
       </c>
       <c r="F69" t="str">
         <v>Por peso</v>
@@ -1781,19 +1781,19 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>741043</v>
+        <v>742121</v>
       </c>
       <c r="B70" t="str">
-        <v>SESAMO BLANCO KILO FFVV</v>
+        <v>LIMON SUTIL KG</v>
       </c>
       <c r="C70" t="str">
         <v/>
       </c>
       <c r="D70" t="str">
-        <v>41043</v>
+        <v>42121</v>
       </c>
       <c r="E70" t="str">
-        <v>9960</v>
+        <v>2190</v>
       </c>
       <c r="F70" t="str">
         <v>Por peso</v>
@@ -1801,19 +1801,19 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>742121</v>
+        <v>742064</v>
       </c>
       <c r="B71" t="str">
-        <v>LIMON SUTIL KG</v>
+        <v>AJO CHILOTE KG</v>
       </c>
       <c r="C71" t="str">
         <v/>
       </c>
       <c r="D71" t="str">
-        <v>42121</v>
+        <v>42064</v>
       </c>
       <c r="E71" t="str">
-        <v>2190</v>
+        <v>10760</v>
       </c>
       <c r="F71" t="str">
         <v>Por peso</v>
@@ -1821,19 +1821,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>742064</v>
+        <v>741031</v>
       </c>
       <c r="B72" t="str">
-        <v>AJO CHILOTE KG</v>
+        <v>AJI VERDE KG</v>
       </c>
       <c r="C72" t="str">
         <v/>
       </c>
       <c r="D72" t="str">
-        <v>42064</v>
+        <v>41031</v>
       </c>
       <c r="E72" t="str">
-        <v>10760</v>
+        <v>5960</v>
       </c>
       <c r="F72" t="str">
         <v>Por peso</v>
@@ -1841,19 +1841,19 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>741031</v>
+        <v>742097</v>
       </c>
       <c r="B73" t="str">
-        <v>AJI VERDE KG</v>
+        <v>LIMON TAHITI KG</v>
       </c>
       <c r="C73" t="str">
         <v/>
       </c>
       <c r="D73" t="str">
-        <v>41031</v>
+        <v>42097</v>
       </c>
       <c r="E73" t="str">
-        <v>5960</v>
+        <v>1490</v>
       </c>
       <c r="F73" t="str">
         <v>Por peso</v>
@@ -1861,19 +1861,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>742097</v>
+        <v>741211</v>
       </c>
       <c r="B74" t="str">
-        <v>LIMON TAHITI KG</v>
+        <v>UVA RED GLOBE KG</v>
       </c>
       <c r="C74" t="str">
         <v/>
       </c>
       <c r="D74" t="str">
-        <v>42097</v>
+        <v>41211</v>
       </c>
       <c r="E74" t="str">
-        <v>1490</v>
+        <v>1190</v>
       </c>
       <c r="F74" t="str">
         <v>Por peso</v>
@@ -1881,19 +1881,19 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>741211</v>
+        <v>741111</v>
       </c>
       <c r="B75" t="str">
-        <v>UVA RED GLOBE KG</v>
+        <v>CANELA EN POLVO KG FFVV</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75" t="str">
-        <v>41211</v>
+        <v>41111</v>
       </c>
       <c r="E75" t="str">
-        <v>1190</v>
+        <v>19160</v>
       </c>
       <c r="F75" t="str">
         <v>Por peso</v>
@@ -1901,19 +1901,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>741111</v>
+        <v>741052</v>
       </c>
       <c r="B76" t="str">
-        <v>CANELA EN POLVO KG FFVV</v>
+        <v>ZAPALLO BUTTERNUT KG</v>
       </c>
       <c r="C76" t="str">
         <v/>
       </c>
       <c r="D76" t="str">
-        <v>41111</v>
+        <v>41052</v>
       </c>
       <c r="E76" t="str">
-        <v>19160</v>
+        <v>690</v>
       </c>
       <c r="F76" t="str">
         <v>Por peso</v>
@@ -1921,19 +1921,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>741052</v>
+        <v>742090</v>
       </c>
       <c r="B77" t="str">
-        <v>ZAPALLO BUTTERNUT KG</v>
+        <v>NARANJA KG</v>
       </c>
       <c r="C77" t="str">
         <v/>
       </c>
       <c r="D77" t="str">
-        <v>41052</v>
+        <v>42090</v>
       </c>
       <c r="E77" t="str">
-        <v>690</v>
+        <v>1290</v>
       </c>
       <c r="F77" t="str">
         <v>Por peso</v>
@@ -1941,19 +1941,19 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>742090</v>
+        <v>742095</v>
       </c>
       <c r="B78" t="str">
-        <v>NARANJA KG</v>
+        <v>MARAVILLA PELADA KG FFVV</v>
       </c>
       <c r="C78" t="str">
         <v/>
       </c>
       <c r="D78" t="str">
-        <v>42090</v>
+        <v>42095</v>
       </c>
       <c r="E78" t="str">
-        <v>1290</v>
+        <v>5160</v>
       </c>
       <c r="F78" t="str">
         <v>Por peso</v>
@@ -1961,19 +1961,19 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>742095</v>
+        <v>744501</v>
       </c>
       <c r="B79" t="str">
-        <v>MARAVILLA PELADA KG FFVV</v>
+        <v>AJO EN POLVO KG FFYVV</v>
       </c>
       <c r="C79" t="str">
         <v/>
       </c>
       <c r="D79" t="str">
-        <v>42095</v>
+        <v>44501</v>
       </c>
       <c r="E79" t="str">
-        <v>5160</v>
+        <v>8760</v>
       </c>
       <c r="F79" t="str">
         <v>Por peso</v>
@@ -1981,19 +1981,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>744501</v>
+        <v>744502</v>
       </c>
       <c r="B80" t="str">
-        <v>AJO EN POLVO KG FFYVV</v>
+        <v>ALINO COMPLETO KG FFYVV</v>
       </c>
       <c r="C80" t="str">
         <v/>
       </c>
       <c r="D80" t="str">
-        <v>44501</v>
+        <v>44502</v>
       </c>
       <c r="E80" t="str">
-        <v>8760</v>
+        <v>8360</v>
       </c>
       <c r="F80" t="str">
         <v>Por peso</v>
@@ -2001,19 +2001,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>744502</v>
+        <v>744503</v>
       </c>
       <c r="B81" t="str">
-        <v>ALINO COMPLETO KG FFYVV</v>
+        <v>BICARBONATO KG FFVV</v>
       </c>
       <c r="C81" t="str">
         <v/>
       </c>
       <c r="D81" t="str">
-        <v>44502</v>
+        <v>44503</v>
       </c>
       <c r="E81" t="str">
-        <v>8360</v>
+        <v>2360</v>
       </c>
       <c r="F81" t="str">
         <v>Por peso</v>
@@ -2021,19 +2021,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>744503</v>
+        <v>744504</v>
       </c>
       <c r="B82" t="str">
-        <v>BICARBONATO KG FFVV</v>
+        <v>COMINO MOLIDO KG FFVV</v>
       </c>
       <c r="C82" t="str">
         <v/>
       </c>
       <c r="D82" t="str">
-        <v>44503</v>
+        <v>44504</v>
       </c>
       <c r="E82" t="str">
-        <v>2360</v>
+        <v>21160</v>
       </c>
       <c r="F82" t="str">
         <v>Por peso</v>
@@ -2041,19 +2041,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>744504</v>
+        <v>744505</v>
       </c>
       <c r="B83" t="str">
-        <v>COMINO MOLIDO KG FFVV</v>
+        <v>MAIZ CURAGUA KG FFVV</v>
       </c>
       <c r="C83" t="str">
         <v/>
       </c>
       <c r="D83" t="str">
-        <v>44504</v>
+        <v>44505</v>
       </c>
       <c r="E83" t="str">
-        <v>21160</v>
+        <v>3160</v>
       </c>
       <c r="F83" t="str">
         <v>Por peso</v>
@@ -2061,19 +2061,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>744505</v>
+        <v>744589</v>
       </c>
       <c r="B84" t="str">
-        <v>MAIZ CURAGUA KG FFVV</v>
+        <v>PALTA HASS KG</v>
       </c>
       <c r="C84" t="str">
         <v/>
       </c>
       <c r="D84" t="str">
-        <v>44505</v>
+        <v>44589</v>
       </c>
       <c r="E84" t="str">
-        <v>3160</v>
+        <v>5690</v>
       </c>
       <c r="F84" t="str">
         <v>Por peso</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>744589</v>
+        <v>742038</v>
       </c>
       <c r="B85" t="str">
-        <v>PALTA HASS KG</v>
+        <v>UVA VERDE KG</v>
       </c>
       <c r="C85" t="str">
         <v/>
       </c>
       <c r="D85" t="str">
-        <v>44589</v>
+        <v>42038</v>
       </c>
       <c r="E85" t="str">
-        <v>5690</v>
+        <v>1590</v>
       </c>
       <c r="F85" t="str">
         <v>Por peso</v>
@@ -2101,19 +2101,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>742038</v>
+        <v>749205</v>
       </c>
       <c r="B86" t="str">
-        <v>UVA VERDE KG</v>
+        <v>VASO MELON TROZOS FFVV</v>
       </c>
       <c r="C86" t="str">
         <v/>
       </c>
       <c r="D86" t="str">
-        <v>42038</v>
+        <v>29205</v>
       </c>
       <c r="E86" t="str">
-        <v>1590</v>
+        <v>790</v>
       </c>
       <c r="F86" t="str">
         <v>Por peso</v>
@@ -2121,19 +2121,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>749205</v>
+        <v>741112</v>
       </c>
       <c r="B87" t="str">
-        <v>VASO MELON TROZOS FFVV</v>
+        <v>COMINO ENTERO KG FFVV</v>
       </c>
       <c r="C87" t="str">
         <v/>
       </c>
       <c r="D87" t="str">
-        <v>29205</v>
+        <v>41112</v>
       </c>
       <c r="E87" t="str">
-        <v>790</v>
+        <v>19160</v>
       </c>
       <c r="F87" t="str">
         <v>Por peso</v>
@@ -2141,19 +2141,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>741112</v>
+        <v>744509</v>
       </c>
       <c r="B88" t="str">
-        <v>COMINO ENTERO KG FFVV</v>
+        <v>PIMIENTA NEGRA MOLIDA KG FFVV</v>
       </c>
       <c r="C88" t="str">
         <v/>
       </c>
       <c r="D88" t="str">
-        <v>41112</v>
+        <v>44509</v>
       </c>
       <c r="E88" t="str">
-        <v>19160</v>
+        <v>27160</v>
       </c>
       <c r="F88" t="str">
         <v>Por peso</v>
@@ -2161,19 +2161,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>744509</v>
+        <v>744510</v>
       </c>
       <c r="B89" t="str">
-        <v>PIMIENTA NEGRA MOLIDA KG FFVV</v>
+        <v>LINAZA MOLIDA KG FFVV</v>
       </c>
       <c r="C89" t="str">
         <v/>
       </c>
       <c r="D89" t="str">
-        <v>44509</v>
+        <v>44510</v>
       </c>
       <c r="E89" t="str">
-        <v>27160</v>
+        <v>5960</v>
       </c>
       <c r="F89" t="str">
         <v>Por peso</v>
@@ -2181,19 +2181,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>744510</v>
+        <v>744511</v>
       </c>
       <c r="B90" t="str">
-        <v>LINAZA MOLIDA KG FFVV</v>
+        <v>LINAZA ENTERA KG FFVV</v>
       </c>
       <c r="C90" t="str">
         <v/>
       </c>
       <c r="D90" t="str">
-        <v>44510</v>
+        <v>44511</v>
       </c>
       <c r="E90" t="str">
-        <v>5960</v>
+        <v>5160</v>
       </c>
       <c r="F90" t="str">
         <v>Por peso</v>
@@ -2201,19 +2201,19 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>744511</v>
+        <v>741401</v>
       </c>
       <c r="B91" t="str">
-        <v>LINAZA ENTERA KG FFVV</v>
+        <v>AJI CACHO CABRA AHUMADO KG</v>
       </c>
       <c r="C91" t="str">
         <v/>
       </c>
       <c r="D91" t="str">
-        <v>44511</v>
+        <v>41401</v>
       </c>
       <c r="E91" t="str">
-        <v>5160</v>
+        <v>13160</v>
       </c>
       <c r="F91" t="str">
         <v>Por peso</v>
@@ -2221,19 +2221,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>741401</v>
+        <v>741011</v>
       </c>
       <c r="B92" t="str">
-        <v>AJI CACHO CABRA AHUMADO KG</v>
+        <v>CURCUMA KG</v>
       </c>
       <c r="C92" t="str">
         <v/>
       </c>
       <c r="D92" t="str">
-        <v>41401</v>
+        <v>41011</v>
       </c>
       <c r="E92" t="str">
-        <v>13160</v>
+        <v>2990</v>
       </c>
       <c r="F92" t="str">
         <v>Por peso</v>
@@ -2241,19 +2241,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>741011</v>
+        <v>744140</v>
       </c>
       <c r="B93" t="str">
-        <v>CURCUMA KG</v>
+        <v>CLAVO DE OLOR MOLIDO KG FFVV</v>
       </c>
       <c r="C93" t="str">
         <v/>
       </c>
       <c r="D93" t="str">
-        <v>41011</v>
+        <v>44140</v>
       </c>
       <c r="E93" t="str">
-        <v>2990</v>
+        <v>18760</v>
       </c>
       <c r="F93" t="str">
         <v>Por peso</v>
@@ -2261,19 +2261,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>744140</v>
+        <v>741083</v>
       </c>
       <c r="B94" t="str">
-        <v>CLAVO DE OLOR MOLIDO KG FFVV</v>
+        <v>SEMILLA DE ZAPALLO KG FFVV</v>
       </c>
       <c r="C94" t="str">
         <v/>
       </c>
       <c r="D94" t="str">
-        <v>44140</v>
+        <v>41083</v>
       </c>
       <c r="E94" t="str">
-        <v>18760</v>
+        <v>14760</v>
       </c>
       <c r="F94" t="str">
         <v>Por peso</v>
@@ -2281,19 +2281,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>741083</v>
+        <v>742511</v>
       </c>
       <c r="B95" t="str">
-        <v>SEMILLA DE ZAPALLO KG FFVV</v>
+        <v>KIWI LIQUIDACION</v>
       </c>
       <c r="C95" t="str">
         <v/>
       </c>
       <c r="D95" t="str">
-        <v>41083</v>
+        <v>42511</v>
       </c>
       <c r="E95" t="str">
-        <v>14760</v>
+        <v>9990</v>
       </c>
       <c r="F95" t="str">
         <v>Por peso</v>
@@ -2301,19 +2301,19 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>742511</v>
+        <v>741519</v>
       </c>
       <c r="B96" t="str">
-        <v>KIWI LIQUIDACION</v>
+        <v>PLATANO BARRAGANETE VERDE KG</v>
       </c>
       <c r="C96" t="str">
         <v/>
       </c>
       <c r="D96" t="str">
-        <v>42511</v>
+        <v>41519</v>
       </c>
       <c r="E96" t="str">
-        <v>9990</v>
+        <v>1990</v>
       </c>
       <c r="F96" t="str">
         <v>Por peso</v>
@@ -2321,19 +2321,19 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>741519</v>
+        <v>744521</v>
       </c>
       <c r="B97" t="str">
-        <v>PLATANO BARRAGANETE VERDE KG</v>
+        <v>CACAO AZUCARADO KG FFYVV</v>
       </c>
       <c r="C97" t="str">
         <v/>
       </c>
       <c r="D97" t="str">
-        <v>41519</v>
+        <v>44521</v>
       </c>
       <c r="E97" t="str">
-        <v>1990</v>
+        <v>12360</v>
       </c>
       <c r="F97" t="str">
         <v>Por peso</v>
@@ -2341,19 +2341,19 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>744521</v>
+        <v>744522</v>
       </c>
       <c r="B98" t="str">
-        <v>CACAO AZUCARADO KG FFYVV</v>
+        <v>PROTEINA VEGETAL KG FFVV</v>
       </c>
       <c r="C98" t="str">
         <v/>
       </c>
       <c r="D98" t="str">
-        <v>44521</v>
+        <v>44522</v>
       </c>
       <c r="E98" t="str">
-        <v>12360</v>
+        <v>4760</v>
       </c>
       <c r="F98" t="str">
         <v>Por peso</v>
@@ -2361,19 +2361,19 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>744522</v>
+        <v>744523</v>
       </c>
       <c r="B99" t="str">
-        <v>PROTEINA VEGETAL KG FFVV</v>
+        <v>CHUNO KG FFVV</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
       <c r="D99" t="str">
-        <v>44522</v>
+        <v>44523</v>
       </c>
       <c r="E99" t="str">
-        <v>4760</v>
+        <v>5160</v>
       </c>
       <c r="F99" t="str">
         <v>Por peso</v>
@@ -2381,19 +2381,19 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>744523</v>
+        <v>744524</v>
       </c>
       <c r="B100" t="str">
-        <v>CHUNO KG FFVV</v>
+        <v>TE CEYLAN HOJA KG FFVV</v>
       </c>
       <c r="C100" t="str">
         <v/>
       </c>
       <c r="D100" t="str">
-        <v>44523</v>
+        <v>44524</v>
       </c>
       <c r="E100" t="str">
-        <v>5160</v>
+        <v>17160</v>
       </c>
       <c r="F100" t="str">
         <v>Por peso</v>
@@ -2401,19 +2401,19 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>744524</v>
+        <v>744525</v>
       </c>
       <c r="B101" t="str">
-        <v>TE CEYLAN HOJA KG FFVV</v>
+        <v>COCO RALLADO KG FFVV</v>
       </c>
       <c r="C101" t="str">
         <v/>
       </c>
       <c r="D101" t="str">
-        <v>44524</v>
+        <v>44525</v>
       </c>
       <c r="E101" t="str">
-        <v>17160</v>
+        <v>14760</v>
       </c>
       <c r="F101" t="str">
         <v>Por peso</v>
@@ -2421,19 +2421,19 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>744525</v>
+        <v>744526</v>
       </c>
       <c r="B102" t="str">
-        <v>COCO RALLADO KG FFVV</v>
+        <v>CANELA ENTERA KG FFVV</v>
       </c>
       <c r="C102" t="str">
         <v/>
       </c>
       <c r="D102" t="str">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="E102" t="str">
-        <v>14760</v>
+        <v>55160</v>
       </c>
       <c r="F102" t="str">
         <v>Por peso</v>
@@ -2441,19 +2441,19 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>744526</v>
+        <v>744527</v>
       </c>
       <c r="B103" t="str">
-        <v>CANELA ENTERA KG FFVV</v>
+        <v>TE VERDE KG FFVV</v>
       </c>
       <c r="C103" t="str">
         <v/>
       </c>
       <c r="D103" t="str">
-        <v>44526</v>
+        <v>44527</v>
       </c>
       <c r="E103" t="str">
-        <v>55160</v>
+        <v>13960</v>
       </c>
       <c r="F103" t="str">
         <v>Por peso</v>
@@ -2461,19 +2461,19 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>744527</v>
+        <v>744528</v>
       </c>
       <c r="B104" t="str">
-        <v>TE VERDE KG FFVV</v>
+        <v>MAICENA KG FFVV</v>
       </c>
       <c r="C104" t="str">
         <v/>
       </c>
       <c r="D104" t="str">
-        <v>44527</v>
+        <v>44528</v>
       </c>
       <c r="E104" t="str">
-        <v>13960</v>
+        <v>3160</v>
       </c>
       <c r="F104" t="str">
         <v>Por peso</v>
@@ -2481,19 +2481,19 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>744528</v>
+        <v>742603</v>
       </c>
       <c r="B105" t="str">
-        <v>MAICENA KG FFVV</v>
+        <v>TOMATE LIQUIDACION</v>
       </c>
       <c r="C105" t="str">
         <v/>
       </c>
       <c r="D105" t="str">
-        <v>44528</v>
+        <v>42603</v>
       </c>
       <c r="E105" t="str">
-        <v>3160</v>
+        <v>9990</v>
       </c>
       <c r="F105" t="str">
         <v>Por peso</v>
@@ -2501,19 +2501,19 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>742603</v>
+        <v>742605</v>
       </c>
       <c r="B106" t="str">
-        <v>TOMATE LIQUIDACION</v>
+        <v>PALTA LIQUIDACION</v>
       </c>
       <c r="C106" t="str">
         <v/>
       </c>
       <c r="D106" t="str">
-        <v>42603</v>
+        <v>42605</v>
       </c>
       <c r="E106" t="str">
-        <v>9990</v>
+        <v>4490</v>
       </c>
       <c r="F106" t="str">
         <v>Por peso</v>
@@ -2521,19 +2521,19 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>742605</v>
+        <v>742606</v>
       </c>
       <c r="B107" t="str">
-        <v>PALTA LIQUIDACION</v>
+        <v>PLATANO LIQUIDACION</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107" t="str">
-        <v>42605</v>
+        <v>42606</v>
       </c>
       <c r="E107" t="str">
-        <v>4490</v>
+        <v>9990</v>
       </c>
       <c r="F107" t="str">
         <v>Por peso</v>
@@ -2541,16 +2541,16 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>742606</v>
+        <v>741607</v>
       </c>
       <c r="B108" t="str">
-        <v>PLATANO LIQUIDACION</v>
+        <v>ZANAHORIA LIQUIDACION</v>
       </c>
       <c r="C108" t="str">
         <v/>
       </c>
       <c r="D108" t="str">
-        <v>42606</v>
+        <v>41607</v>
       </c>
       <c r="E108" t="str">
         <v>9990</v>
@@ -2561,16 +2561,16 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>741607</v>
+        <v>742402</v>
       </c>
       <c r="B109" t="str">
-        <v>ZANAHORIA LIQUIDACION</v>
+        <v>CIRUELA LIQUIDACION</v>
       </c>
       <c r="C109" t="str">
         <v/>
       </c>
       <c r="D109" t="str">
-        <v>41607</v>
+        <v>42402</v>
       </c>
       <c r="E109" t="str">
         <v>9990</v>
@@ -2581,16 +2581,16 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>742402</v>
+        <v>742120</v>
       </c>
       <c r="B110" t="str">
-        <v>CIRUELA LIQUIDACION</v>
+        <v>PERA LIQUIDACION</v>
       </c>
       <c r="C110" t="str">
         <v/>
       </c>
       <c r="D110" t="str">
-        <v>42402</v>
+        <v>42120</v>
       </c>
       <c r="E110" t="str">
         <v>9990</v>
@@ -2601,19 +2601,19 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>742120</v>
+        <v>742126</v>
       </c>
       <c r="B111" t="str">
-        <v>PERA LIQUIDACION</v>
+        <v>DURAZNO LIQUIDACION KG</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111" t="str">
-        <v>42120</v>
+        <v>42126</v>
       </c>
       <c r="E111" t="str">
-        <v>9990</v>
+        <v>1990</v>
       </c>
       <c r="F111" t="str">
         <v>Por peso</v>
@@ -2621,19 +2621,19 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>742126</v>
+        <v>742127</v>
       </c>
       <c r="B112" t="str">
-        <v>DURAZNO LIQUIDACION KG</v>
+        <v>LIMON LIQUIDACION</v>
       </c>
       <c r="C112" t="str">
         <v/>
       </c>
       <c r="D112" t="str">
-        <v>42126</v>
+        <v>42127</v>
       </c>
       <c r="E112" t="str">
-        <v>1990</v>
+        <v>9990</v>
       </c>
       <c r="F112" t="str">
         <v>Por peso</v>
@@ -2641,16 +2641,16 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>742127</v>
+        <v>742128</v>
       </c>
       <c r="B113" t="str">
-        <v>LIMON LIQUIDACION</v>
+        <v>POROTO VERDE LIQUIDACION KG</v>
       </c>
       <c r="C113" t="str">
         <v/>
       </c>
       <c r="D113" t="str">
-        <v>42127</v>
+        <v>42128</v>
       </c>
       <c r="E113" t="str">
         <v>9990</v>
@@ -2661,16 +2661,16 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>742128</v>
+        <v>742129</v>
       </c>
       <c r="B114" t="str">
-        <v>POROTO VERDE LIQUIDACION KG</v>
+        <v>POROTO GRANADO LIQUIDACION</v>
       </c>
       <c r="C114" t="str">
         <v/>
       </c>
       <c r="D114" t="str">
-        <v>42128</v>
+        <v>42129</v>
       </c>
       <c r="E114" t="str">
         <v>9990</v>
@@ -2681,16 +2681,16 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>742129</v>
+        <v>742130</v>
       </c>
       <c r="B115" t="str">
-        <v>POROTO GRANADO LIQUIDACION</v>
+        <v>MANZANA LIQUIDACION</v>
       </c>
       <c r="C115" t="str">
         <v/>
       </c>
       <c r="D115" t="str">
-        <v>42129</v>
+        <v>42130</v>
       </c>
       <c r="E115" t="str">
         <v>9990</v>
@@ -2701,16 +2701,16 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>742130</v>
+        <v>741250</v>
       </c>
       <c r="B116" t="str">
-        <v>MANZANA LIQUIDACION</v>
+        <v>UVA LIQUIDACION</v>
       </c>
       <c r="C116" t="str">
         <v/>
       </c>
       <c r="D116" t="str">
-        <v>42130</v>
+        <v>41250</v>
       </c>
       <c r="E116" t="str">
         <v>9990</v>
@@ -2721,16 +2721,16 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>741250</v>
+        <v>742421</v>
       </c>
       <c r="B117" t="str">
-        <v>UVA LIQUIDACION</v>
+        <v>NARANJA LIQUIDACION</v>
       </c>
       <c r="C117" t="str">
         <v/>
       </c>
       <c r="D117" t="str">
-        <v>41250</v>
+        <v>42421</v>
       </c>
       <c r="E117" t="str">
         <v>9990</v>
@@ -2741,19 +2741,19 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>742421</v>
+        <v>745000</v>
       </c>
       <c r="B118" t="str">
-        <v>NARANJA LIQUIDACION</v>
+        <v>AJO LIQUIDACION</v>
       </c>
       <c r="C118" t="str">
         <v/>
       </c>
       <c r="D118" t="str">
-        <v>42421</v>
+        <v>45000</v>
       </c>
       <c r="E118" t="str">
-        <v>9990</v>
+        <v>9999</v>
       </c>
       <c r="F118" t="str">
         <v>Por peso</v>
@@ -2761,19 +2761,19 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>745000</v>
+        <v>742300</v>
       </c>
       <c r="B119" t="str">
-        <v>AJO LIQUIDACION</v>
+        <v>PALTA NEGRA LA CRUZ KG</v>
       </c>
       <c r="C119" t="str">
         <v/>
       </c>
       <c r="D119" t="str">
-        <v>45000</v>
+        <v>42300</v>
       </c>
       <c r="E119" t="str">
-        <v>9999</v>
+        <v>3890</v>
       </c>
       <c r="F119" t="str">
         <v>Por peso</v>
@@ -2781,19 +2781,19 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>742300</v>
+        <v>740303</v>
       </c>
       <c r="B120" t="str">
-        <v>PALTA NEGRA LA CRUZ KG</v>
+        <v>PAPA LIQUIDACION</v>
       </c>
       <c r="C120" t="str">
         <v/>
       </c>
       <c r="D120" t="str">
-        <v>42300</v>
+        <v>40303</v>
       </c>
       <c r="E120" t="str">
-        <v>3890</v>
+        <v>9990</v>
       </c>
       <c r="F120" t="str">
         <v>Por peso</v>
@@ -2801,19 +2801,19 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>740303</v>
+        <v>742549</v>
       </c>
       <c r="B121" t="str">
-        <v>PAPA LIQUIDACION</v>
+        <v>NECTARIN LIQUIDACION</v>
       </c>
       <c r="C121" t="str">
         <v/>
       </c>
       <c r="D121" t="str">
-        <v>40303</v>
+        <v>42549</v>
       </c>
       <c r="E121" t="str">
-        <v>9990</v>
+        <v>2290</v>
       </c>
       <c r="F121" t="str">
         <v>Por peso</v>
@@ -2821,19 +2821,19 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>742549</v>
+        <v>748913</v>
       </c>
       <c r="B122" t="str">
-        <v>NECTARIN LIQUIDACION</v>
+        <v>JENGIBRE EN POLVO FFVV</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
       <c r="D122" t="str">
-        <v>42549</v>
+        <v>48913</v>
       </c>
       <c r="E122" t="str">
-        <v>2290</v>
+        <v>14760</v>
       </c>
       <c r="F122" t="str">
         <v>Por peso</v>
@@ -2841,19 +2841,19 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>748913</v>
+        <v>741110</v>
       </c>
       <c r="B123" t="str">
-        <v>JENGIBRE EN POLVO FFVV</v>
+        <v>AJI COLOR KILO FFYVV</v>
       </c>
       <c r="C123" t="str">
         <v/>
       </c>
       <c r="D123" t="str">
-        <v>48913</v>
+        <v>41110</v>
       </c>
       <c r="E123" t="str">
-        <v>14760</v>
+        <v>7160</v>
       </c>
       <c r="F123" t="str">
         <v>Por peso</v>
@@ -2861,19 +2861,19 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>741110</v>
+        <v>742333</v>
       </c>
       <c r="B124" t="str">
-        <v>AJI COLOR KILO FFYVV</v>
+        <v>MANZANA BICOLOR KG</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124" t="str">
-        <v>41110</v>
+        <v>42333</v>
       </c>
       <c r="E124" t="str">
-        <v>7160</v>
+        <v>990</v>
       </c>
       <c r="F124" t="str">
         <v>Por peso</v>
@@ -2881,19 +2881,19 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>742333</v>
+        <v>742999</v>
       </c>
       <c r="B125" t="str">
-        <v>MANZANA BICOLOR KG</v>
+        <v>CIRUELA SECA KG FFVV</v>
       </c>
       <c r="C125" t="str">
         <v/>
       </c>
       <c r="D125" t="str">
-        <v>42333</v>
+        <v>42999</v>
       </c>
       <c r="E125" t="str">
-        <v>990</v>
+        <v>6760</v>
       </c>
       <c r="F125" t="str">
         <v>Por peso</v>
@@ -2901,19 +2901,19 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>742999</v>
+        <v>741222</v>
       </c>
       <c r="B126" t="str">
-        <v>CIRUELA SECA KG FFVV</v>
+        <v>OREGANO KG FFVV</v>
       </c>
       <c r="C126" t="str">
         <v/>
       </c>
       <c r="D126" t="str">
-        <v>42999</v>
+        <v>41222</v>
       </c>
       <c r="E126" t="str">
-        <v>6760</v>
+        <v>10360</v>
       </c>
       <c r="F126" t="str">
         <v>Por peso</v>
@@ -2921,19 +2921,19 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>741222</v>
+        <v>741076</v>
       </c>
       <c r="B127" t="str">
-        <v>OREGANO KG FFVV</v>
+        <v>AJO KG</v>
       </c>
       <c r="C127" t="str">
         <v/>
       </c>
       <c r="D127" t="str">
-        <v>41222</v>
+        <v>41076</v>
       </c>
       <c r="E127" t="str">
-        <v>10360</v>
+        <v>4760</v>
       </c>
       <c r="F127" t="str">
         <v>Por peso</v>
@@ -2953,7 +2953,7 @@
         <v>41076</v>
       </c>
       <c r="E128" t="str">
-        <v>4760</v>
+        <v>2996</v>
       </c>
       <c r="F128" t="str">
         <v>Por peso</v>
@@ -2961,19 +2961,19 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>741076</v>
+        <v>741041</v>
       </c>
       <c r="B129" t="str">
-        <v>AJO KG</v>
+        <v>PAPA ZONA SUR KG</v>
       </c>
       <c r="C129" t="str">
         <v/>
       </c>
       <c r="D129" t="str">
-        <v>41076</v>
+        <v>41041</v>
       </c>
       <c r="E129" t="str">
-        <v>2996</v>
+        <v>990</v>
       </c>
       <c r="F129" t="str">
         <v>Por peso</v>
@@ -2981,19 +2981,19 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>741041</v>
+        <v>744018</v>
       </c>
       <c r="B130" t="str">
-        <v>PAPA ZONA SUR KG</v>
+        <v>MIX FRUTOS SECOS KG FFVV</v>
       </c>
       <c r="C130" t="str">
         <v/>
       </c>
       <c r="D130" t="str">
-        <v>41041</v>
+        <v>44018</v>
       </c>
       <c r="E130" t="str">
-        <v>990</v>
+        <v>6760</v>
       </c>
       <c r="F130" t="str">
         <v>Por peso</v>
@@ -3001,19 +3001,19 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>744018</v>
+        <v>748081</v>
       </c>
       <c r="B131" t="str">
-        <v>MIX FRUTOS SECOS KG FFVV</v>
+        <v>MANCAQUI KG</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
       <c r="D131" t="str">
-        <v>44018</v>
+        <v>48081</v>
       </c>
       <c r="E131" t="str">
-        <v>6760</v>
+        <v>1390</v>
       </c>
       <c r="F131" t="str">
         <v>Por peso</v>

--- a/MaestraPLU_FFVV.xlsx
+++ b/MaestraPLU_FFVV.xlsx
@@ -1153,7 +1153,7 @@
         <v>42041</v>
       </c>
       <c r="E38" t="str">
-        <v>1690</v>
+        <v>1490</v>
       </c>
       <c r="F38" t="str">
         <v>Por peso</v>
@@ -2773,7 +2773,7 @@
         <v>42300</v>
       </c>
       <c r="E119" t="str">
-        <v>3890</v>
+        <v>3590</v>
       </c>
       <c r="F119" t="str">
         <v>Por peso</v>

--- a/MaestraPLU_FFVV.xlsx
+++ b/MaestraPLU_FFVV.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F137"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -761,19 +761,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>742036</v>
+        <v>742022</v>
       </c>
       <c r="B19" t="str">
-        <v>PAPAYA KG</v>
+        <v>NUECES KG FFVV</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>42036</v>
+        <v>42022</v>
       </c>
       <c r="E19" t="str">
-        <v>2990</v>
+        <v>14760</v>
       </c>
       <c r="F19" t="str">
         <v>Por peso</v>
@@ -781,19 +781,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>742022</v>
+        <v>742044</v>
       </c>
       <c r="B20" t="str">
-        <v>NUECES KG FFVV</v>
+        <v>MEMBRILLO KG</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>42022</v>
+        <v>42044</v>
       </c>
       <c r="E20" t="str">
-        <v>14760</v>
+        <v>990</v>
       </c>
       <c r="F20" t="str">
         <v>Por peso</v>
@@ -801,19 +801,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>742018</v>
+        <v>742015</v>
       </c>
       <c r="B21" t="str">
-        <v>NECTARIN AMARILLO KG</v>
+        <v>MANZANA VERDE KG</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>42018</v>
+        <v>42015</v>
       </c>
       <c r="E21" t="str">
-        <v>1290</v>
+        <v>990</v>
       </c>
       <c r="F21" t="str">
         <v>Por peso</v>
@@ -821,16 +821,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>742044</v>
+        <v>742013</v>
       </c>
       <c r="B22" t="str">
-        <v>MEMBRILLO KG</v>
+        <v>MANZANA ROJA KG</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>42044</v>
+        <v>42013</v>
       </c>
       <c r="E22" t="str">
         <v>990</v>
@@ -841,16 +841,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>742015</v>
+        <v>742066</v>
       </c>
       <c r="B23" t="str">
-        <v>MANZANA VERDE KG</v>
+        <v>MANZANA ROYAL GALA KG</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>42015</v>
+        <v>42066</v>
       </c>
       <c r="E23" t="str">
         <v>990</v>
@@ -861,16 +861,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>742013</v>
+        <v>742067</v>
       </c>
       <c r="B24" t="str">
-        <v>MANZANA ROJA KG</v>
+        <v>MANZANA FUJI KG</v>
       </c>
       <c r="C24" t="str">
         <v/>
       </c>
       <c r="D24" t="str">
-        <v>42013</v>
+        <v>42067</v>
       </c>
       <c r="E24" t="str">
         <v>990</v>
@@ -881,19 +881,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>742066</v>
+        <v>742102</v>
       </c>
       <c r="B25" t="str">
-        <v>MANZANA ROYAL GALA KG</v>
+        <v>MANGOS KG</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>42066</v>
+        <v>42102</v>
       </c>
       <c r="E25" t="str">
-        <v>990</v>
+        <v>2890</v>
       </c>
       <c r="F25" t="str">
         <v>Por peso</v>
@@ -901,19 +901,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>742067</v>
+        <v>742011</v>
       </c>
       <c r="B26" t="str">
-        <v>MANZANA FUJI KG</v>
+        <v>LIMON KG</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
       <c r="D26" t="str">
-        <v>42067</v>
+        <v>42011</v>
       </c>
       <c r="E26" t="str">
-        <v>990</v>
+        <v>1290</v>
       </c>
       <c r="F26" t="str">
         <v>Por peso</v>
@@ -921,19 +921,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>742102</v>
+        <v>742010</v>
       </c>
       <c r="B27" t="str">
-        <v>MANGOS KG</v>
+        <v>KIWI KG</v>
       </c>
       <c r="C27" t="str">
         <v/>
       </c>
       <c r="D27" t="str">
-        <v>42102</v>
+        <v>42010</v>
       </c>
       <c r="E27" t="str">
-        <v>2890</v>
+        <v>1190</v>
       </c>
       <c r="F27" t="str">
         <v>Por peso</v>
@@ -941,19 +941,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>742011</v>
+        <v>742051</v>
       </c>
       <c r="B28" t="str">
-        <v>LIMON KG</v>
+        <v>GRANADAS KG</v>
       </c>
       <c r="C28" t="str">
         <v/>
       </c>
       <c r="D28" t="str">
-        <v>42011</v>
+        <v>42051</v>
       </c>
       <c r="E28" t="str">
-        <v>1290</v>
+        <v>1990</v>
       </c>
       <c r="F28" t="str">
         <v>Por peso</v>
@@ -961,19 +961,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>742010</v>
+        <v>742033</v>
       </c>
       <c r="B29" t="str">
-        <v>KIWI KG</v>
+        <v>CIRUELA KG</v>
       </c>
       <c r="C29" t="str">
         <v/>
       </c>
       <c r="D29" t="str">
-        <v>42010</v>
+        <v>42033</v>
       </c>
       <c r="E29" t="str">
-        <v>1190</v>
+        <v>690</v>
       </c>
       <c r="F29" t="str">
         <v>Por peso</v>
@@ -981,19 +981,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>742051</v>
+        <v>742042</v>
       </c>
       <c r="B30" t="str">
-        <v>GRANADAS KG</v>
+        <v>UVA NEGRA KG</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30" t="str">
-        <v>42051</v>
+        <v>42042</v>
       </c>
       <c r="E30" t="str">
-        <v>1990</v>
+        <v>1190</v>
       </c>
       <c r="F30" t="str">
         <v>Por peso</v>
@@ -1001,19 +1001,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>742012</v>
+        <v>742041</v>
       </c>
       <c r="B31" t="str">
-        <v>NECTARIN PLATANO KG</v>
+        <v>TOMATE LARGA VIDA KG</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>42012</v>
+        <v>42041</v>
       </c>
       <c r="E31" t="str">
-        <v>990</v>
+        <v>1490</v>
       </c>
       <c r="F31" t="str">
         <v>Por peso</v>
@@ -1021,19 +1021,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>742014</v>
+        <v>742166</v>
       </c>
       <c r="B32" t="str">
-        <v>DURAZNO CONSERVERO KG</v>
+        <v>CACAO AMARGO KG FFVV</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>42014</v>
+        <v>42166</v>
       </c>
       <c r="E32" t="str">
-        <v>1190</v>
+        <v>14760</v>
       </c>
       <c r="F32" t="str">
         <v>Por peso</v>
@@ -1041,19 +1041,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>742009</v>
+        <v>742135</v>
       </c>
       <c r="B33" t="str">
-        <v>DURAZNO AMARILLO KG</v>
+        <v>SANDIA EXTRA PP KG</v>
       </c>
       <c r="C33" t="str">
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>42009</v>
+        <v>42135</v>
       </c>
       <c r="E33" t="str">
-        <v>990</v>
+        <v>490</v>
       </c>
       <c r="F33" t="str">
         <v>Por peso</v>
@@ -1061,19 +1061,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>742122</v>
+        <v>741835</v>
       </c>
       <c r="B34" t="str">
-        <v>DURAZNO BLANCO KG</v>
+        <v>ANIS ESTRELLA KG FFVV</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>42122</v>
+        <v>41835</v>
       </c>
       <c r="E34" t="str">
-        <v>990</v>
+        <v>27160</v>
       </c>
       <c r="F34" t="str">
         <v>Por peso</v>
@@ -1081,19 +1081,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>742033</v>
+        <v>741828</v>
       </c>
       <c r="B35" t="str">
-        <v>CIRUELA KG</v>
+        <v>PEPINO FRUTA LIQUIDACION</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>42033</v>
+        <v>41828</v>
       </c>
       <c r="E35" t="str">
-        <v>690</v>
+        <v>9990</v>
       </c>
       <c r="F35" t="str">
         <v>Por peso</v>
@@ -1101,19 +1101,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>742040</v>
+        <v>741826</v>
       </c>
       <c r="B36" t="str">
-        <v>TUNAS KG</v>
+        <v>TOMATE CHERRY KG FFVV</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>42040</v>
+        <v>41826</v>
       </c>
       <c r="E36" t="str">
-        <v>1190</v>
+        <v>4760</v>
       </c>
       <c r="F36" t="str">
         <v>Por peso</v>
@@ -1121,19 +1121,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>742042</v>
+        <v>741820</v>
       </c>
       <c r="B37" t="str">
-        <v>UVA NEGRA KG</v>
+        <v>MERKEN KG FFVV</v>
       </c>
       <c r="C37" t="str">
         <v/>
       </c>
       <c r="D37" t="str">
-        <v>42042</v>
+        <v>41820</v>
       </c>
       <c r="E37" t="str">
-        <v>1190</v>
+        <v>12360</v>
       </c>
       <c r="F37" t="str">
         <v>Por peso</v>
@@ -1141,19 +1141,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>742041</v>
+        <v>745142</v>
       </c>
       <c r="B38" t="str">
-        <v>TOMATE LARGA VIDA KG</v>
+        <v>CEBOLLA MORADA KG</v>
       </c>
       <c r="C38" t="str">
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>42041</v>
+        <v>45142</v>
       </c>
       <c r="E38" t="str">
-        <v>1490</v>
+        <v>790</v>
       </c>
       <c r="F38" t="str">
         <v>Por peso</v>
@@ -1161,19 +1161,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>742166</v>
+        <v>742075</v>
       </c>
       <c r="B39" t="str">
-        <v>CACAO AMARGO KG FFVV</v>
+        <v>PERA FORELLE KG</v>
       </c>
       <c r="C39" t="str">
         <v/>
       </c>
       <c r="D39" t="str">
-        <v>42166</v>
+        <v>42075</v>
       </c>
       <c r="E39" t="str">
-        <v>14760</v>
+        <v>890</v>
       </c>
       <c r="F39" t="str">
         <v>Por peso</v>
@@ -1181,19 +1181,19 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>742135</v>
+        <v>742118</v>
       </c>
       <c r="B40" t="str">
-        <v>SANDIA EXTRA PP KG</v>
+        <v>CLEMENTINA MANDARINA KG</v>
       </c>
       <c r="C40" t="str">
         <v/>
       </c>
       <c r="D40" t="str">
-        <v>42135</v>
+        <v>42118</v>
       </c>
       <c r="E40" t="str">
-        <v>490</v>
+        <v>1490</v>
       </c>
       <c r="F40" t="str">
         <v>Por peso</v>
@@ -1201,19 +1201,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>741835</v>
+        <v>742016</v>
       </c>
       <c r="B41" t="str">
-        <v>ANIS ESTRELLA KG FFVV</v>
+        <v>CASTANAS KILO FFVV</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
       <c r="D41" t="str">
-        <v>41835</v>
+        <v>42016</v>
       </c>
       <c r="E41" t="str">
-        <v>27160</v>
+        <v>1990</v>
       </c>
       <c r="F41" t="str">
         <v>Por peso</v>
@@ -1221,19 +1221,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>741828</v>
+        <v>742001</v>
       </c>
       <c r="B42" t="str">
-        <v>PEPINO FRUTA LIQUIDACION</v>
+        <v>FRUTA CONFITADA KG FFVV</v>
       </c>
       <c r="C42" t="str">
         <v/>
       </c>
       <c r="D42" t="str">
-        <v>41828</v>
+        <v>42001</v>
       </c>
       <c r="E42" t="str">
-        <v>9990</v>
+        <v>5560</v>
       </c>
       <c r="F42" t="str">
         <v>Por peso</v>
@@ -1241,19 +1241,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>741826</v>
+        <v>742158</v>
       </c>
       <c r="B43" t="str">
-        <v>TOMATE CHERRY KG FFVV</v>
+        <v>MANZANA CRISS PINK KG</v>
       </c>
       <c r="C43" t="str">
         <v/>
       </c>
       <c r="D43" t="str">
-        <v>41826</v>
+        <v>42158</v>
       </c>
       <c r="E43" t="str">
-        <v>4760</v>
+        <v>990</v>
       </c>
       <c r="F43" t="str">
         <v>Por peso</v>
@@ -1261,19 +1261,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>741820</v>
+        <v>741064</v>
       </c>
       <c r="B44" t="str">
-        <v>MERKEN KG FFVV</v>
+        <v>ZAPALLO JAMBOREE SAMPSON PP KG</v>
       </c>
       <c r="C44" t="str">
         <v/>
       </c>
       <c r="D44" t="str">
-        <v>41820</v>
+        <v>41064</v>
       </c>
       <c r="E44" t="str">
-        <v>12360</v>
+        <v>790</v>
       </c>
       <c r="F44" t="str">
         <v>Por peso</v>
@@ -1281,16 +1281,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>745142</v>
+        <v>741039</v>
       </c>
       <c r="B45" t="str">
-        <v>CEBOLLA MORADA KG</v>
+        <v>ZAPALLO CAMOTE KG</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45" t="str">
-        <v>45142</v>
+        <v>41039</v>
       </c>
       <c r="E45" t="str">
         <v>790</v>
@@ -1301,19 +1301,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>742075</v>
+        <v>741025</v>
       </c>
       <c r="B46" t="str">
-        <v>PERA FORELLE KG</v>
+        <v>POROTO VERDE KG</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46" t="str">
-        <v>42075</v>
+        <v>41025</v>
       </c>
       <c r="E46" t="str">
-        <v>890</v>
+        <v>2290</v>
       </c>
       <c r="F46" t="str">
         <v>Por peso</v>
@@ -1321,19 +1321,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>742118</v>
+        <v>741026</v>
       </c>
       <c r="B47" t="str">
-        <v>CLEMENTINA MANDARINA KG</v>
+        <v>POROTO GRANADO KG</v>
       </c>
       <c r="C47" t="str">
         <v/>
       </c>
       <c r="D47" t="str">
-        <v>42118</v>
+        <v>41026</v>
       </c>
       <c r="E47" t="str">
-        <v>1490</v>
+        <v>2290</v>
       </c>
       <c r="F47" t="str">
         <v>Por peso</v>
@@ -1341,19 +1341,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>742016</v>
+        <v>741051</v>
       </c>
       <c r="B48" t="str">
-        <v>CASTANAS KILO FFVV</v>
+        <v>PAPA LAVADA KG</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>42016</v>
+        <v>41051</v>
       </c>
       <c r="E48" t="str">
-        <v>1990</v>
+        <v>890</v>
       </c>
       <c r="F48" t="str">
         <v>Por peso</v>
@@ -1361,19 +1361,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>742001</v>
+        <v>741002</v>
       </c>
       <c r="B49" t="str">
-        <v>FRUTA CONFITADA KG FFVV</v>
+        <v>AJI LIQUIDACION</v>
       </c>
       <c r="C49" t="str">
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>42001</v>
+        <v>41002</v>
       </c>
       <c r="E49" t="str">
-        <v>5560</v>
+        <v>9990</v>
       </c>
       <c r="F49" t="str">
         <v>Por peso</v>
@@ -1381,19 +1381,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>742158</v>
+        <v>741021</v>
       </c>
       <c r="B50" t="str">
-        <v>MANZANA CRISS PINK KG</v>
+        <v>MOTE KG</v>
       </c>
       <c r="C50" t="str">
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>42158</v>
+        <v>41021</v>
       </c>
       <c r="E50" t="str">
-        <v>990</v>
+        <v>1290</v>
       </c>
       <c r="F50" t="str">
         <v>Por peso</v>
@@ -1401,19 +1401,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>741064</v>
+        <v>741014</v>
       </c>
       <c r="B51" t="str">
-        <v>ZAPALLO JAMBOREE SAMPSON PP KG</v>
+        <v>HABAS KG</v>
       </c>
       <c r="C51" t="str">
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>41064</v>
+        <v>41014</v>
       </c>
       <c r="E51" t="str">
-        <v>790</v>
+        <v>990</v>
       </c>
       <c r="F51" t="str">
         <v>Por peso</v>
@@ -1421,19 +1421,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>741039</v>
+        <v>741046</v>
       </c>
       <c r="B52" t="str">
-        <v>ZAPALLO CAMOTE KG</v>
+        <v>AJI CACHO CABRA SECO KG</v>
       </c>
       <c r="C52" t="str">
         <v/>
       </c>
       <c r="D52" t="str">
-        <v>41039</v>
+        <v>41046</v>
       </c>
       <c r="E52" t="str">
-        <v>790</v>
+        <v>13160</v>
       </c>
       <c r="F52" t="str">
         <v>Por peso</v>
@@ -1441,19 +1441,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>741025</v>
+        <v>741079</v>
       </c>
       <c r="B53" t="str">
-        <v>POROTO VERDE KG</v>
+        <v>CEBOLLA BLANCA CRISTAL KG</v>
       </c>
       <c r="C53" t="str">
         <v/>
       </c>
       <c r="D53" t="str">
-        <v>41025</v>
+        <v>41079</v>
       </c>
       <c r="E53" t="str">
-        <v>2290</v>
+        <v>790</v>
       </c>
       <c r="F53" t="str">
         <v>Por peso</v>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>741026</v>
+        <v>741080</v>
       </c>
       <c r="B54" t="str">
-        <v>POROTO GRANADO KG</v>
+        <v>CEBOLLA CUGAT PP KG</v>
       </c>
       <c r="C54" t="str">
         <v/>
       </c>
       <c r="D54" t="str">
-        <v>41026</v>
+        <v>41080</v>
       </c>
       <c r="E54" t="str">
-        <v>2290</v>
+        <v>690</v>
       </c>
       <c r="F54" t="str">
         <v>Por peso</v>
@@ -1481,19 +1481,19 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>741051</v>
+        <v>741055</v>
       </c>
       <c r="B55" t="str">
-        <v>PAPA LAVADA KG</v>
+        <v>BRUSELAS KG</v>
       </c>
       <c r="C55" t="str">
         <v/>
       </c>
       <c r="D55" t="str">
-        <v>41051</v>
+        <v>41055</v>
       </c>
       <c r="E55" t="str">
-        <v>890</v>
+        <v>2590</v>
       </c>
       <c r="F55" t="str">
         <v>Por peso</v>
@@ -1501,19 +1501,19 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>741002</v>
+        <v>741129</v>
       </c>
       <c r="B56" t="str">
-        <v>AJI LIQUIDACION</v>
+        <v>PAPA SURENA KILO</v>
       </c>
       <c r="C56" t="str">
         <v/>
       </c>
       <c r="D56" t="str">
-        <v>41002</v>
+        <v>41129</v>
       </c>
       <c r="E56" t="str">
-        <v>9990</v>
+        <v>690</v>
       </c>
       <c r="F56" t="str">
         <v>Por peso</v>
@@ -1521,19 +1521,19 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>741021</v>
+        <v>741042</v>
       </c>
       <c r="B57" t="str">
-        <v>MOTE KG</v>
+        <v>ZANAHORIA KG</v>
       </c>
       <c r="C57" t="str">
         <v/>
       </c>
       <c r="D57" t="str">
-        <v>41021</v>
+        <v>41042</v>
       </c>
       <c r="E57" t="str">
-        <v>1290</v>
+        <v>690</v>
       </c>
       <c r="F57" t="str">
         <v>Por peso</v>
@@ -1541,19 +1541,19 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>741014</v>
+        <v>741420</v>
       </c>
       <c r="B58" t="str">
-        <v>HABAS KG</v>
+        <v>PAPA CAMOTE KG</v>
       </c>
       <c r="C58" t="str">
         <v/>
       </c>
       <c r="D58" t="str">
-        <v>41014</v>
+        <v>41420</v>
       </c>
       <c r="E58" t="str">
-        <v>990</v>
+        <v>1990</v>
       </c>
       <c r="F58" t="str">
         <v>Por peso</v>
@@ -1561,19 +1561,19 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>741046</v>
+        <v>741030</v>
       </c>
       <c r="B59" t="str">
-        <v>AJI CACHO CABRA SECO KG</v>
+        <v>PAPA KG</v>
       </c>
       <c r="C59" t="str">
         <v/>
       </c>
       <c r="D59" t="str">
-        <v>41046</v>
+        <v>41030</v>
       </c>
       <c r="E59" t="str">
-        <v>13160</v>
+        <v>790</v>
       </c>
       <c r="F59" t="str">
         <v>Por peso</v>
@@ -1581,19 +1581,19 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>741079</v>
+        <v>741107</v>
       </c>
       <c r="B60" t="str">
-        <v>CEBOLLA BLANCA CRISTAL KG</v>
+        <v>CRANBERRY KG FFVV</v>
       </c>
       <c r="C60" t="str">
         <v/>
       </c>
       <c r="D60" t="str">
-        <v>41079</v>
+        <v>41107</v>
       </c>
       <c r="E60" t="str">
-        <v>790</v>
+        <v>12360</v>
       </c>
       <c r="F60" t="str">
         <v>Por peso</v>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>741080</v>
+        <v>741180</v>
       </c>
       <c r="B61" t="str">
-        <v>CEBOLLA CUGAT PP KG</v>
+        <v>PAPA BLANCA KG</v>
       </c>
       <c r="C61" t="str">
         <v/>
       </c>
       <c r="D61" t="str">
-        <v>41080</v>
+        <v>41180</v>
       </c>
       <c r="E61" t="str">
-        <v>690</v>
+        <v>1190</v>
       </c>
       <c r="F61" t="str">
         <v>Por peso</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>741055</v>
+        <v>741043</v>
       </c>
       <c r="B62" t="str">
-        <v>BRUSELAS KG</v>
+        <v>SESAMO BLANCO KILO FFVV</v>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
       <c r="D62" t="str">
-        <v>41055</v>
+        <v>41043</v>
       </c>
       <c r="E62" t="str">
-        <v>2590</v>
+        <v>9960</v>
       </c>
       <c r="F62" t="str">
         <v>Por peso</v>
@@ -1641,19 +1641,19 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>741129</v>
+        <v>742121</v>
       </c>
       <c r="B63" t="str">
-        <v>PAPA SURENA KILO</v>
+        <v>LIMON SUTIL KG</v>
       </c>
       <c r="C63" t="str">
         <v/>
       </c>
       <c r="D63" t="str">
-        <v>41129</v>
+        <v>42121</v>
       </c>
       <c r="E63" t="str">
-        <v>690</v>
+        <v>2190</v>
       </c>
       <c r="F63" t="str">
         <v>Por peso</v>
@@ -1661,19 +1661,19 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>741042</v>
+        <v>742064</v>
       </c>
       <c r="B64" t="str">
-        <v>ZANAHORIA KG</v>
+        <v>AJO CHILOTE KG</v>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64" t="str">
-        <v>41042</v>
+        <v>42064</v>
       </c>
       <c r="E64" t="str">
-        <v>690</v>
+        <v>10760</v>
       </c>
       <c r="F64" t="str">
         <v>Por peso</v>
@@ -1681,19 +1681,19 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>741420</v>
+        <v>741031</v>
       </c>
       <c r="B65" t="str">
-        <v>PAPA CAMOTE KG</v>
+        <v>AJI VERDE KG</v>
       </c>
       <c r="C65" t="str">
         <v/>
       </c>
       <c r="D65" t="str">
-        <v>41420</v>
+        <v>41031</v>
       </c>
       <c r="E65" t="str">
-        <v>1990</v>
+        <v>5960</v>
       </c>
       <c r="F65" t="str">
         <v>Por peso</v>
@@ -1701,19 +1701,19 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>741030</v>
+        <v>741211</v>
       </c>
       <c r="B66" t="str">
-        <v>PAPA KG</v>
+        <v>UVA RED GLOBE KG</v>
       </c>
       <c r="C66" t="str">
         <v/>
       </c>
       <c r="D66" t="str">
-        <v>41030</v>
+        <v>41211</v>
       </c>
       <c r="E66" t="str">
-        <v>790</v>
+        <v>1190</v>
       </c>
       <c r="F66" t="str">
         <v>Por peso</v>
@@ -1721,19 +1721,19 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>741107</v>
+        <v>741111</v>
       </c>
       <c r="B67" t="str">
-        <v>CRANBERRY KG FFVV</v>
+        <v>CANELA EN POLVO KG FFVV</v>
       </c>
       <c r="C67" t="str">
         <v/>
       </c>
       <c r="D67" t="str">
-        <v>41107</v>
+        <v>41111</v>
       </c>
       <c r="E67" t="str">
-        <v>12360</v>
+        <v>19160</v>
       </c>
       <c r="F67" t="str">
         <v>Por peso</v>
@@ -1741,19 +1741,19 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>741180</v>
+        <v>741052</v>
       </c>
       <c r="B68" t="str">
-        <v>PAPA BLANCA KG</v>
+        <v>ZAPALLO BUTTERNUT KG</v>
       </c>
       <c r="C68" t="str">
         <v/>
       </c>
       <c r="D68" t="str">
-        <v>41180</v>
+        <v>41052</v>
       </c>
       <c r="E68" t="str">
-        <v>1190</v>
+        <v>690</v>
       </c>
       <c r="F68" t="str">
         <v>Por peso</v>
@@ -1761,19 +1761,19 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>741043</v>
+        <v>742090</v>
       </c>
       <c r="B69" t="str">
-        <v>SESAMO BLANCO KILO FFVV</v>
+        <v>NARANJA KG</v>
       </c>
       <c r="C69" t="str">
         <v/>
       </c>
       <c r="D69" t="str">
-        <v>41043</v>
+        <v>42090</v>
       </c>
       <c r="E69" t="str">
-        <v>9960</v>
+        <v>1290</v>
       </c>
       <c r="F69" t="str">
         <v>Por peso</v>
@@ -1781,19 +1781,19 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>742121</v>
+        <v>742095</v>
       </c>
       <c r="B70" t="str">
-        <v>LIMON SUTIL KG</v>
+        <v>MARAVILLA PELADA KG FFVV</v>
       </c>
       <c r="C70" t="str">
         <v/>
       </c>
       <c r="D70" t="str">
-        <v>42121</v>
+        <v>42095</v>
       </c>
       <c r="E70" t="str">
-        <v>2190</v>
+        <v>5160</v>
       </c>
       <c r="F70" t="str">
         <v>Por peso</v>
@@ -1801,19 +1801,19 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>742064</v>
+        <v>744501</v>
       </c>
       <c r="B71" t="str">
-        <v>AJO CHILOTE KG</v>
+        <v>AJO EN POLVO KG FFYVV</v>
       </c>
       <c r="C71" t="str">
         <v/>
       </c>
       <c r="D71" t="str">
-        <v>42064</v>
+        <v>44501</v>
       </c>
       <c r="E71" t="str">
-        <v>10760</v>
+        <v>8760</v>
       </c>
       <c r="F71" t="str">
         <v>Por peso</v>
@@ -1821,19 +1821,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>741031</v>
+        <v>744502</v>
       </c>
       <c r="B72" t="str">
-        <v>AJI VERDE KG</v>
+        <v>ALINO COMPLETO KG FFYVV</v>
       </c>
       <c r="C72" t="str">
         <v/>
       </c>
       <c r="D72" t="str">
-        <v>41031</v>
+        <v>44502</v>
       </c>
       <c r="E72" t="str">
-        <v>5960</v>
+        <v>8360</v>
       </c>
       <c r="F72" t="str">
         <v>Por peso</v>
@@ -1841,19 +1841,19 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>742097</v>
+        <v>744503</v>
       </c>
       <c r="B73" t="str">
-        <v>LIMON TAHITI KG</v>
+        <v>BICARBONATO KG FFVV</v>
       </c>
       <c r="C73" t="str">
         <v/>
       </c>
       <c r="D73" t="str">
-        <v>42097</v>
+        <v>44503</v>
       </c>
       <c r="E73" t="str">
-        <v>1490</v>
+        <v>2360</v>
       </c>
       <c r="F73" t="str">
         <v>Por peso</v>
@@ -1861,19 +1861,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>741211</v>
+        <v>744504</v>
       </c>
       <c r="B74" t="str">
-        <v>UVA RED GLOBE KG</v>
+        <v>COMINO MOLIDO KG FFVV</v>
       </c>
       <c r="C74" t="str">
         <v/>
       </c>
       <c r="D74" t="str">
-        <v>41211</v>
+        <v>44504</v>
       </c>
       <c r="E74" t="str">
-        <v>1190</v>
+        <v>21160</v>
       </c>
       <c r="F74" t="str">
         <v>Por peso</v>
@@ -1881,19 +1881,19 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>741111</v>
+        <v>744505</v>
       </c>
       <c r="B75" t="str">
-        <v>CANELA EN POLVO KG FFVV</v>
+        <v>MAIZ CURAGUA KG FFVV</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75" t="str">
-        <v>41111</v>
+        <v>44505</v>
       </c>
       <c r="E75" t="str">
-        <v>19160</v>
+        <v>3160</v>
       </c>
       <c r="F75" t="str">
         <v>Por peso</v>
@@ -1901,19 +1901,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>741052</v>
+        <v>744589</v>
       </c>
       <c r="B76" t="str">
-        <v>ZAPALLO BUTTERNUT KG</v>
+        <v>PALTA HASS KG</v>
       </c>
       <c r="C76" t="str">
         <v/>
       </c>
       <c r="D76" t="str">
-        <v>41052</v>
+        <v>44589</v>
       </c>
       <c r="E76" t="str">
-        <v>690</v>
+        <v>5690</v>
       </c>
       <c r="F76" t="str">
         <v>Por peso</v>
@@ -1921,19 +1921,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>742090</v>
+        <v>742038</v>
       </c>
       <c r="B77" t="str">
-        <v>NARANJA KG</v>
+        <v>UVA VERDE KG</v>
       </c>
       <c r="C77" t="str">
         <v/>
       </c>
       <c r="D77" t="str">
-        <v>42090</v>
+        <v>42038</v>
       </c>
       <c r="E77" t="str">
-        <v>1290</v>
+        <v>1590</v>
       </c>
       <c r="F77" t="str">
         <v>Por peso</v>
@@ -1941,19 +1941,19 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>742095</v>
+        <v>749205</v>
       </c>
       <c r="B78" t="str">
-        <v>MARAVILLA PELADA KG FFVV</v>
+        <v>VASO MELON TROZOS FFVV</v>
       </c>
       <c r="C78" t="str">
         <v/>
       </c>
       <c r="D78" t="str">
-        <v>42095</v>
+        <v>29205</v>
       </c>
       <c r="E78" t="str">
-        <v>5160</v>
+        <v>790</v>
       </c>
       <c r="F78" t="str">
         <v>Por peso</v>
@@ -1961,19 +1961,19 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>744501</v>
+        <v>741112</v>
       </c>
       <c r="B79" t="str">
-        <v>AJO EN POLVO KG FFYVV</v>
+        <v>COMINO ENTERO KG FFVV</v>
       </c>
       <c r="C79" t="str">
         <v/>
       </c>
       <c r="D79" t="str">
-        <v>44501</v>
+        <v>41112</v>
       </c>
       <c r="E79" t="str">
-        <v>8760</v>
+        <v>19160</v>
       </c>
       <c r="F79" t="str">
         <v>Por peso</v>
@@ -1981,19 +1981,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>744502</v>
+        <v>744509</v>
       </c>
       <c r="B80" t="str">
-        <v>ALINO COMPLETO KG FFYVV</v>
+        <v>PIMIENTA NEGRA MOLIDA KG FFVV</v>
       </c>
       <c r="C80" t="str">
         <v/>
       </c>
       <c r="D80" t="str">
-        <v>44502</v>
+        <v>44509</v>
       </c>
       <c r="E80" t="str">
-        <v>8360</v>
+        <v>27160</v>
       </c>
       <c r="F80" t="str">
         <v>Por peso</v>
@@ -2001,19 +2001,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>744503</v>
+        <v>744510</v>
       </c>
       <c r="B81" t="str">
-        <v>BICARBONATO KG FFVV</v>
+        <v>LINAZA MOLIDA KG FFVV</v>
       </c>
       <c r="C81" t="str">
         <v/>
       </c>
       <c r="D81" t="str">
-        <v>44503</v>
+        <v>44510</v>
       </c>
       <c r="E81" t="str">
-        <v>2360</v>
+        <v>5960</v>
       </c>
       <c r="F81" t="str">
         <v>Por peso</v>
@@ -2021,19 +2021,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>744504</v>
+        <v>744511</v>
       </c>
       <c r="B82" t="str">
-        <v>COMINO MOLIDO KG FFVV</v>
+        <v>LINAZA ENTERA KG FFVV</v>
       </c>
       <c r="C82" t="str">
         <v/>
       </c>
       <c r="D82" t="str">
-        <v>44504</v>
+        <v>44511</v>
       </c>
       <c r="E82" t="str">
-        <v>21160</v>
+        <v>5160</v>
       </c>
       <c r="F82" t="str">
         <v>Por peso</v>
@@ -2041,19 +2041,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>744505</v>
+        <v>741401</v>
       </c>
       <c r="B83" t="str">
-        <v>MAIZ CURAGUA KG FFVV</v>
+        <v>AJI CACHO CABRA AHUMADO KG</v>
       </c>
       <c r="C83" t="str">
         <v/>
       </c>
       <c r="D83" t="str">
-        <v>44505</v>
+        <v>41401</v>
       </c>
       <c r="E83" t="str">
-        <v>3160</v>
+        <v>13160</v>
       </c>
       <c r="F83" t="str">
         <v>Por peso</v>
@@ -2061,19 +2061,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>744589</v>
+        <v>741011</v>
       </c>
       <c r="B84" t="str">
-        <v>PALTA HASS KG</v>
+        <v>CURCUMA KG</v>
       </c>
       <c r="C84" t="str">
         <v/>
       </c>
       <c r="D84" t="str">
-        <v>44589</v>
+        <v>41011</v>
       </c>
       <c r="E84" t="str">
-        <v>5690</v>
+        <v>2990</v>
       </c>
       <c r="F84" t="str">
         <v>Por peso</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>742038</v>
+        <v>744140</v>
       </c>
       <c r="B85" t="str">
-        <v>UVA VERDE KG</v>
+        <v>CLAVO DE OLOR MOLIDO KG FFVV</v>
       </c>
       <c r="C85" t="str">
         <v/>
       </c>
       <c r="D85" t="str">
-        <v>42038</v>
+        <v>44140</v>
       </c>
       <c r="E85" t="str">
-        <v>1590</v>
+        <v>18760</v>
       </c>
       <c r="F85" t="str">
         <v>Por peso</v>
@@ -2101,19 +2101,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>749205</v>
+        <v>741083</v>
       </c>
       <c r="B86" t="str">
-        <v>VASO MELON TROZOS FFVV</v>
+        <v>SEMILLA DE ZAPALLO KG FFVV</v>
       </c>
       <c r="C86" t="str">
         <v/>
       </c>
       <c r="D86" t="str">
-        <v>29205</v>
+        <v>41083</v>
       </c>
       <c r="E86" t="str">
-        <v>790</v>
+        <v>14760</v>
       </c>
       <c r="F86" t="str">
         <v>Por peso</v>
@@ -2121,19 +2121,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>741112</v>
+        <v>742511</v>
       </c>
       <c r="B87" t="str">
-        <v>COMINO ENTERO KG FFVV</v>
+        <v>KIWI LIQUIDACION</v>
       </c>
       <c r="C87" t="str">
         <v/>
       </c>
       <c r="D87" t="str">
-        <v>41112</v>
+        <v>42511</v>
       </c>
       <c r="E87" t="str">
-        <v>19160</v>
+        <v>9990</v>
       </c>
       <c r="F87" t="str">
         <v>Por peso</v>
@@ -2141,19 +2141,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>744509</v>
+        <v>741519</v>
       </c>
       <c r="B88" t="str">
-        <v>PIMIENTA NEGRA MOLIDA KG FFVV</v>
+        <v>PLATANO BARRAGANETE VERDE KG</v>
       </c>
       <c r="C88" t="str">
         <v/>
       </c>
       <c r="D88" t="str">
-        <v>44509</v>
+        <v>41519</v>
       </c>
       <c r="E88" t="str">
-        <v>27160</v>
+        <v>1990</v>
       </c>
       <c r="F88" t="str">
         <v>Por peso</v>
@@ -2161,19 +2161,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>744510</v>
+        <v>744521</v>
       </c>
       <c r="B89" t="str">
-        <v>LINAZA MOLIDA KG FFVV</v>
+        <v>CACAO AZUCARADO KG FFYVV</v>
       </c>
       <c r="C89" t="str">
         <v/>
       </c>
       <c r="D89" t="str">
-        <v>44510</v>
+        <v>44521</v>
       </c>
       <c r="E89" t="str">
-        <v>5960</v>
+        <v>12360</v>
       </c>
       <c r="F89" t="str">
         <v>Por peso</v>
@@ -2181,19 +2181,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>744511</v>
+        <v>744522</v>
       </c>
       <c r="B90" t="str">
-        <v>LINAZA ENTERA KG FFVV</v>
+        <v>PROTEINA VEGETAL KG FFVV</v>
       </c>
       <c r="C90" t="str">
         <v/>
       </c>
       <c r="D90" t="str">
-        <v>44511</v>
+        <v>44522</v>
       </c>
       <c r="E90" t="str">
-        <v>5160</v>
+        <v>4760</v>
       </c>
       <c r="F90" t="str">
         <v>Por peso</v>
@@ -2201,19 +2201,19 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>741401</v>
+        <v>744523</v>
       </c>
       <c r="B91" t="str">
-        <v>AJI CACHO CABRA AHUMADO KG</v>
+        <v>CHUNO KG FFVV</v>
       </c>
       <c r="C91" t="str">
         <v/>
       </c>
       <c r="D91" t="str">
-        <v>41401</v>
+        <v>44523</v>
       </c>
       <c r="E91" t="str">
-        <v>13160</v>
+        <v>5160</v>
       </c>
       <c r="F91" t="str">
         <v>Por peso</v>
@@ -2221,19 +2221,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>741011</v>
+        <v>744524</v>
       </c>
       <c r="B92" t="str">
-        <v>CURCUMA KG</v>
+        <v>TE CEYLAN HOJA KG FFVV</v>
       </c>
       <c r="C92" t="str">
         <v/>
       </c>
       <c r="D92" t="str">
-        <v>41011</v>
+        <v>44524</v>
       </c>
       <c r="E92" t="str">
-        <v>2990</v>
+        <v>17160</v>
       </c>
       <c r="F92" t="str">
         <v>Por peso</v>
@@ -2241,19 +2241,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>744140</v>
+        <v>744525</v>
       </c>
       <c r="B93" t="str">
-        <v>CLAVO DE OLOR MOLIDO KG FFVV</v>
+        <v>COCO RALLADO KG FFVV</v>
       </c>
       <c r="C93" t="str">
         <v/>
       </c>
       <c r="D93" t="str">
-        <v>44140</v>
+        <v>44525</v>
       </c>
       <c r="E93" t="str">
-        <v>18760</v>
+        <v>14760</v>
       </c>
       <c r="F93" t="str">
         <v>Por peso</v>
@@ -2261,19 +2261,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>741083</v>
+        <v>744526</v>
       </c>
       <c r="B94" t="str">
-        <v>SEMILLA DE ZAPALLO KG FFVV</v>
+        <v>CANELA ENTERA KG FFVV</v>
       </c>
       <c r="C94" t="str">
         <v/>
       </c>
       <c r="D94" t="str">
-        <v>41083</v>
+        <v>44526</v>
       </c>
       <c r="E94" t="str">
-        <v>14760</v>
+        <v>55160</v>
       </c>
       <c r="F94" t="str">
         <v>Por peso</v>
@@ -2281,19 +2281,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>742511</v>
+        <v>744527</v>
       </c>
       <c r="B95" t="str">
-        <v>KIWI LIQUIDACION</v>
+        <v>TE VERDE KG FFVV</v>
       </c>
       <c r="C95" t="str">
         <v/>
       </c>
       <c r="D95" t="str">
-        <v>42511</v>
+        <v>44527</v>
       </c>
       <c r="E95" t="str">
-        <v>9990</v>
+        <v>13960</v>
       </c>
       <c r="F95" t="str">
         <v>Por peso</v>
@@ -2301,19 +2301,19 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>741519</v>
+        <v>744528</v>
       </c>
       <c r="B96" t="str">
-        <v>PLATANO BARRAGANETE VERDE KG</v>
+        <v>MAICENA KG FFVV</v>
       </c>
       <c r="C96" t="str">
         <v/>
       </c>
       <c r="D96" t="str">
-        <v>41519</v>
+        <v>44528</v>
       </c>
       <c r="E96" t="str">
-        <v>1990</v>
+        <v>3160</v>
       </c>
       <c r="F96" t="str">
         <v>Por peso</v>
@@ -2321,19 +2321,19 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>744521</v>
+        <v>742603</v>
       </c>
       <c r="B97" t="str">
-        <v>CACAO AZUCARADO KG FFYVV</v>
+        <v>TOMATE LIQUIDACION</v>
       </c>
       <c r="C97" t="str">
         <v/>
       </c>
       <c r="D97" t="str">
-        <v>44521</v>
+        <v>42603</v>
       </c>
       <c r="E97" t="str">
-        <v>12360</v>
+        <v>9990</v>
       </c>
       <c r="F97" t="str">
         <v>Por peso</v>
@@ -2341,19 +2341,19 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>744522</v>
+        <v>742605</v>
       </c>
       <c r="B98" t="str">
-        <v>PROTEINA VEGETAL KG FFVV</v>
+        <v>PALTA LIQUIDACION</v>
       </c>
       <c r="C98" t="str">
         <v/>
       </c>
       <c r="D98" t="str">
-        <v>44522</v>
+        <v>42605</v>
       </c>
       <c r="E98" t="str">
-        <v>4760</v>
+        <v>4490</v>
       </c>
       <c r="F98" t="str">
         <v>Por peso</v>
@@ -2361,19 +2361,19 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>744523</v>
+        <v>742606</v>
       </c>
       <c r="B99" t="str">
-        <v>CHUNO KG FFVV</v>
+        <v>PLATANO LIQUIDACION</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
       <c r="D99" t="str">
-        <v>44523</v>
+        <v>42606</v>
       </c>
       <c r="E99" t="str">
-        <v>5160</v>
+        <v>9990</v>
       </c>
       <c r="F99" t="str">
         <v>Por peso</v>
@@ -2381,19 +2381,19 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>744524</v>
+        <v>741607</v>
       </c>
       <c r="B100" t="str">
-        <v>TE CEYLAN HOJA KG FFVV</v>
+        <v>ZANAHORIA LIQUIDACION</v>
       </c>
       <c r="C100" t="str">
         <v/>
       </c>
       <c r="D100" t="str">
-        <v>44524</v>
+        <v>41607</v>
       </c>
       <c r="E100" t="str">
-        <v>17160</v>
+        <v>9990</v>
       </c>
       <c r="F100" t="str">
         <v>Por peso</v>
@@ -2401,19 +2401,19 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>744525</v>
+        <v>742402</v>
       </c>
       <c r="B101" t="str">
-        <v>COCO RALLADO KG FFVV</v>
+        <v>CIRUELA LIQUIDACION</v>
       </c>
       <c r="C101" t="str">
         <v/>
       </c>
       <c r="D101" t="str">
-        <v>44525</v>
+        <v>42402</v>
       </c>
       <c r="E101" t="str">
-        <v>14760</v>
+        <v>9990</v>
       </c>
       <c r="F101" t="str">
         <v>Por peso</v>
@@ -2421,19 +2421,19 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>744526</v>
+        <v>742120</v>
       </c>
       <c r="B102" t="str">
-        <v>CANELA ENTERA KG FFVV</v>
+        <v>PERA LIQUIDACION</v>
       </c>
       <c r="C102" t="str">
         <v/>
       </c>
       <c r="D102" t="str">
-        <v>44526</v>
+        <v>42120</v>
       </c>
       <c r="E102" t="str">
-        <v>55160</v>
+        <v>9990</v>
       </c>
       <c r="F102" t="str">
         <v>Por peso</v>
@@ -2441,19 +2441,19 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>744527</v>
+        <v>742126</v>
       </c>
       <c r="B103" t="str">
-        <v>TE VERDE KG FFVV</v>
+        <v>DURAZNO LIQUIDACION KG</v>
       </c>
       <c r="C103" t="str">
         <v/>
       </c>
       <c r="D103" t="str">
-        <v>44527</v>
+        <v>42126</v>
       </c>
       <c r="E103" t="str">
-        <v>13960</v>
+        <v>1990</v>
       </c>
       <c r="F103" t="str">
         <v>Por peso</v>
@@ -2461,19 +2461,19 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>744528</v>
+        <v>742127</v>
       </c>
       <c r="B104" t="str">
-        <v>MAICENA KG FFVV</v>
+        <v>LIMON LIQUIDACION</v>
       </c>
       <c r="C104" t="str">
         <v/>
       </c>
       <c r="D104" t="str">
-        <v>44528</v>
+        <v>42127</v>
       </c>
       <c r="E104" t="str">
-        <v>3160</v>
+        <v>9990</v>
       </c>
       <c r="F104" t="str">
         <v>Por peso</v>
@@ -2481,16 +2481,16 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>742603</v>
+        <v>742128</v>
       </c>
       <c r="B105" t="str">
-        <v>TOMATE LIQUIDACION</v>
+        <v>POROTO VERDE LIQUIDACION KG</v>
       </c>
       <c r="C105" t="str">
         <v/>
       </c>
       <c r="D105" t="str">
-        <v>42603</v>
+        <v>42128</v>
       </c>
       <c r="E105" t="str">
         <v>9990</v>
@@ -2501,19 +2501,19 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>742605</v>
+        <v>742129</v>
       </c>
       <c r="B106" t="str">
-        <v>PALTA LIQUIDACION</v>
+        <v>POROTO GRANADO LIQUIDACION</v>
       </c>
       <c r="C106" t="str">
         <v/>
       </c>
       <c r="D106" t="str">
-        <v>42605</v>
+        <v>42129</v>
       </c>
       <c r="E106" t="str">
-        <v>4490</v>
+        <v>9990</v>
       </c>
       <c r="F106" t="str">
         <v>Por peso</v>
@@ -2521,16 +2521,16 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>742606</v>
+        <v>742130</v>
       </c>
       <c r="B107" t="str">
-        <v>PLATANO LIQUIDACION</v>
+        <v>MANZANA LIQUIDACION</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107" t="str">
-        <v>42606</v>
+        <v>42130</v>
       </c>
       <c r="E107" t="str">
         <v>9990</v>
@@ -2541,16 +2541,16 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>741607</v>
+        <v>741250</v>
       </c>
       <c r="B108" t="str">
-        <v>ZANAHORIA LIQUIDACION</v>
+        <v>UVA LIQUIDACION</v>
       </c>
       <c r="C108" t="str">
         <v/>
       </c>
       <c r="D108" t="str">
-        <v>41607</v>
+        <v>41250</v>
       </c>
       <c r="E108" t="str">
         <v>9990</v>
@@ -2561,16 +2561,16 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>742402</v>
+        <v>742421</v>
       </c>
       <c r="B109" t="str">
-        <v>CIRUELA LIQUIDACION</v>
+        <v>NARANJA LIQUIDACION</v>
       </c>
       <c r="C109" t="str">
         <v/>
       </c>
       <c r="D109" t="str">
-        <v>42402</v>
+        <v>42421</v>
       </c>
       <c r="E109" t="str">
         <v>9990</v>
@@ -2581,19 +2581,19 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>742120</v>
+        <v>745000</v>
       </c>
       <c r="B110" t="str">
-        <v>PERA LIQUIDACION</v>
+        <v>AJO LIQUIDACION</v>
       </c>
       <c r="C110" t="str">
         <v/>
       </c>
       <c r="D110" t="str">
-        <v>42120</v>
+        <v>45000</v>
       </c>
       <c r="E110" t="str">
-        <v>9990</v>
+        <v>9999</v>
       </c>
       <c r="F110" t="str">
         <v>Por peso</v>
@@ -2601,19 +2601,19 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>742126</v>
+        <v>742300</v>
       </c>
       <c r="B111" t="str">
-        <v>DURAZNO LIQUIDACION KG</v>
+        <v>PALTA NEGRA LA CRUZ KG</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111" t="str">
-        <v>42126</v>
+        <v>42300</v>
       </c>
       <c r="E111" t="str">
-        <v>1990</v>
+        <v>3590</v>
       </c>
       <c r="F111" t="str">
         <v>Por peso</v>
@@ -2621,16 +2621,16 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>742127</v>
+        <v>740303</v>
       </c>
       <c r="B112" t="str">
-        <v>LIMON LIQUIDACION</v>
+        <v>PAPA LIQUIDACION</v>
       </c>
       <c r="C112" t="str">
         <v/>
       </c>
       <c r="D112" t="str">
-        <v>42127</v>
+        <v>40303</v>
       </c>
       <c r="E112" t="str">
         <v>9990</v>
@@ -2641,19 +2641,19 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>742128</v>
+        <v>742549</v>
       </c>
       <c r="B113" t="str">
-        <v>POROTO VERDE LIQUIDACION KG</v>
+        <v>NECTARIN LIQUIDACION</v>
       </c>
       <c r="C113" t="str">
         <v/>
       </c>
       <c r="D113" t="str">
-        <v>42128</v>
+        <v>42549</v>
       </c>
       <c r="E113" t="str">
-        <v>9990</v>
+        <v>2290</v>
       </c>
       <c r="F113" t="str">
         <v>Por peso</v>
@@ -2661,19 +2661,19 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>742129</v>
+        <v>748913</v>
       </c>
       <c r="B114" t="str">
-        <v>POROTO GRANADO LIQUIDACION</v>
+        <v>JENGIBRE EN POLVO FFVV</v>
       </c>
       <c r="C114" t="str">
         <v/>
       </c>
       <c r="D114" t="str">
-        <v>42129</v>
+        <v>48913</v>
       </c>
       <c r="E114" t="str">
-        <v>9990</v>
+        <v>14760</v>
       </c>
       <c r="F114" t="str">
         <v>Por peso</v>
@@ -2681,19 +2681,19 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>742130</v>
+        <v>741110</v>
       </c>
       <c r="B115" t="str">
-        <v>MANZANA LIQUIDACION</v>
+        <v>AJI COLOR KILO FFYVV</v>
       </c>
       <c r="C115" t="str">
         <v/>
       </c>
       <c r="D115" t="str">
-        <v>42130</v>
+        <v>41110</v>
       </c>
       <c r="E115" t="str">
-        <v>9990</v>
+        <v>7160</v>
       </c>
       <c r="F115" t="str">
         <v>Por peso</v>
@@ -2701,19 +2701,19 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>741250</v>
+        <v>742333</v>
       </c>
       <c r="B116" t="str">
-        <v>UVA LIQUIDACION</v>
+        <v>MANZANA BICOLOR KG</v>
       </c>
       <c r="C116" t="str">
         <v/>
       </c>
       <c r="D116" t="str">
-        <v>41250</v>
+        <v>42333</v>
       </c>
       <c r="E116" t="str">
-        <v>9990</v>
+        <v>990</v>
       </c>
       <c r="F116" t="str">
         <v>Por peso</v>
@@ -2721,19 +2721,19 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>742421</v>
+        <v>742999</v>
       </c>
       <c r="B117" t="str">
-        <v>NARANJA LIQUIDACION</v>
+        <v>CIRUELA SECA KG FFVV</v>
       </c>
       <c r="C117" t="str">
         <v/>
       </c>
       <c r="D117" t="str">
-        <v>42421</v>
+        <v>42999</v>
       </c>
       <c r="E117" t="str">
-        <v>9990</v>
+        <v>6760</v>
       </c>
       <c r="F117" t="str">
         <v>Por peso</v>
@@ -2741,19 +2741,19 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>745000</v>
+        <v>741222</v>
       </c>
       <c r="B118" t="str">
-        <v>AJO LIQUIDACION</v>
+        <v>OREGANO KG FFVV</v>
       </c>
       <c r="C118" t="str">
         <v/>
       </c>
       <c r="D118" t="str">
-        <v>45000</v>
+        <v>41222</v>
       </c>
       <c r="E118" t="str">
-        <v>9999</v>
+        <v>10360</v>
       </c>
       <c r="F118" t="str">
         <v>Por peso</v>
@@ -2761,19 +2761,19 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>742300</v>
+        <v>741076</v>
       </c>
       <c r="B119" t="str">
-        <v>PALTA NEGRA LA CRUZ KG</v>
+        <v>AJO KG</v>
       </c>
       <c r="C119" t="str">
         <v/>
       </c>
       <c r="D119" t="str">
-        <v>42300</v>
+        <v>41076</v>
       </c>
       <c r="E119" t="str">
-        <v>3590</v>
+        <v>4760</v>
       </c>
       <c r="F119" t="str">
         <v>Por peso</v>
@@ -2781,19 +2781,19 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>740303</v>
+        <v>741076</v>
       </c>
       <c r="B120" t="str">
-        <v>PAPA LIQUIDACION</v>
+        <v>AJO KG</v>
       </c>
       <c r="C120" t="str">
         <v/>
       </c>
       <c r="D120" t="str">
-        <v>40303</v>
+        <v>41076</v>
       </c>
       <c r="E120" t="str">
-        <v>9990</v>
+        <v>2996</v>
       </c>
       <c r="F120" t="str">
         <v>Por peso</v>
@@ -2801,19 +2801,19 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>742549</v>
+        <v>741041</v>
       </c>
       <c r="B121" t="str">
-        <v>NECTARIN LIQUIDACION</v>
+        <v>PAPA ZONA SUR KG</v>
       </c>
       <c r="C121" t="str">
         <v/>
       </c>
       <c r="D121" t="str">
-        <v>42549</v>
+        <v>41041</v>
       </c>
       <c r="E121" t="str">
-        <v>2290</v>
+        <v>990</v>
       </c>
       <c r="F121" t="str">
         <v>Por peso</v>
@@ -2821,19 +2821,19 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>748913</v>
+        <v>744018</v>
       </c>
       <c r="B122" t="str">
-        <v>JENGIBRE EN POLVO FFVV</v>
+        <v>MIX FRUTOS SECOS KG FFVV</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
       <c r="D122" t="str">
-        <v>48913</v>
+        <v>44018</v>
       </c>
       <c r="E122" t="str">
-        <v>14760</v>
+        <v>6760</v>
       </c>
       <c r="F122" t="str">
         <v>Por peso</v>
@@ -2841,19 +2841,19 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>741110</v>
+        <v>748081</v>
       </c>
       <c r="B123" t="str">
-        <v>AJI COLOR KILO FFYVV</v>
+        <v>MANCAQUI KG</v>
       </c>
       <c r="C123" t="str">
         <v/>
       </c>
       <c r="D123" t="str">
-        <v>41110</v>
+        <v>48081</v>
       </c>
       <c r="E123" t="str">
-        <v>7160</v>
+        <v>1390</v>
       </c>
       <c r="F123" t="str">
         <v>Por peso</v>
@@ -2861,19 +2861,19 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>742333</v>
+        <v>747810</v>
       </c>
       <c r="B124" t="str">
-        <v>MANZANA BICOLOR KG</v>
+        <v>MANI SIN SAL KG FFVV</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124" t="str">
-        <v>42333</v>
+        <v>47810</v>
       </c>
       <c r="E124" t="str">
-        <v>990</v>
+        <v>4990</v>
       </c>
       <c r="F124" t="str">
         <v>Por peso</v>
@@ -2881,19 +2881,19 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>742999</v>
+        <v>747809</v>
       </c>
       <c r="B125" t="str">
-        <v>CIRUELA SECA KG FFVV</v>
+        <v>MANI CON SAL KG FFVV</v>
       </c>
       <c r="C125" t="str">
         <v/>
       </c>
       <c r="D125" t="str">
-        <v>42999</v>
+        <v>47809</v>
       </c>
       <c r="E125" t="str">
-        <v>6760</v>
+        <v>4990</v>
       </c>
       <c r="F125" t="str">
         <v>Por peso</v>
@@ -2901,19 +2901,19 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>741222</v>
+        <v>746548</v>
       </c>
       <c r="B126" t="str">
-        <v>OREGANO KG FFVV</v>
+        <v>PAPA CHILOTA MIX KILO</v>
       </c>
       <c r="C126" t="str">
         <v/>
       </c>
       <c r="D126" t="str">
-        <v>41222</v>
+        <v>46548</v>
       </c>
       <c r="E126" t="str">
-        <v>10360</v>
+        <v>2590</v>
       </c>
       <c r="F126" t="str">
         <v>Por peso</v>
@@ -2921,19 +2921,19 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>741076</v>
+        <v>743062</v>
       </c>
       <c r="B127" t="str">
-        <v>AJO KG</v>
+        <v>CEBOLLA KG FFVV</v>
       </c>
       <c r="C127" t="str">
         <v/>
       </c>
       <c r="D127" t="str">
-        <v>41076</v>
+        <v>43062</v>
       </c>
       <c r="E127" t="str">
-        <v>4760</v>
+        <v>690</v>
       </c>
       <c r="F127" t="str">
         <v>Por peso</v>
@@ -2941,19 +2941,19 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>741076</v>
+        <v>743654</v>
       </c>
       <c r="B128" t="str">
-        <v>AJO KG</v>
+        <v>DATILES KG FFVV</v>
       </c>
       <c r="C128" t="str">
         <v/>
       </c>
       <c r="D128" t="str">
-        <v>41076</v>
+        <v>43654</v>
       </c>
       <c r="E128" t="str">
-        <v>2996</v>
+        <v>7160</v>
       </c>
       <c r="F128" t="str">
         <v>Por peso</v>
@@ -2961,19 +2961,19 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>741041</v>
+        <v>744552</v>
       </c>
       <c r="B129" t="str">
-        <v>PAPA ZONA SUR KG</v>
+        <v>CHIA KG FFVV</v>
       </c>
       <c r="C129" t="str">
         <v/>
       </c>
       <c r="D129" t="str">
-        <v>41041</v>
+        <v>44552</v>
       </c>
       <c r="E129" t="str">
-        <v>990</v>
+        <v>9960</v>
       </c>
       <c r="F129" t="str">
         <v>Por peso</v>
@@ -2981,19 +2981,19 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>744018</v>
+        <v>742939</v>
       </c>
       <c r="B130" t="str">
-        <v>MIX FRUTOS SECOS KG FFVV</v>
+        <v>CEBOLLA LIQUIDACION</v>
       </c>
       <c r="C130" t="str">
         <v/>
       </c>
       <c r="D130" t="str">
-        <v>44018</v>
+        <v>42939</v>
       </c>
       <c r="E130" t="str">
-        <v>6760</v>
+        <v>9990</v>
       </c>
       <c r="F130" t="str">
         <v>Por peso</v>
@@ -3001,19 +3001,19 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>748081</v>
+        <v>743232</v>
       </c>
       <c r="B131" t="str">
-        <v>MANCAQUI KG</v>
+        <v>POMELO LIQUIDACION</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
       <c r="D131" t="str">
-        <v>48081</v>
+        <v>43232</v>
       </c>
       <c r="E131" t="str">
-        <v>1390</v>
+        <v>9990</v>
       </c>
       <c r="F131" t="str">
         <v>Por peso</v>
@@ -3021,19 +3021,19 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>747810</v>
+        <v>743233</v>
       </c>
       <c r="B132" t="str">
-        <v>MANI SIN SAL KG FFVV</v>
+        <v>MANGO LIQUIDACION</v>
       </c>
       <c r="C132" t="str">
         <v/>
       </c>
       <c r="D132" t="str">
-        <v>47810</v>
+        <v>43233</v>
       </c>
       <c r="E132" t="str">
-        <v>4990</v>
+        <v>9990</v>
       </c>
       <c r="F132" t="str">
         <v>Por peso</v>
@@ -3041,19 +3041,19 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>747809</v>
+        <v>743237</v>
       </c>
       <c r="B133" t="str">
-        <v>MANI CON SAL KG FFVV</v>
+        <v>UVA ROSADA KG</v>
       </c>
       <c r="C133" t="str">
         <v/>
       </c>
       <c r="D133" t="str">
-        <v>47809</v>
+        <v>43237</v>
       </c>
       <c r="E133" t="str">
-        <v>4990</v>
+        <v>1190</v>
       </c>
       <c r="F133" t="str">
         <v>Por peso</v>
@@ -3061,19 +3061,19 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>746548</v>
+        <v>743038</v>
       </c>
       <c r="B134" t="str">
-        <v>PAPA CHILOTA MIX KILO</v>
+        <v>CURCUMA MOLIDA KG FFVV</v>
       </c>
       <c r="C134" t="str">
         <v/>
       </c>
       <c r="D134" t="str">
-        <v>46548</v>
+        <v>43038</v>
       </c>
       <c r="E134" t="str">
-        <v>2590</v>
+        <v>12360</v>
       </c>
       <c r="F134" t="str">
         <v>Por peso</v>
@@ -3081,19 +3081,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>743062</v>
+        <v>746364</v>
       </c>
       <c r="B135" t="str">
-        <v>CEBOLLA KG FFVV</v>
+        <v>QUINOA KG FFVV</v>
       </c>
       <c r="C135" t="str">
         <v/>
       </c>
       <c r="D135" t="str">
-        <v>43062</v>
+        <v>46364</v>
       </c>
       <c r="E135" t="str">
-        <v>690</v>
+        <v>9160</v>
       </c>
       <c r="F135" t="str">
         <v>Por peso</v>
@@ -3101,16 +3101,16 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>743654</v>
+        <v>744007</v>
       </c>
       <c r="B136" t="str">
-        <v>DATILES KG FFVV</v>
+        <v>CHIA ENTERA GRANEL ARUNA KG</v>
       </c>
       <c r="C136" t="str">
         <v/>
       </c>
       <c r="D136" t="str">
-        <v>43654</v>
+        <v>44007</v>
       </c>
       <c r="E136" t="str">
         <v>7160</v>
@@ -3121,187 +3121,27 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>744552</v>
+        <v>743437</v>
       </c>
       <c r="B137" t="str">
-        <v>CHIA KG FFVV</v>
+        <v>CLAVO DE OLOR KG FFVV</v>
       </c>
       <c r="C137" t="str">
         <v/>
       </c>
       <c r="D137" t="str">
-        <v>44552</v>
+        <v>43437</v>
       </c>
       <c r="E137" t="str">
-        <v>9960</v>
+        <v>36360</v>
       </c>
       <c r="F137" t="str">
-        <v>Por peso</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>742939</v>
-      </c>
-      <c r="B138" t="str">
-        <v>CEBOLLA LIQUIDACION</v>
-      </c>
-      <c r="C138" t="str">
-        <v/>
-      </c>
-      <c r="D138" t="str">
-        <v>42939</v>
-      </c>
-      <c r="E138" t="str">
-        <v>9990</v>
-      </c>
-      <c r="F138" t="str">
-        <v>Por peso</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>743232</v>
-      </c>
-      <c r="B139" t="str">
-        <v>POMELO LIQUIDACION</v>
-      </c>
-      <c r="C139" t="str">
-        <v/>
-      </c>
-      <c r="D139" t="str">
-        <v>43232</v>
-      </c>
-      <c r="E139" t="str">
-        <v>9990</v>
-      </c>
-      <c r="F139" t="str">
-        <v>Por peso</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>743233</v>
-      </c>
-      <c r="B140" t="str">
-        <v>MANGO LIQUIDACION</v>
-      </c>
-      <c r="C140" t="str">
-        <v/>
-      </c>
-      <c r="D140" t="str">
-        <v>43233</v>
-      </c>
-      <c r="E140" t="str">
-        <v>9990</v>
-      </c>
-      <c r="F140" t="str">
-        <v>Por peso</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>743237</v>
-      </c>
-      <c r="B141" t="str">
-        <v>UVA ROSADA KG</v>
-      </c>
-      <c r="C141" t="str">
-        <v/>
-      </c>
-      <c r="D141" t="str">
-        <v>43237</v>
-      </c>
-      <c r="E141" t="str">
-        <v>1190</v>
-      </c>
-      <c r="F141" t="str">
-        <v>Por peso</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>743038</v>
-      </c>
-      <c r="B142" t="str">
-        <v>CURCUMA MOLIDA KG FFVV</v>
-      </c>
-      <c r="C142" t="str">
-        <v/>
-      </c>
-      <c r="D142" t="str">
-        <v>43038</v>
-      </c>
-      <c r="E142" t="str">
-        <v>12360</v>
-      </c>
-      <c r="F142" t="str">
-        <v>Por peso</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>746364</v>
-      </c>
-      <c r="B143" t="str">
-        <v>QUINOA KG FFVV</v>
-      </c>
-      <c r="C143" t="str">
-        <v/>
-      </c>
-      <c r="D143" t="str">
-        <v>46364</v>
-      </c>
-      <c r="E143" t="str">
-        <v>9160</v>
-      </c>
-      <c r="F143" t="str">
-        <v>Por peso</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>744007</v>
-      </c>
-      <c r="B144" t="str">
-        <v>CHIA ENTERA GRANEL ARUNA KG</v>
-      </c>
-      <c r="C144" t="str">
-        <v/>
-      </c>
-      <c r="D144" t="str">
-        <v>44007</v>
-      </c>
-      <c r="E144" t="str">
-        <v>7160</v>
-      </c>
-      <c r="F144" t="str">
-        <v>Por peso</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>743437</v>
-      </c>
-      <c r="B145" t="str">
-        <v>CLAVO DE OLOR KG FFVV</v>
-      </c>
-      <c r="C145" t="str">
-        <v/>
-      </c>
-      <c r="D145" t="str">
-        <v>43437</v>
-      </c>
-      <c r="E145" t="str">
-        <v>36360</v>
-      </c>
-      <c r="F145" t="str">
         <v>Por peso</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F145"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F137"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/MaestraPLU_FFVV.xlsx
+++ b/MaestraPLU_FFVV.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F138"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>741032</v>
+        <v>742011</v>
       </c>
       <c r="B2" t="str">
-        <v>JENGIBRE KG</v>
+        <v>LIMON KG</v>
       </c>
       <c r="C2" t="str">
         <v/>
       </c>
       <c r="D2" t="str">
-        <v>51032</v>
+        <v>42011</v>
       </c>
       <c r="E2" t="str">
-        <v>3560</v>
+        <v>1000</v>
       </c>
       <c r="F2" t="str">
         <v>Por peso</v>
@@ -441,19 +441,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>745146</v>
+        <v>742041</v>
       </c>
       <c r="B3" t="str">
-        <v>ALMENDRA KG FFVV</v>
+        <v>TOMATE LARGA VIDA KG</v>
       </c>
       <c r="C3" t="str">
         <v/>
       </c>
       <c r="D3" t="str">
-        <v>45146</v>
+        <v>42041</v>
       </c>
       <c r="E3" t="str">
-        <v>16760</v>
+        <v>1190</v>
       </c>
       <c r="F3" t="str">
         <v>Por peso</v>
@@ -461,19 +461,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>744023</v>
+        <v>742033</v>
       </c>
       <c r="B4" t="str">
-        <v>CHUCHOCA MOLIDA KG FFVV</v>
+        <v>CIRUELA KG</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
       <c r="D4" t="str">
-        <v>44023</v>
+        <v>42033</v>
       </c>
       <c r="E4" t="str">
-        <v>1960</v>
+        <v>500</v>
       </c>
       <c r="F4" t="str">
         <v>Por peso</v>
@@ -481,19 +481,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>743024</v>
+        <v>742010</v>
       </c>
       <c r="B5" t="str">
-        <v>PASAS MORENAS KG FFVV</v>
+        <v>KIWI KG</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5" t="str">
-        <v>43024</v>
+        <v>42010</v>
       </c>
       <c r="E5" t="str">
-        <v>5160</v>
+        <v>990</v>
       </c>
       <c r="F5" t="str">
         <v>Por peso</v>
@@ -501,19 +501,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>744019</v>
+        <v>741042</v>
       </c>
       <c r="B6" t="str">
-        <v>PASAS RUBIA KG FFVV</v>
+        <v>ZANAHORIA KG</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
       <c r="D6" t="str">
-        <v>44019</v>
+        <v>41042</v>
       </c>
       <c r="E6" t="str">
-        <v>9960</v>
+        <v>500</v>
       </c>
       <c r="F6" t="str">
         <v>Por peso</v>
@@ -521,19 +521,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>744160</v>
+        <v>741032</v>
       </c>
       <c r="B7" t="str">
-        <v>YUCA KG FFVV</v>
+        <v>JENGIBRE KG</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7" t="str">
-        <v>44160</v>
+        <v>51032</v>
       </c>
       <c r="E7" t="str">
-        <v>3490</v>
+        <v>3560</v>
       </c>
       <c r="F7" t="str">
         <v>Por peso</v>
@@ -541,19 +541,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>744153</v>
+        <v>745146</v>
       </c>
       <c r="B8" t="str">
-        <v>TUNAS LIQUIDACION KG</v>
+        <v>ALMENDRA KG FFVV</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>44153</v>
+        <v>45146</v>
       </c>
       <c r="E8" t="str">
-        <v>9990</v>
+        <v>16760</v>
       </c>
       <c r="F8" t="str">
         <v>Por peso</v>
@@ -561,19 +561,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>744146</v>
+        <v>744023</v>
       </c>
       <c r="B9" t="str">
-        <v>FLOR DE JAMAICA KG FFVV</v>
+        <v>CHUCHOCA MOLIDA KG FFVV</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9" t="str">
-        <v>44146</v>
+        <v>44023</v>
       </c>
       <c r="E9" t="str">
-        <v>27960</v>
+        <v>1960</v>
       </c>
       <c r="F9" t="str">
         <v>Por peso</v>
@@ -581,19 +581,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>745147</v>
+        <v>743024</v>
       </c>
       <c r="B10" t="str">
-        <v>HUESILLOS KG FFVV</v>
+        <v>PASAS MORENAS KG FFVV</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>45147</v>
+        <v>43024</v>
       </c>
       <c r="E10" t="str">
-        <v>9560</v>
+        <v>5160</v>
       </c>
       <c r="F10" t="str">
         <v>Por peso</v>
@@ -601,19 +601,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>742072</v>
+        <v>744019</v>
       </c>
       <c r="B11" t="str">
-        <v>SANDIA PRIMERA PP KG</v>
+        <v>PASAS RUBIA KG FFVV</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>42072</v>
+        <v>44019</v>
       </c>
       <c r="E11" t="str">
-        <v>490</v>
+        <v>9960</v>
       </c>
       <c r="F11" t="str">
         <v>Por peso</v>
@@ -621,19 +621,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>742031</v>
+        <v>744160</v>
       </c>
       <c r="B12" t="str">
-        <v>PLATANO KG</v>
+        <v>YUCA KG FFVV</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12" t="str">
-        <v>42031</v>
+        <v>44160</v>
       </c>
       <c r="E12" t="str">
-        <v>1690</v>
+        <v>3490</v>
       </c>
       <c r="F12" t="str">
         <v>Por peso</v>
@@ -641,19 +641,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>742025</v>
+        <v>744153</v>
       </c>
       <c r="B13" t="str">
-        <v>POMELO KG</v>
+        <v>TUNAS LIQUIDACION KG</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13" t="str">
-        <v>42025</v>
+        <v>44153</v>
       </c>
       <c r="E13" t="str">
-        <v>890</v>
+        <v>9990</v>
       </c>
       <c r="F13" t="str">
         <v>Por peso</v>
@@ -661,19 +661,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>742045</v>
+        <v>744146</v>
       </c>
       <c r="B14" t="str">
-        <v>PERA PACKHAM KG</v>
+        <v>FLOR DE JAMAICA KG FFVV</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>42045</v>
+        <v>44146</v>
       </c>
       <c r="E14" t="str">
-        <v>890</v>
+        <v>27960</v>
       </c>
       <c r="F14" t="str">
         <v>Por peso</v>
@@ -681,19 +681,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>742024</v>
+        <v>745147</v>
       </c>
       <c r="B15" t="str">
-        <v>PERA WINTERNELLY KG</v>
+        <v>HUESILLOS KG FFVV</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>42024</v>
+        <v>45147</v>
       </c>
       <c r="E15" t="str">
-        <v>890</v>
+        <v>9560</v>
       </c>
       <c r="F15" t="str">
         <v>Por peso</v>
@@ -701,19 +701,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>742082</v>
+        <v>742072</v>
       </c>
       <c r="B16" t="str">
-        <v>PERA BERRY BOSC</v>
+        <v>SANDIA PRIMERA PP KG</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>42082</v>
+        <v>42072</v>
       </c>
       <c r="E16" t="str">
-        <v>890</v>
+        <v>490</v>
       </c>
       <c r="F16" t="str">
         <v>Por peso</v>
@@ -721,19 +721,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>742081</v>
+        <v>742031</v>
       </c>
       <c r="B17" t="str">
-        <v>PERA ASIATICA KG</v>
+        <v>PLATANO KG</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>42081</v>
+        <v>42031</v>
       </c>
       <c r="E17" t="str">
-        <v>990</v>
+        <v>1690</v>
       </c>
       <c r="F17" t="str">
         <v>Por peso</v>
@@ -741,19 +741,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>742026</v>
+        <v>742025</v>
       </c>
       <c r="B18" t="str">
-        <v>PEPINO FRUTA KG</v>
+        <v>POMELO KG</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>42026</v>
+        <v>42025</v>
       </c>
       <c r="E18" t="str">
-        <v>1790</v>
+        <v>890</v>
       </c>
       <c r="F18" t="str">
         <v>Por peso</v>
@@ -761,19 +761,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>742022</v>
+        <v>742045</v>
       </c>
       <c r="B19" t="str">
-        <v>NUECES KG FFVV</v>
+        <v>PERA PACKHAM KG</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>42022</v>
+        <v>42045</v>
       </c>
       <c r="E19" t="str">
-        <v>14760</v>
+        <v>890</v>
       </c>
       <c r="F19" t="str">
         <v>Por peso</v>
@@ -781,19 +781,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>742044</v>
+        <v>742024</v>
       </c>
       <c r="B20" t="str">
-        <v>MEMBRILLO KG</v>
+        <v>PERA WINTERNELLY KG</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>42044</v>
+        <v>42024</v>
       </c>
       <c r="E20" t="str">
-        <v>990</v>
+        <v>890</v>
       </c>
       <c r="F20" t="str">
         <v>Por peso</v>
@@ -801,19 +801,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>742015</v>
+        <v>742082</v>
       </c>
       <c r="B21" t="str">
-        <v>MANZANA VERDE KG</v>
+        <v>PERA BERRY BOSC</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>42015</v>
+        <v>42082</v>
       </c>
       <c r="E21" t="str">
-        <v>990</v>
+        <v>890</v>
       </c>
       <c r="F21" t="str">
         <v>Por peso</v>
@@ -821,16 +821,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>742013</v>
+        <v>742081</v>
       </c>
       <c r="B22" t="str">
-        <v>MANZANA ROJA KG</v>
+        <v>PERA ASIATICA KG</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>42013</v>
+        <v>42081</v>
       </c>
       <c r="E22" t="str">
         <v>990</v>
@@ -841,19 +841,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>742066</v>
+        <v>742026</v>
       </c>
       <c r="B23" t="str">
-        <v>MANZANA ROYAL GALA KG</v>
+        <v>PEPINO FRUTA KG</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>42066</v>
+        <v>42026</v>
       </c>
       <c r="E23" t="str">
-        <v>990</v>
+        <v>1790</v>
       </c>
       <c r="F23" t="str">
         <v>Por peso</v>
@@ -861,19 +861,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>742067</v>
+        <v>742022</v>
       </c>
       <c r="B24" t="str">
-        <v>MANZANA FUJI KG</v>
+        <v>NUECES KG FFVV</v>
       </c>
       <c r="C24" t="str">
         <v/>
       </c>
       <c r="D24" t="str">
-        <v>42067</v>
+        <v>42022</v>
       </c>
       <c r="E24" t="str">
-        <v>990</v>
+        <v>14760</v>
       </c>
       <c r="F24" t="str">
         <v>Por peso</v>
@@ -881,19 +881,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>742102</v>
+        <v>742044</v>
       </c>
       <c r="B25" t="str">
-        <v>MANGOS KG</v>
+        <v>MEMBRILLO KG</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>42102</v>
+        <v>42044</v>
       </c>
       <c r="E25" t="str">
-        <v>2890</v>
+        <v>990</v>
       </c>
       <c r="F25" t="str">
         <v>Por peso</v>
@@ -901,19 +901,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>742011</v>
+        <v>742015</v>
       </c>
       <c r="B26" t="str">
-        <v>LIMON KG</v>
+        <v>MANZANA VERDE KG</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
       <c r="D26" t="str">
-        <v>42011</v>
+        <v>42015</v>
       </c>
       <c r="E26" t="str">
-        <v>1290</v>
+        <v>990</v>
       </c>
       <c r="F26" t="str">
         <v>Por peso</v>
@@ -921,19 +921,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>742010</v>
+        <v>742013</v>
       </c>
       <c r="B27" t="str">
-        <v>KIWI KG</v>
+        <v>MANZANA ROJA KG</v>
       </c>
       <c r="C27" t="str">
         <v/>
       </c>
       <c r="D27" t="str">
-        <v>42010</v>
+        <v>42013</v>
       </c>
       <c r="E27" t="str">
-        <v>1190</v>
+        <v>990</v>
       </c>
       <c r="F27" t="str">
         <v>Por peso</v>
@@ -941,19 +941,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>742051</v>
+        <v>742066</v>
       </c>
       <c r="B28" t="str">
-        <v>GRANADAS KG</v>
+        <v>MANZANA ROYAL GALA KG</v>
       </c>
       <c r="C28" t="str">
         <v/>
       </c>
       <c r="D28" t="str">
-        <v>42051</v>
+        <v>42066</v>
       </c>
       <c r="E28" t="str">
-        <v>1990</v>
+        <v>990</v>
       </c>
       <c r="F28" t="str">
         <v>Por peso</v>
@@ -961,19 +961,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>742033</v>
+        <v>742067</v>
       </c>
       <c r="B29" t="str">
-        <v>CIRUELA KG</v>
+        <v>MANZANA FUJI KG</v>
       </c>
       <c r="C29" t="str">
         <v/>
       </c>
       <c r="D29" t="str">
-        <v>42033</v>
+        <v>42067</v>
       </c>
       <c r="E29" t="str">
-        <v>690</v>
+        <v>990</v>
       </c>
       <c r="F29" t="str">
         <v>Por peso</v>
@@ -981,19 +981,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>742042</v>
+        <v>742102</v>
       </c>
       <c r="B30" t="str">
-        <v>UVA NEGRA KG</v>
+        <v>MANGOS KG</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30" t="str">
-        <v>42042</v>
+        <v>42102</v>
       </c>
       <c r="E30" t="str">
-        <v>1190</v>
+        <v>2890</v>
       </c>
       <c r="F30" t="str">
         <v>Por peso</v>
@@ -1001,19 +1001,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>742041</v>
+        <v>742051</v>
       </c>
       <c r="B31" t="str">
-        <v>TOMATE LARGA VIDA KG</v>
+        <v>GRANADAS KG</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>42041</v>
+        <v>42051</v>
       </c>
       <c r="E31" t="str">
-        <v>1490</v>
+        <v>1990</v>
       </c>
       <c r="F31" t="str">
         <v>Por peso</v>
@@ -1021,19 +1021,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>742166</v>
+        <v>742042</v>
       </c>
       <c r="B32" t="str">
-        <v>CACAO AMARGO KG FFVV</v>
+        <v>UVA NEGRA KG</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>42166</v>
+        <v>42042</v>
       </c>
       <c r="E32" t="str">
-        <v>14760</v>
+        <v>1190</v>
       </c>
       <c r="F32" t="str">
         <v>Por peso</v>
@@ -1041,19 +1041,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>742135</v>
+        <v>742006</v>
       </c>
       <c r="B33" t="str">
-        <v>SANDIA EXTRA PP KG</v>
+        <v>CEREZAS KILO</v>
       </c>
       <c r="C33" t="str">
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>42135</v>
+        <v>42006</v>
       </c>
       <c r="E33" t="str">
-        <v>490</v>
+        <v>1290</v>
       </c>
       <c r="F33" t="str">
         <v>Por peso</v>
@@ -1061,19 +1061,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>741835</v>
+        <v>742166</v>
       </c>
       <c r="B34" t="str">
-        <v>ANIS ESTRELLA KG FFVV</v>
+        <v>CACAO AMARGO KG FFVV</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>41835</v>
+        <v>42166</v>
       </c>
       <c r="E34" t="str">
-        <v>27160</v>
+        <v>14760</v>
       </c>
       <c r="F34" t="str">
         <v>Por peso</v>
@@ -1081,19 +1081,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>741828</v>
+        <v>742135</v>
       </c>
       <c r="B35" t="str">
-        <v>PEPINO FRUTA LIQUIDACION</v>
+        <v>SANDIA EXTRA PP KG</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>41828</v>
+        <v>42135</v>
       </c>
       <c r="E35" t="str">
-        <v>9990</v>
+        <v>490</v>
       </c>
       <c r="F35" t="str">
         <v>Por peso</v>
@@ -1101,19 +1101,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>741826</v>
+        <v>741835</v>
       </c>
       <c r="B36" t="str">
-        <v>TOMATE CHERRY KG FFVV</v>
+        <v>ANIS ESTRELLA KG FFVV</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>41826</v>
+        <v>41835</v>
       </c>
       <c r="E36" t="str">
-        <v>4760</v>
+        <v>27160</v>
       </c>
       <c r="F36" t="str">
         <v>Por peso</v>
@@ -1121,19 +1121,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>741820</v>
+        <v>741828</v>
       </c>
       <c r="B37" t="str">
-        <v>MERKEN KG FFVV</v>
+        <v>PEPINO FRUTA LIQUIDACION</v>
       </c>
       <c r="C37" t="str">
         <v/>
       </c>
       <c r="D37" t="str">
-        <v>41820</v>
+        <v>41828</v>
       </c>
       <c r="E37" t="str">
-        <v>12360</v>
+        <v>9990</v>
       </c>
       <c r="F37" t="str">
         <v>Por peso</v>
@@ -1141,19 +1141,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>745142</v>
+        <v>741826</v>
       </c>
       <c r="B38" t="str">
-        <v>CEBOLLA MORADA KG</v>
+        <v>TOMATE CHERRY KG FFVV</v>
       </c>
       <c r="C38" t="str">
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>45142</v>
+        <v>41826</v>
       </c>
       <c r="E38" t="str">
-        <v>790</v>
+        <v>4760</v>
       </c>
       <c r="F38" t="str">
         <v>Por peso</v>
@@ -1161,19 +1161,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>742075</v>
+        <v>741820</v>
       </c>
       <c r="B39" t="str">
-        <v>PERA FORELLE KG</v>
+        <v>MERKEN KG FFVV</v>
       </c>
       <c r="C39" t="str">
         <v/>
       </c>
       <c r="D39" t="str">
-        <v>42075</v>
+        <v>41820</v>
       </c>
       <c r="E39" t="str">
-        <v>890</v>
+        <v>12360</v>
       </c>
       <c r="F39" t="str">
         <v>Por peso</v>
@@ -1181,19 +1181,19 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>742118</v>
+        <v>745142</v>
       </c>
       <c r="B40" t="str">
-        <v>CLEMENTINA MANDARINA KG</v>
+        <v>CEBOLLA MORADA KG</v>
       </c>
       <c r="C40" t="str">
         <v/>
       </c>
       <c r="D40" t="str">
-        <v>42118</v>
+        <v>45142</v>
       </c>
       <c r="E40" t="str">
-        <v>1490</v>
+        <v>790</v>
       </c>
       <c r="F40" t="str">
         <v>Por peso</v>
@@ -1201,19 +1201,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>742016</v>
+        <v>742075</v>
       </c>
       <c r="B41" t="str">
-        <v>CASTANAS KILO FFVV</v>
+        <v>PERA FORELLE KG</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
       <c r="D41" t="str">
-        <v>42016</v>
+        <v>42075</v>
       </c>
       <c r="E41" t="str">
-        <v>1990</v>
+        <v>890</v>
       </c>
       <c r="F41" t="str">
         <v>Por peso</v>
@@ -1221,19 +1221,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>742001</v>
+        <v>742118</v>
       </c>
       <c r="B42" t="str">
-        <v>FRUTA CONFITADA KG FFVV</v>
+        <v>CLEMENTINA MANDARINA KG</v>
       </c>
       <c r="C42" t="str">
         <v/>
       </c>
       <c r="D42" t="str">
-        <v>42001</v>
+        <v>42118</v>
       </c>
       <c r="E42" t="str">
-        <v>5560</v>
+        <v>1490</v>
       </c>
       <c r="F42" t="str">
         <v>Por peso</v>
@@ -1241,19 +1241,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>742158</v>
+        <v>742016</v>
       </c>
       <c r="B43" t="str">
-        <v>MANZANA CRISS PINK KG</v>
+        <v>CASTANAS KILO FFVV</v>
       </c>
       <c r="C43" t="str">
         <v/>
       </c>
       <c r="D43" t="str">
-        <v>42158</v>
+        <v>42016</v>
       </c>
       <c r="E43" t="str">
-        <v>990</v>
+        <v>1990</v>
       </c>
       <c r="F43" t="str">
         <v>Por peso</v>
@@ -1261,19 +1261,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>741064</v>
+        <v>742001</v>
       </c>
       <c r="B44" t="str">
-        <v>ZAPALLO JAMBOREE SAMPSON PP KG</v>
+        <v>FRUTA CONFITADA KG FFVV</v>
       </c>
       <c r="C44" t="str">
         <v/>
       </c>
       <c r="D44" t="str">
-        <v>41064</v>
+        <v>42001</v>
       </c>
       <c r="E44" t="str">
-        <v>790</v>
+        <v>5560</v>
       </c>
       <c r="F44" t="str">
         <v>Por peso</v>
@@ -1281,19 +1281,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>741039</v>
+        <v>742158</v>
       </c>
       <c r="B45" t="str">
-        <v>ZAPALLO CAMOTE KG</v>
+        <v>MANZANA CRISS PINK KG</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45" t="str">
-        <v>41039</v>
+        <v>42158</v>
       </c>
       <c r="E45" t="str">
-        <v>790</v>
+        <v>990</v>
       </c>
       <c r="F45" t="str">
         <v>Por peso</v>
@@ -1301,19 +1301,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>741025</v>
+        <v>741064</v>
       </c>
       <c r="B46" t="str">
-        <v>POROTO VERDE KG</v>
+        <v>ZAPALLO JAMBOREE SAMPSON PP KG</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46" t="str">
-        <v>41025</v>
+        <v>41064</v>
       </c>
       <c r="E46" t="str">
-        <v>2290</v>
+        <v>790</v>
       </c>
       <c r="F46" t="str">
         <v>Por peso</v>
@@ -1321,19 +1321,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>741026</v>
+        <v>741039</v>
       </c>
       <c r="B47" t="str">
-        <v>POROTO GRANADO KG</v>
+        <v>ZAPALLO CAMOTE KG</v>
       </c>
       <c r="C47" t="str">
         <v/>
       </c>
       <c r="D47" t="str">
-        <v>41026</v>
+        <v>41039</v>
       </c>
       <c r="E47" t="str">
-        <v>2290</v>
+        <v>790</v>
       </c>
       <c r="F47" t="str">
         <v>Por peso</v>
@@ -1341,19 +1341,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>741051</v>
+        <v>741025</v>
       </c>
       <c r="B48" t="str">
-        <v>PAPA LAVADA KG</v>
+        <v>POROTO VERDE KG</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>41051</v>
+        <v>41025</v>
       </c>
       <c r="E48" t="str">
-        <v>890</v>
+        <v>2290</v>
       </c>
       <c r="F48" t="str">
         <v>Por peso</v>
@@ -1361,19 +1361,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>741002</v>
+        <v>741026</v>
       </c>
       <c r="B49" t="str">
-        <v>AJI LIQUIDACION</v>
+        <v>POROTO GRANADO KG</v>
       </c>
       <c r="C49" t="str">
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>41002</v>
+        <v>41026</v>
       </c>
       <c r="E49" t="str">
-        <v>9990</v>
+        <v>2290</v>
       </c>
       <c r="F49" t="str">
         <v>Por peso</v>
@@ -1381,19 +1381,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>741021</v>
+        <v>741051</v>
       </c>
       <c r="B50" t="str">
-        <v>MOTE KG</v>
+        <v>PAPA LAVADA KG</v>
       </c>
       <c r="C50" t="str">
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>41021</v>
+        <v>41051</v>
       </c>
       <c r="E50" t="str">
-        <v>1290</v>
+        <v>890</v>
       </c>
       <c r="F50" t="str">
         <v>Por peso</v>
@@ -1401,19 +1401,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>741014</v>
+        <v>741002</v>
       </c>
       <c r="B51" t="str">
-        <v>HABAS KG</v>
+        <v>AJI LIQUIDACION</v>
       </c>
       <c r="C51" t="str">
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>41014</v>
+        <v>41002</v>
       </c>
       <c r="E51" t="str">
-        <v>990</v>
+        <v>9990</v>
       </c>
       <c r="F51" t="str">
         <v>Por peso</v>
@@ -1421,19 +1421,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>741046</v>
+        <v>741021</v>
       </c>
       <c r="B52" t="str">
-        <v>AJI CACHO CABRA SECO KG</v>
+        <v>MOTE KG</v>
       </c>
       <c r="C52" t="str">
         <v/>
       </c>
       <c r="D52" t="str">
-        <v>41046</v>
+        <v>41021</v>
       </c>
       <c r="E52" t="str">
-        <v>13160</v>
+        <v>1290</v>
       </c>
       <c r="F52" t="str">
         <v>Por peso</v>
@@ -1441,19 +1441,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>741079</v>
+        <v>741014</v>
       </c>
       <c r="B53" t="str">
-        <v>CEBOLLA BLANCA CRISTAL KG</v>
+        <v>HABAS KG</v>
       </c>
       <c r="C53" t="str">
         <v/>
       </c>
       <c r="D53" t="str">
-        <v>41079</v>
+        <v>41014</v>
       </c>
       <c r="E53" t="str">
-        <v>790</v>
+        <v>990</v>
       </c>
       <c r="F53" t="str">
         <v>Por peso</v>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>741080</v>
+        <v>741046</v>
       </c>
       <c r="B54" t="str">
-        <v>CEBOLLA CUGAT PP KG</v>
+        <v>AJI CACHO CABRA SECO KG</v>
       </c>
       <c r="C54" t="str">
         <v/>
       </c>
       <c r="D54" t="str">
-        <v>41080</v>
+        <v>41046</v>
       </c>
       <c r="E54" t="str">
-        <v>690</v>
+        <v>13160</v>
       </c>
       <c r="F54" t="str">
         <v>Por peso</v>
@@ -1481,19 +1481,19 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>741055</v>
+        <v>741079</v>
       </c>
       <c r="B55" t="str">
-        <v>BRUSELAS KG</v>
+        <v>CEBOLLA BLANCA CRISTAL KG</v>
       </c>
       <c r="C55" t="str">
         <v/>
       </c>
       <c r="D55" t="str">
-        <v>41055</v>
+        <v>41079</v>
       </c>
       <c r="E55" t="str">
-        <v>2590</v>
+        <v>790</v>
       </c>
       <c r="F55" t="str">
         <v>Por peso</v>
@@ -1501,16 +1501,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>741129</v>
+        <v>741080</v>
       </c>
       <c r="B56" t="str">
-        <v>PAPA SURENA KILO</v>
+        <v>CEBOLLA CUGAT PP KG</v>
       </c>
       <c r="C56" t="str">
         <v/>
       </c>
       <c r="D56" t="str">
-        <v>41129</v>
+        <v>41080</v>
       </c>
       <c r="E56" t="str">
         <v>690</v>
@@ -1521,19 +1521,19 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>741042</v>
+        <v>741055</v>
       </c>
       <c r="B57" t="str">
-        <v>ZANAHORIA KG</v>
+        <v>BRUSELAS KG</v>
       </c>
       <c r="C57" t="str">
         <v/>
       </c>
       <c r="D57" t="str">
-        <v>41042</v>
+        <v>41055</v>
       </c>
       <c r="E57" t="str">
-        <v>690</v>
+        <v>2590</v>
       </c>
       <c r="F57" t="str">
         <v>Por peso</v>
@@ -1541,19 +1541,19 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>741420</v>
+        <v>741129</v>
       </c>
       <c r="B58" t="str">
-        <v>PAPA CAMOTE KG</v>
+        <v>PAPA SURENA KILO</v>
       </c>
       <c r="C58" t="str">
         <v/>
       </c>
       <c r="D58" t="str">
-        <v>41420</v>
+        <v>41129</v>
       </c>
       <c r="E58" t="str">
-        <v>1990</v>
+        <v>690</v>
       </c>
       <c r="F58" t="str">
         <v>Por peso</v>
@@ -1561,19 +1561,19 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>741030</v>
+        <v>741420</v>
       </c>
       <c r="B59" t="str">
-        <v>PAPA KG</v>
+        <v>PAPA CAMOTE KG</v>
       </c>
       <c r="C59" t="str">
         <v/>
       </c>
       <c r="D59" t="str">
-        <v>41030</v>
+        <v>41420</v>
       </c>
       <c r="E59" t="str">
-        <v>790</v>
+        <v>1990</v>
       </c>
       <c r="F59" t="str">
         <v>Por peso</v>
@@ -1581,19 +1581,19 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>741107</v>
+        <v>741030</v>
       </c>
       <c r="B60" t="str">
-        <v>CRANBERRY KG FFVV</v>
+        <v>PAPA KG</v>
       </c>
       <c r="C60" t="str">
         <v/>
       </c>
       <c r="D60" t="str">
-        <v>41107</v>
+        <v>41030</v>
       </c>
       <c r="E60" t="str">
-        <v>12360</v>
+        <v>790</v>
       </c>
       <c r="F60" t="str">
         <v>Por peso</v>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>741180</v>
+        <v>741107</v>
       </c>
       <c r="B61" t="str">
-        <v>PAPA BLANCA KG</v>
+        <v>CRANBERRY KG FFVV</v>
       </c>
       <c r="C61" t="str">
         <v/>
       </c>
       <c r="D61" t="str">
-        <v>41180</v>
+        <v>41107</v>
       </c>
       <c r="E61" t="str">
-        <v>1190</v>
+        <v>12360</v>
       </c>
       <c r="F61" t="str">
         <v>Por peso</v>
@@ -1621,19 +1621,19 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>741043</v>
+        <v>741180</v>
       </c>
       <c r="B62" t="str">
-        <v>SESAMO BLANCO KILO FFVV</v>
+        <v>PAPA BLANCA KG</v>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
       <c r="D62" t="str">
-        <v>41043</v>
+        <v>41180</v>
       </c>
       <c r="E62" t="str">
-        <v>9960</v>
+        <v>1190</v>
       </c>
       <c r="F62" t="str">
         <v>Por peso</v>
@@ -1641,19 +1641,19 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>742121</v>
+        <v>741043</v>
       </c>
       <c r="B63" t="str">
-        <v>LIMON SUTIL KG</v>
+        <v>SESAMO BLANCO KILO FFVV</v>
       </c>
       <c r="C63" t="str">
         <v/>
       </c>
       <c r="D63" t="str">
-        <v>42121</v>
+        <v>41043</v>
       </c>
       <c r="E63" t="str">
-        <v>2190</v>
+        <v>9960</v>
       </c>
       <c r="F63" t="str">
         <v>Por peso</v>
@@ -1661,19 +1661,19 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>742064</v>
+        <v>742121</v>
       </c>
       <c r="B64" t="str">
-        <v>AJO CHILOTE KG</v>
+        <v>LIMON SUTIL KG</v>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64" t="str">
-        <v>42064</v>
+        <v>42121</v>
       </c>
       <c r="E64" t="str">
-        <v>10760</v>
+        <v>2190</v>
       </c>
       <c r="F64" t="str">
         <v>Por peso</v>
@@ -1681,19 +1681,19 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>741031</v>
+        <v>742064</v>
       </c>
       <c r="B65" t="str">
-        <v>AJI VERDE KG</v>
+        <v>AJO CHILOTE KG</v>
       </c>
       <c r="C65" t="str">
         <v/>
       </c>
       <c r="D65" t="str">
-        <v>41031</v>
+        <v>42064</v>
       </c>
       <c r="E65" t="str">
-        <v>5960</v>
+        <v>10760</v>
       </c>
       <c r="F65" t="str">
         <v>Por peso</v>
@@ -1701,19 +1701,19 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>741211</v>
+        <v>741031</v>
       </c>
       <c r="B66" t="str">
-        <v>UVA RED GLOBE KG</v>
+        <v>AJI VERDE KG</v>
       </c>
       <c r="C66" t="str">
         <v/>
       </c>
       <c r="D66" t="str">
-        <v>41211</v>
+        <v>41031</v>
       </c>
       <c r="E66" t="str">
-        <v>1190</v>
+        <v>5960</v>
       </c>
       <c r="F66" t="str">
         <v>Por peso</v>
@@ -1721,19 +1721,19 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>741111</v>
+        <v>741211</v>
       </c>
       <c r="B67" t="str">
-        <v>CANELA EN POLVO KG FFVV</v>
+        <v>UVA RED GLOBE KG</v>
       </c>
       <c r="C67" t="str">
         <v/>
       </c>
       <c r="D67" t="str">
-        <v>41111</v>
+        <v>41211</v>
       </c>
       <c r="E67" t="str">
-        <v>19160</v>
+        <v>1190</v>
       </c>
       <c r="F67" t="str">
         <v>Por peso</v>
@@ -1741,19 +1741,19 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>741052</v>
+        <v>741111</v>
       </c>
       <c r="B68" t="str">
-        <v>ZAPALLO BUTTERNUT KG</v>
+        <v>CANELA EN POLVO KG FFVV</v>
       </c>
       <c r="C68" t="str">
         <v/>
       </c>
       <c r="D68" t="str">
-        <v>41052</v>
+        <v>41111</v>
       </c>
       <c r="E68" t="str">
-        <v>690</v>
+        <v>19160</v>
       </c>
       <c r="F68" t="str">
         <v>Por peso</v>
@@ -1761,19 +1761,19 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>742090</v>
+        <v>741052</v>
       </c>
       <c r="B69" t="str">
-        <v>NARANJA KG</v>
+        <v>ZAPALLO BUTTERNUT KG</v>
       </c>
       <c r="C69" t="str">
         <v/>
       </c>
       <c r="D69" t="str">
-        <v>42090</v>
+        <v>41052</v>
       </c>
       <c r="E69" t="str">
-        <v>1290</v>
+        <v>690</v>
       </c>
       <c r="F69" t="str">
         <v>Por peso</v>
@@ -1781,19 +1781,19 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>742095</v>
+        <v>742090</v>
       </c>
       <c r="B70" t="str">
-        <v>MARAVILLA PELADA KG FFVV</v>
+        <v>NARANJA KG</v>
       </c>
       <c r="C70" t="str">
         <v/>
       </c>
       <c r="D70" t="str">
-        <v>42095</v>
+        <v>42090</v>
       </c>
       <c r="E70" t="str">
-        <v>5160</v>
+        <v>1290</v>
       </c>
       <c r="F70" t="str">
         <v>Por peso</v>
@@ -1801,19 +1801,19 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>744501</v>
+        <v>742095</v>
       </c>
       <c r="B71" t="str">
-        <v>AJO EN POLVO KG FFYVV</v>
+        <v>MARAVILLA PELADA KG FFVV</v>
       </c>
       <c r="C71" t="str">
         <v/>
       </c>
       <c r="D71" t="str">
-        <v>44501</v>
+        <v>42095</v>
       </c>
       <c r="E71" t="str">
-        <v>8760</v>
+        <v>5160</v>
       </c>
       <c r="F71" t="str">
         <v>Por peso</v>
@@ -1821,19 +1821,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>744502</v>
+        <v>744501</v>
       </c>
       <c r="B72" t="str">
-        <v>ALINO COMPLETO KG FFYVV</v>
+        <v>AJO EN POLVO KG FFYVV</v>
       </c>
       <c r="C72" t="str">
         <v/>
       </c>
       <c r="D72" t="str">
-        <v>44502</v>
+        <v>44501</v>
       </c>
       <c r="E72" t="str">
-        <v>8360</v>
+        <v>8760</v>
       </c>
       <c r="F72" t="str">
         <v>Por peso</v>
@@ -1841,19 +1841,19 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>744503</v>
+        <v>744502</v>
       </c>
       <c r="B73" t="str">
-        <v>BICARBONATO KG FFVV</v>
+        <v>ALINO COMPLETO KG FFYVV</v>
       </c>
       <c r="C73" t="str">
         <v/>
       </c>
       <c r="D73" t="str">
-        <v>44503</v>
+        <v>44502</v>
       </c>
       <c r="E73" t="str">
-        <v>2360</v>
+        <v>8360</v>
       </c>
       <c r="F73" t="str">
         <v>Por peso</v>
@@ -1861,19 +1861,19 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>744504</v>
+        <v>744503</v>
       </c>
       <c r="B74" t="str">
-        <v>COMINO MOLIDO KG FFVV</v>
+        <v>BICARBONATO KG FFVV</v>
       </c>
       <c r="C74" t="str">
         <v/>
       </c>
       <c r="D74" t="str">
-        <v>44504</v>
+        <v>44503</v>
       </c>
       <c r="E74" t="str">
-        <v>21160</v>
+        <v>2360</v>
       </c>
       <c r="F74" t="str">
         <v>Por peso</v>
@@ -1881,19 +1881,19 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>744505</v>
+        <v>744504</v>
       </c>
       <c r="B75" t="str">
-        <v>MAIZ CURAGUA KG FFVV</v>
+        <v>COMINO MOLIDO KG FFVV</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75" t="str">
-        <v>44505</v>
+        <v>44504</v>
       </c>
       <c r="E75" t="str">
-        <v>3160</v>
+        <v>21160</v>
       </c>
       <c r="F75" t="str">
         <v>Por peso</v>
@@ -1901,19 +1901,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>744589</v>
+        <v>744505</v>
       </c>
       <c r="B76" t="str">
-        <v>PALTA HASS KG</v>
+        <v>MAIZ CURAGUA KG FFVV</v>
       </c>
       <c r="C76" t="str">
         <v/>
       </c>
       <c r="D76" t="str">
-        <v>44589</v>
+        <v>44505</v>
       </c>
       <c r="E76" t="str">
-        <v>5690</v>
+        <v>3160</v>
       </c>
       <c r="F76" t="str">
         <v>Por peso</v>
@@ -1921,19 +1921,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>742038</v>
+        <v>744589</v>
       </c>
       <c r="B77" t="str">
-        <v>UVA VERDE KG</v>
+        <v>PALTA HASS KG</v>
       </c>
       <c r="C77" t="str">
         <v/>
       </c>
       <c r="D77" t="str">
-        <v>42038</v>
+        <v>44589</v>
       </c>
       <c r="E77" t="str">
-        <v>1590</v>
+        <v>5690</v>
       </c>
       <c r="F77" t="str">
         <v>Por peso</v>
@@ -1941,19 +1941,19 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>749205</v>
+        <v>742038</v>
       </c>
       <c r="B78" t="str">
-        <v>VASO MELON TROZOS FFVV</v>
+        <v>UVA VERDE KG</v>
       </c>
       <c r="C78" t="str">
         <v/>
       </c>
       <c r="D78" t="str">
-        <v>29205</v>
+        <v>42038</v>
       </c>
       <c r="E78" t="str">
-        <v>790</v>
+        <v>1590</v>
       </c>
       <c r="F78" t="str">
         <v>Por peso</v>
@@ -1961,19 +1961,19 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>741112</v>
+        <v>749205</v>
       </c>
       <c r="B79" t="str">
-        <v>COMINO ENTERO KG FFVV</v>
+        <v>VASO MELON TROZOS FFVV</v>
       </c>
       <c r="C79" t="str">
         <v/>
       </c>
       <c r="D79" t="str">
-        <v>41112</v>
+        <v>29205</v>
       </c>
       <c r="E79" t="str">
-        <v>19160</v>
+        <v>790</v>
       </c>
       <c r="F79" t="str">
         <v>Por peso</v>
@@ -1981,19 +1981,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>744509</v>
+        <v>741112</v>
       </c>
       <c r="B80" t="str">
-        <v>PIMIENTA NEGRA MOLIDA KG FFVV</v>
+        <v>COMINO ENTERO KG FFVV</v>
       </c>
       <c r="C80" t="str">
         <v/>
       </c>
       <c r="D80" t="str">
-        <v>44509</v>
+        <v>41112</v>
       </c>
       <c r="E80" t="str">
-        <v>27160</v>
+        <v>19160</v>
       </c>
       <c r="F80" t="str">
         <v>Por peso</v>
@@ -2001,19 +2001,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>744510</v>
+        <v>744509</v>
       </c>
       <c r="B81" t="str">
-        <v>LINAZA MOLIDA KG FFVV</v>
+        <v>PIMIENTA NEGRA MOLIDA KG FFVV</v>
       </c>
       <c r="C81" t="str">
         <v/>
       </c>
       <c r="D81" t="str">
-        <v>44510</v>
+        <v>44509</v>
       </c>
       <c r="E81" t="str">
-        <v>5960</v>
+        <v>27160</v>
       </c>
       <c r="F81" t="str">
         <v>Por peso</v>
@@ -2021,19 +2021,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>744511</v>
+        <v>744510</v>
       </c>
       <c r="B82" t="str">
-        <v>LINAZA ENTERA KG FFVV</v>
+        <v>LINAZA MOLIDA KG FFVV</v>
       </c>
       <c r="C82" t="str">
         <v/>
       </c>
       <c r="D82" t="str">
-        <v>44511</v>
+        <v>44510</v>
       </c>
       <c r="E82" t="str">
-        <v>5160</v>
+        <v>5960</v>
       </c>
       <c r="F82" t="str">
         <v>Por peso</v>
@@ -2041,19 +2041,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>741401</v>
+        <v>744511</v>
       </c>
       <c r="B83" t="str">
-        <v>AJI CACHO CABRA AHUMADO KG</v>
+        <v>LINAZA ENTERA KG FFVV</v>
       </c>
       <c r="C83" t="str">
         <v/>
       </c>
       <c r="D83" t="str">
-        <v>41401</v>
+        <v>44511</v>
       </c>
       <c r="E83" t="str">
-        <v>13160</v>
+        <v>5160</v>
       </c>
       <c r="F83" t="str">
         <v>Por peso</v>
@@ -2061,19 +2061,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>741011</v>
+        <v>741401</v>
       </c>
       <c r="B84" t="str">
-        <v>CURCUMA KG</v>
+        <v>AJI CACHO CABRA AHUMADO KG</v>
       </c>
       <c r="C84" t="str">
         <v/>
       </c>
       <c r="D84" t="str">
-        <v>41011</v>
+        <v>41401</v>
       </c>
       <c r="E84" t="str">
-        <v>2990</v>
+        <v>13160</v>
       </c>
       <c r="F84" t="str">
         <v>Por peso</v>
@@ -2081,19 +2081,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>744140</v>
+        <v>741011</v>
       </c>
       <c r="B85" t="str">
-        <v>CLAVO DE OLOR MOLIDO KG FFVV</v>
+        <v>CURCUMA KG</v>
       </c>
       <c r="C85" t="str">
         <v/>
       </c>
       <c r="D85" t="str">
-        <v>44140</v>
+        <v>41011</v>
       </c>
       <c r="E85" t="str">
-        <v>18760</v>
+        <v>2990</v>
       </c>
       <c r="F85" t="str">
         <v>Por peso</v>
@@ -2101,19 +2101,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>741083</v>
+        <v>744140</v>
       </c>
       <c r="B86" t="str">
-        <v>SEMILLA DE ZAPALLO KG FFVV</v>
+        <v>CLAVO DE OLOR MOLIDO KG FFVV</v>
       </c>
       <c r="C86" t="str">
         <v/>
       </c>
       <c r="D86" t="str">
-        <v>41083</v>
+        <v>44140</v>
       </c>
       <c r="E86" t="str">
-        <v>14760</v>
+        <v>18760</v>
       </c>
       <c r="F86" t="str">
         <v>Por peso</v>
@@ -2121,19 +2121,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>742511</v>
+        <v>741083</v>
       </c>
       <c r="B87" t="str">
-        <v>KIWI LIQUIDACION</v>
+        <v>SEMILLA DE ZAPALLO KG FFVV</v>
       </c>
       <c r="C87" t="str">
         <v/>
       </c>
       <c r="D87" t="str">
-        <v>42511</v>
+        <v>41083</v>
       </c>
       <c r="E87" t="str">
-        <v>9990</v>
+        <v>14760</v>
       </c>
       <c r="F87" t="str">
         <v>Por peso</v>
@@ -2141,19 +2141,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>741519</v>
+        <v>742511</v>
       </c>
       <c r="B88" t="str">
-        <v>PLATANO BARRAGANETE VERDE KG</v>
+        <v>KIWI LIQUIDACION</v>
       </c>
       <c r="C88" t="str">
         <v/>
       </c>
       <c r="D88" t="str">
-        <v>41519</v>
+        <v>42511</v>
       </c>
       <c r="E88" t="str">
-        <v>1990</v>
+        <v>9990</v>
       </c>
       <c r="F88" t="str">
         <v>Por peso</v>
@@ -2161,19 +2161,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>744521</v>
+        <v>741519</v>
       </c>
       <c r="B89" t="str">
-        <v>CACAO AZUCARADO KG FFYVV</v>
+        <v>PLATANO BARRAGANETE VERDE KG</v>
       </c>
       <c r="C89" t="str">
         <v/>
       </c>
       <c r="D89" t="str">
-        <v>44521</v>
+        <v>41519</v>
       </c>
       <c r="E89" t="str">
-        <v>12360</v>
+        <v>1990</v>
       </c>
       <c r="F89" t="str">
         <v>Por peso</v>
@@ -2181,19 +2181,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>744522</v>
+        <v>744521</v>
       </c>
       <c r="B90" t="str">
-        <v>PROTEINA VEGETAL KG FFVV</v>
+        <v>CACAO AZUCARADO KG FFYVV</v>
       </c>
       <c r="C90" t="str">
         <v/>
       </c>
       <c r="D90" t="str">
-        <v>44522</v>
+        <v>44521</v>
       </c>
       <c r="E90" t="str">
-        <v>4760</v>
+        <v>12360</v>
       </c>
       <c r="F90" t="str">
         <v>Por peso</v>
@@ -2201,19 +2201,19 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>744523</v>
+        <v>744522</v>
       </c>
       <c r="B91" t="str">
-        <v>CHUNO KG FFVV</v>
+        <v>PROTEINA VEGETAL KG FFVV</v>
       </c>
       <c r="C91" t="str">
         <v/>
       </c>
       <c r="D91" t="str">
-        <v>44523</v>
+        <v>44522</v>
       </c>
       <c r="E91" t="str">
-        <v>5160</v>
+        <v>4760</v>
       </c>
       <c r="F91" t="str">
         <v>Por peso</v>
@@ -2221,19 +2221,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>744524</v>
+        <v>744523</v>
       </c>
       <c r="B92" t="str">
-        <v>TE CEYLAN HOJA KG FFVV</v>
+        <v>CHUNO KG FFVV</v>
       </c>
       <c r="C92" t="str">
         <v/>
       </c>
       <c r="D92" t="str">
-        <v>44524</v>
+        <v>44523</v>
       </c>
       <c r="E92" t="str">
-        <v>17160</v>
+        <v>5160</v>
       </c>
       <c r="F92" t="str">
         <v>Por peso</v>
@@ -2241,19 +2241,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>744525</v>
+        <v>744524</v>
       </c>
       <c r="B93" t="str">
-        <v>COCO RALLADO KG FFVV</v>
+        <v>TE CEYLAN HOJA KG FFVV</v>
       </c>
       <c r="C93" t="str">
         <v/>
       </c>
       <c r="D93" t="str">
-        <v>44525</v>
+        <v>44524</v>
       </c>
       <c r="E93" t="str">
-        <v>14760</v>
+        <v>17160</v>
       </c>
       <c r="F93" t="str">
         <v>Por peso</v>
@@ -2261,19 +2261,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>744526</v>
+        <v>744525</v>
       </c>
       <c r="B94" t="str">
-        <v>CANELA ENTERA KG FFVV</v>
+        <v>COCO RALLADO KG FFVV</v>
       </c>
       <c r="C94" t="str">
         <v/>
       </c>
       <c r="D94" t="str">
-        <v>44526</v>
+        <v>44525</v>
       </c>
       <c r="E94" t="str">
-        <v>55160</v>
+        <v>14760</v>
       </c>
       <c r="F94" t="str">
         <v>Por peso</v>
@@ -2281,19 +2281,19 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>744527</v>
+        <v>744526</v>
       </c>
       <c r="B95" t="str">
-        <v>TE VERDE KG FFVV</v>
+        <v>CANELA ENTERA KG FFVV</v>
       </c>
       <c r="C95" t="str">
         <v/>
       </c>
       <c r="D95" t="str">
-        <v>44527</v>
+        <v>44526</v>
       </c>
       <c r="E95" t="str">
-        <v>13960</v>
+        <v>55160</v>
       </c>
       <c r="F95" t="str">
         <v>Por peso</v>
@@ -2301,19 +2301,19 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>744528</v>
+        <v>744527</v>
       </c>
       <c r="B96" t="str">
-        <v>MAICENA KG FFVV</v>
+        <v>TE VERDE KG FFVV</v>
       </c>
       <c r="C96" t="str">
         <v/>
       </c>
       <c r="D96" t="str">
-        <v>44528</v>
+        <v>44527</v>
       </c>
       <c r="E96" t="str">
-        <v>3160</v>
+        <v>13960</v>
       </c>
       <c r="F96" t="str">
         <v>Por peso</v>
@@ -2321,19 +2321,19 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>742603</v>
+        <v>744528</v>
       </c>
       <c r="B97" t="str">
-        <v>TOMATE LIQUIDACION</v>
+        <v>MAICENA KG FFVV</v>
       </c>
       <c r="C97" t="str">
         <v/>
       </c>
       <c r="D97" t="str">
-        <v>42603</v>
+        <v>44528</v>
       </c>
       <c r="E97" t="str">
-        <v>9990</v>
+        <v>3160</v>
       </c>
       <c r="F97" t="str">
         <v>Por peso</v>
@@ -2341,19 +2341,19 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>742605</v>
+        <v>742603</v>
       </c>
       <c r="B98" t="str">
-        <v>PALTA LIQUIDACION</v>
+        <v>TOMATE LIQUIDACION</v>
       </c>
       <c r="C98" t="str">
         <v/>
       </c>
       <c r="D98" t="str">
-        <v>42605</v>
+        <v>42603</v>
       </c>
       <c r="E98" t="str">
-        <v>4490</v>
+        <v>9990</v>
       </c>
       <c r="F98" t="str">
         <v>Por peso</v>
@@ -2361,19 +2361,19 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>742606</v>
+        <v>742605</v>
       </c>
       <c r="B99" t="str">
-        <v>PLATANO LIQUIDACION</v>
+        <v>PALTA LIQUIDACION</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
       <c r="D99" t="str">
-        <v>42606</v>
+        <v>42605</v>
       </c>
       <c r="E99" t="str">
-        <v>9990</v>
+        <v>4490</v>
       </c>
       <c r="F99" t="str">
         <v>Por peso</v>
@@ -2381,16 +2381,16 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>741607</v>
+        <v>742606</v>
       </c>
       <c r="B100" t="str">
-        <v>ZANAHORIA LIQUIDACION</v>
+        <v>PLATANO LIQUIDACION</v>
       </c>
       <c r="C100" t="str">
         <v/>
       </c>
       <c r="D100" t="str">
-        <v>41607</v>
+        <v>42606</v>
       </c>
       <c r="E100" t="str">
         <v>9990</v>
@@ -2401,16 +2401,16 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>742402</v>
+        <v>741607</v>
       </c>
       <c r="B101" t="str">
-        <v>CIRUELA LIQUIDACION</v>
+        <v>ZANAHORIA LIQUIDACION</v>
       </c>
       <c r="C101" t="str">
         <v/>
       </c>
       <c r="D101" t="str">
-        <v>42402</v>
+        <v>41607</v>
       </c>
       <c r="E101" t="str">
         <v>9990</v>
@@ -2421,16 +2421,16 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>742120</v>
+        <v>742402</v>
       </c>
       <c r="B102" t="str">
-        <v>PERA LIQUIDACION</v>
+        <v>CIRUELA LIQUIDACION</v>
       </c>
       <c r="C102" t="str">
         <v/>
       </c>
       <c r="D102" t="str">
-        <v>42120</v>
+        <v>42402</v>
       </c>
       <c r="E102" t="str">
         <v>9990</v>
@@ -2441,19 +2441,19 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>742126</v>
+        <v>742120</v>
       </c>
       <c r="B103" t="str">
-        <v>DURAZNO LIQUIDACION KG</v>
+        <v>PERA LIQUIDACION</v>
       </c>
       <c r="C103" t="str">
         <v/>
       </c>
       <c r="D103" t="str">
-        <v>42126</v>
+        <v>42120</v>
       </c>
       <c r="E103" t="str">
-        <v>1990</v>
+        <v>9990</v>
       </c>
       <c r="F103" t="str">
         <v>Por peso</v>
@@ -2461,19 +2461,19 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>742127</v>
+        <v>742126</v>
       </c>
       <c r="B104" t="str">
-        <v>LIMON LIQUIDACION</v>
+        <v>DURAZNO LIQUIDACION KG</v>
       </c>
       <c r="C104" t="str">
         <v/>
       </c>
       <c r="D104" t="str">
-        <v>42127</v>
+        <v>42126</v>
       </c>
       <c r="E104" t="str">
-        <v>9990</v>
+        <v>1990</v>
       </c>
       <c r="F104" t="str">
         <v>Por peso</v>
@@ -2481,16 +2481,16 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>742128</v>
+        <v>742127</v>
       </c>
       <c r="B105" t="str">
-        <v>POROTO VERDE LIQUIDACION KG</v>
+        <v>LIMON LIQUIDACION</v>
       </c>
       <c r="C105" t="str">
         <v/>
       </c>
       <c r="D105" t="str">
-        <v>42128</v>
+        <v>42127</v>
       </c>
       <c r="E105" t="str">
         <v>9990</v>
@@ -2501,16 +2501,16 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>742129</v>
+        <v>742128</v>
       </c>
       <c r="B106" t="str">
-        <v>POROTO GRANADO LIQUIDACION</v>
+        <v>POROTO VERDE LIQUIDACION KG</v>
       </c>
       <c r="C106" t="str">
         <v/>
       </c>
       <c r="D106" t="str">
-        <v>42129</v>
+        <v>42128</v>
       </c>
       <c r="E106" t="str">
         <v>9990</v>
@@ -2521,16 +2521,16 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>742130</v>
+        <v>742129</v>
       </c>
       <c r="B107" t="str">
-        <v>MANZANA LIQUIDACION</v>
+        <v>POROTO GRANADO LIQUIDACION</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107" t="str">
-        <v>42130</v>
+        <v>42129</v>
       </c>
       <c r="E107" t="str">
         <v>9990</v>
@@ -2541,16 +2541,16 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>741250</v>
+        <v>742130</v>
       </c>
       <c r="B108" t="str">
-        <v>UVA LIQUIDACION</v>
+        <v>MANZANA LIQUIDACION</v>
       </c>
       <c r="C108" t="str">
         <v/>
       </c>
       <c r="D108" t="str">
-        <v>41250</v>
+        <v>42130</v>
       </c>
       <c r="E108" t="str">
         <v>9990</v>
@@ -2561,16 +2561,16 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>742421</v>
+        <v>741250</v>
       </c>
       <c r="B109" t="str">
-        <v>NARANJA LIQUIDACION</v>
+        <v>UVA LIQUIDACION</v>
       </c>
       <c r="C109" t="str">
         <v/>
       </c>
       <c r="D109" t="str">
-        <v>42421</v>
+        <v>41250</v>
       </c>
       <c r="E109" t="str">
         <v>9990</v>
@@ -2581,19 +2581,19 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>745000</v>
+        <v>742421</v>
       </c>
       <c r="B110" t="str">
-        <v>AJO LIQUIDACION</v>
+        <v>NARANJA LIQUIDACION</v>
       </c>
       <c r="C110" t="str">
         <v/>
       </c>
       <c r="D110" t="str">
-        <v>45000</v>
+        <v>42421</v>
       </c>
       <c r="E110" t="str">
-        <v>9999</v>
+        <v>9990</v>
       </c>
       <c r="F110" t="str">
         <v>Por peso</v>
@@ -2601,19 +2601,19 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>742300</v>
+        <v>745000</v>
       </c>
       <c r="B111" t="str">
-        <v>PALTA NEGRA LA CRUZ KG</v>
+        <v>AJO LIQUIDACION</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111" t="str">
-        <v>42300</v>
+        <v>45000</v>
       </c>
       <c r="E111" t="str">
-        <v>3590</v>
+        <v>9999</v>
       </c>
       <c r="F111" t="str">
         <v>Por peso</v>
@@ -2621,19 +2621,19 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>740303</v>
+        <v>742300</v>
       </c>
       <c r="B112" t="str">
-        <v>PAPA LIQUIDACION</v>
+        <v>PALTA NEGRA LA CRUZ KG</v>
       </c>
       <c r="C112" t="str">
         <v/>
       </c>
       <c r="D112" t="str">
-        <v>40303</v>
+        <v>42300</v>
       </c>
       <c r="E112" t="str">
-        <v>9990</v>
+        <v>3590</v>
       </c>
       <c r="F112" t="str">
         <v>Por peso</v>
@@ -2641,19 +2641,19 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>742549</v>
+        <v>740303</v>
       </c>
       <c r="B113" t="str">
-        <v>NECTARIN LIQUIDACION</v>
+        <v>PAPA LIQUIDACION</v>
       </c>
       <c r="C113" t="str">
         <v/>
       </c>
       <c r="D113" t="str">
-        <v>42549</v>
+        <v>40303</v>
       </c>
       <c r="E113" t="str">
-        <v>2290</v>
+        <v>9990</v>
       </c>
       <c r="F113" t="str">
         <v>Por peso</v>
@@ -2661,19 +2661,19 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>748913</v>
+        <v>742549</v>
       </c>
       <c r="B114" t="str">
-        <v>JENGIBRE EN POLVO FFVV</v>
+        <v>NECTARIN LIQUIDACION</v>
       </c>
       <c r="C114" t="str">
         <v/>
       </c>
       <c r="D114" t="str">
-        <v>48913</v>
+        <v>42549</v>
       </c>
       <c r="E114" t="str">
-        <v>14760</v>
+        <v>2290</v>
       </c>
       <c r="F114" t="str">
         <v>Por peso</v>
@@ -2681,19 +2681,19 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>741110</v>
+        <v>748913</v>
       </c>
       <c r="B115" t="str">
-        <v>AJI COLOR KILO FFYVV</v>
+        <v>JENGIBRE EN POLVO FFVV</v>
       </c>
       <c r="C115" t="str">
         <v/>
       </c>
       <c r="D115" t="str">
-        <v>41110</v>
+        <v>48913</v>
       </c>
       <c r="E115" t="str">
-        <v>7160</v>
+        <v>14760</v>
       </c>
       <c r="F115" t="str">
         <v>Por peso</v>
@@ -2701,19 +2701,19 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>742333</v>
+        <v>741110</v>
       </c>
       <c r="B116" t="str">
-        <v>MANZANA BICOLOR KG</v>
+        <v>AJI COLOR KILO FFYVV</v>
       </c>
       <c r="C116" t="str">
         <v/>
       </c>
       <c r="D116" t="str">
-        <v>42333</v>
+        <v>41110</v>
       </c>
       <c r="E116" t="str">
-        <v>990</v>
+        <v>7160</v>
       </c>
       <c r="F116" t="str">
         <v>Por peso</v>
@@ -2721,19 +2721,19 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>742999</v>
+        <v>742333</v>
       </c>
       <c r="B117" t="str">
-        <v>CIRUELA SECA KG FFVV</v>
+        <v>MANZANA BICOLOR KG</v>
       </c>
       <c r="C117" t="str">
         <v/>
       </c>
       <c r="D117" t="str">
-        <v>42999</v>
+        <v>42333</v>
       </c>
       <c r="E117" t="str">
-        <v>6760</v>
+        <v>990</v>
       </c>
       <c r="F117" t="str">
         <v>Por peso</v>
@@ -2741,19 +2741,19 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>741222</v>
+        <v>742999</v>
       </c>
       <c r="B118" t="str">
-        <v>OREGANO KG FFVV</v>
+        <v>CIRUELA SECA KG FFVV</v>
       </c>
       <c r="C118" t="str">
         <v/>
       </c>
       <c r="D118" t="str">
-        <v>41222</v>
+        <v>42999</v>
       </c>
       <c r="E118" t="str">
-        <v>10360</v>
+        <v>6760</v>
       </c>
       <c r="F118" t="str">
         <v>Por peso</v>
@@ -2761,19 +2761,19 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>741076</v>
+        <v>741222</v>
       </c>
       <c r="B119" t="str">
-        <v>AJO KG</v>
+        <v>OREGANO KG FFVV</v>
       </c>
       <c r="C119" t="str">
         <v/>
       </c>
       <c r="D119" t="str">
-        <v>41076</v>
+        <v>41222</v>
       </c>
       <c r="E119" t="str">
-        <v>4760</v>
+        <v>10360</v>
       </c>
       <c r="F119" t="str">
         <v>Por peso</v>
@@ -2793,7 +2793,7 @@
         <v>41076</v>
       </c>
       <c r="E120" t="str">
-        <v>2996</v>
+        <v>4760</v>
       </c>
       <c r="F120" t="str">
         <v>Por peso</v>
@@ -2801,19 +2801,19 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>741041</v>
+        <v>741076</v>
       </c>
       <c r="B121" t="str">
-        <v>PAPA ZONA SUR KG</v>
+        <v>AJO KG</v>
       </c>
       <c r="C121" t="str">
         <v/>
       </c>
       <c r="D121" t="str">
-        <v>41041</v>
+        <v>41076</v>
       </c>
       <c r="E121" t="str">
-        <v>990</v>
+        <v>2996</v>
       </c>
       <c r="F121" t="str">
         <v>Por peso</v>
@@ -2821,19 +2821,19 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>744018</v>
+        <v>741041</v>
       </c>
       <c r="B122" t="str">
-        <v>MIX FRUTOS SECOS KG FFVV</v>
+        <v>PAPA ZONA SUR KG</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
       <c r="D122" t="str">
-        <v>44018</v>
+        <v>41041</v>
       </c>
       <c r="E122" t="str">
-        <v>6760</v>
+        <v>990</v>
       </c>
       <c r="F122" t="str">
         <v>Por peso</v>
@@ -2841,19 +2841,19 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>748081</v>
+        <v>744018</v>
       </c>
       <c r="B123" t="str">
-        <v>MANCAQUI KG</v>
+        <v>MIX FRUTOS SECOS KG FFVV</v>
       </c>
       <c r="C123" t="str">
         <v/>
       </c>
       <c r="D123" t="str">
-        <v>48081</v>
+        <v>44018</v>
       </c>
       <c r="E123" t="str">
-        <v>1390</v>
+        <v>6760</v>
       </c>
       <c r="F123" t="str">
         <v>Por peso</v>
@@ -2861,19 +2861,19 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>747810</v>
+        <v>748081</v>
       </c>
       <c r="B124" t="str">
-        <v>MANI SIN SAL KG FFVV</v>
+        <v>MANCAQUI KG</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124" t="str">
-        <v>47810</v>
+        <v>48081</v>
       </c>
       <c r="E124" t="str">
-        <v>4990</v>
+        <v>1390</v>
       </c>
       <c r="F124" t="str">
         <v>Por peso</v>
@@ -2881,16 +2881,16 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>747809</v>
+        <v>747810</v>
       </c>
       <c r="B125" t="str">
-        <v>MANI CON SAL KG FFVV</v>
+        <v>MANI SIN SAL KG FFVV</v>
       </c>
       <c r="C125" t="str">
         <v/>
       </c>
       <c r="D125" t="str">
-        <v>47809</v>
+        <v>47810</v>
       </c>
       <c r="E125" t="str">
         <v>4990</v>
@@ -2901,19 +2901,19 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>746548</v>
+        <v>747809</v>
       </c>
       <c r="B126" t="str">
-        <v>PAPA CHILOTA MIX KILO</v>
+        <v>MANI CON SAL KG FFVV</v>
       </c>
       <c r="C126" t="str">
         <v/>
       </c>
       <c r="D126" t="str">
-        <v>46548</v>
+        <v>47809</v>
       </c>
       <c r="E126" t="str">
-        <v>2590</v>
+        <v>4990</v>
       </c>
       <c r="F126" t="str">
         <v>Por peso</v>
@@ -2921,19 +2921,19 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>743062</v>
+        <v>746548</v>
       </c>
       <c r="B127" t="str">
-        <v>CEBOLLA KG FFVV</v>
+        <v>PAPA CHILOTA MIX KILO</v>
       </c>
       <c r="C127" t="str">
         <v/>
       </c>
       <c r="D127" t="str">
-        <v>43062</v>
+        <v>46548</v>
       </c>
       <c r="E127" t="str">
-        <v>690</v>
+        <v>2590</v>
       </c>
       <c r="F127" t="str">
         <v>Por peso</v>
@@ -2941,19 +2941,19 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>743654</v>
+        <v>743062</v>
       </c>
       <c r="B128" t="str">
-        <v>DATILES KG FFVV</v>
+        <v>CEBOLLA KG FFVV</v>
       </c>
       <c r="C128" t="str">
         <v/>
       </c>
       <c r="D128" t="str">
-        <v>43654</v>
+        <v>43062</v>
       </c>
       <c r="E128" t="str">
-        <v>7160</v>
+        <v>690</v>
       </c>
       <c r="F128" t="str">
         <v>Por peso</v>
@@ -2961,19 +2961,19 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>744552</v>
+        <v>743654</v>
       </c>
       <c r="B129" t="str">
-        <v>CHIA KG FFVV</v>
+        <v>DATILES KG FFVV</v>
       </c>
       <c r="C129" t="str">
         <v/>
       </c>
       <c r="D129" t="str">
-        <v>44552</v>
+        <v>43654</v>
       </c>
       <c r="E129" t="str">
-        <v>9960</v>
+        <v>7160</v>
       </c>
       <c r="F129" t="str">
         <v>Por peso</v>
@@ -2981,19 +2981,19 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>742939</v>
+        <v>744552</v>
       </c>
       <c r="B130" t="str">
-        <v>CEBOLLA LIQUIDACION</v>
+        <v>CHIA KG FFVV</v>
       </c>
       <c r="C130" t="str">
         <v/>
       </c>
       <c r="D130" t="str">
-        <v>42939</v>
+        <v>44552</v>
       </c>
       <c r="E130" t="str">
-        <v>9990</v>
+        <v>9960</v>
       </c>
       <c r="F130" t="str">
         <v>Por peso</v>
@@ -3001,16 +3001,16 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>743232</v>
+        <v>742939</v>
       </c>
       <c r="B131" t="str">
-        <v>POMELO LIQUIDACION</v>
+        <v>CEBOLLA LIQUIDACION</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
       <c r="D131" t="str">
-        <v>43232</v>
+        <v>42939</v>
       </c>
       <c r="E131" t="str">
         <v>9990</v>
@@ -3021,16 +3021,16 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>743233</v>
+        <v>743232</v>
       </c>
       <c r="B132" t="str">
-        <v>MANGO LIQUIDACION</v>
+        <v>POMELO LIQUIDACION</v>
       </c>
       <c r="C132" t="str">
         <v/>
       </c>
       <c r="D132" t="str">
-        <v>43233</v>
+        <v>43232</v>
       </c>
       <c r="E132" t="str">
         <v>9990</v>
@@ -3041,19 +3041,19 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>743237</v>
+        <v>743233</v>
       </c>
       <c r="B133" t="str">
-        <v>UVA ROSADA KG</v>
+        <v>MANGO LIQUIDACION</v>
       </c>
       <c r="C133" t="str">
         <v/>
       </c>
       <c r="D133" t="str">
-        <v>43237</v>
+        <v>43233</v>
       </c>
       <c r="E133" t="str">
-        <v>1190</v>
+        <v>9990</v>
       </c>
       <c r="F133" t="str">
         <v>Por peso</v>
@@ -3061,19 +3061,19 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>743038</v>
+        <v>743237</v>
       </c>
       <c r="B134" t="str">
-        <v>CURCUMA MOLIDA KG FFVV</v>
+        <v>UVA ROSADA KG</v>
       </c>
       <c r="C134" t="str">
         <v/>
       </c>
       <c r="D134" t="str">
-        <v>43038</v>
+        <v>43237</v>
       </c>
       <c r="E134" t="str">
-        <v>12360</v>
+        <v>1190</v>
       </c>
       <c r="F134" t="str">
         <v>Por peso</v>
@@ -3081,19 +3081,19 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>746364</v>
+        <v>743038</v>
       </c>
       <c r="B135" t="str">
-        <v>QUINOA KG FFVV</v>
+        <v>CURCUMA MOLIDA KG FFVV</v>
       </c>
       <c r="C135" t="str">
         <v/>
       </c>
       <c r="D135" t="str">
-        <v>46364</v>
+        <v>43038</v>
       </c>
       <c r="E135" t="str">
-        <v>9160</v>
+        <v>12360</v>
       </c>
       <c r="F135" t="str">
         <v>Por peso</v>
@@ -3101,19 +3101,19 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>744007</v>
+        <v>746364</v>
       </c>
       <c r="B136" t="str">
-        <v>CHIA ENTERA GRANEL ARUNA KG</v>
+        <v>QUINOA KG FFVV</v>
       </c>
       <c r="C136" t="str">
         <v/>
       </c>
       <c r="D136" t="str">
-        <v>44007</v>
+        <v>46364</v>
       </c>
       <c r="E136" t="str">
-        <v>7160</v>
+        <v>9160</v>
       </c>
       <c r="F136" t="str">
         <v>Por peso</v>
@@ -3121,27 +3121,47 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
+        <v>744007</v>
+      </c>
+      <c r="B137" t="str">
+        <v>CHIA ENTERA GRANEL ARUNA KG</v>
+      </c>
+      <c r="C137" t="str">
+        <v/>
+      </c>
+      <c r="D137" t="str">
+        <v>44007</v>
+      </c>
+      <c r="E137" t="str">
+        <v>7160</v>
+      </c>
+      <c r="F137" t="str">
+        <v>Por peso</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
         <v>743437</v>
       </c>
-      <c r="B137" t="str">
+      <c r="B138" t="str">
         <v>CLAVO DE OLOR KG FFVV</v>
       </c>
-      <c r="C137" t="str">
-        <v/>
-      </c>
-      <c r="D137" t="str">
+      <c r="C138" t="str">
+        <v/>
+      </c>
+      <c r="D138" t="str">
         <v>43437</v>
       </c>
-      <c r="E137" t="str">
+      <c r="E138" t="str">
         <v>36360</v>
       </c>
-      <c r="F137" t="str">
+      <c r="F138" t="str">
         <v>Por peso</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F137"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F138"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/MaestraPLU_FFVV.xlsx
+++ b/MaestraPLU_FFVV.xlsx
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>742011</v>
+        <v>741032</v>
       </c>
       <c r="B2" t="str">
-        <v>LIMON KG</v>
+        <v>JENGIBRE KG</v>
       </c>
       <c r="C2" t="str">
         <v/>
       </c>
       <c r="D2" t="str">
-        <v>42011</v>
+        <v>51032</v>
       </c>
       <c r="E2" t="str">
-        <v>1000</v>
+        <v>3560</v>
       </c>
       <c r="F2" t="str">
         <v>Por peso</v>
@@ -441,19 +441,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>742041</v>
+        <v>745146</v>
       </c>
       <c r="B3" t="str">
-        <v>TOMATE LARGA VIDA KG</v>
+        <v>ALMENDRA KG FFVV</v>
       </c>
       <c r="C3" t="str">
         <v/>
       </c>
       <c r="D3" t="str">
-        <v>42041</v>
+        <v>45146</v>
       </c>
       <c r="E3" t="str">
-        <v>1190</v>
+        <v>16760</v>
       </c>
       <c r="F3" t="str">
         <v>Por peso</v>
@@ -461,19 +461,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>742033</v>
+        <v>744023</v>
       </c>
       <c r="B4" t="str">
-        <v>CIRUELA KG</v>
+        <v>CHUCHOCA MOLIDA KG FFVV</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
       <c r="D4" t="str">
-        <v>42033</v>
+        <v>44023</v>
       </c>
       <c r="E4" t="str">
-        <v>500</v>
+        <v>1960</v>
       </c>
       <c r="F4" t="str">
         <v>Por peso</v>
@@ -481,19 +481,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>742010</v>
+        <v>743024</v>
       </c>
       <c r="B5" t="str">
-        <v>KIWI KG</v>
+        <v>PASAS MORENAS KG FFVV</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5" t="str">
-        <v>42010</v>
+        <v>43024</v>
       </c>
       <c r="E5" t="str">
-        <v>990</v>
+        <v>5160</v>
       </c>
       <c r="F5" t="str">
         <v>Por peso</v>
@@ -501,19 +501,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>741042</v>
+        <v>744019</v>
       </c>
       <c r="B6" t="str">
-        <v>ZANAHORIA KG</v>
+        <v>PASAS RUBIA KG FFVV</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
       <c r="D6" t="str">
-        <v>41042</v>
+        <v>44019</v>
       </c>
       <c r="E6" t="str">
-        <v>500</v>
+        <v>9960</v>
       </c>
       <c r="F6" t="str">
         <v>Por peso</v>
@@ -521,19 +521,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>741032</v>
+        <v>744160</v>
       </c>
       <c r="B7" t="str">
-        <v>JENGIBRE KG</v>
+        <v>YUCA KG FFVV</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7" t="str">
-        <v>51032</v>
+        <v>44160</v>
       </c>
       <c r="E7" t="str">
-        <v>3560</v>
+        <v>3490</v>
       </c>
       <c r="F7" t="str">
         <v>Por peso</v>
@@ -541,19 +541,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>745146</v>
+        <v>744153</v>
       </c>
       <c r="B8" t="str">
-        <v>ALMENDRA KG FFVV</v>
+        <v>TUNAS LIQUIDACION KG</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>45146</v>
+        <v>44153</v>
       </c>
       <c r="E8" t="str">
-        <v>16760</v>
+        <v>9990</v>
       </c>
       <c r="F8" t="str">
         <v>Por peso</v>
@@ -561,19 +561,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>744023</v>
+        <v>744146</v>
       </c>
       <c r="B9" t="str">
-        <v>CHUCHOCA MOLIDA KG FFVV</v>
+        <v>FLOR DE JAMAICA KG FFVV</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9" t="str">
-        <v>44023</v>
+        <v>44146</v>
       </c>
       <c r="E9" t="str">
-        <v>1960</v>
+        <v>27960</v>
       </c>
       <c r="F9" t="str">
         <v>Por peso</v>
@@ -581,19 +581,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>743024</v>
+        <v>745147</v>
       </c>
       <c r="B10" t="str">
-        <v>PASAS MORENAS KG FFVV</v>
+        <v>HUESILLOS KG FFVV</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>43024</v>
+        <v>45147</v>
       </c>
       <c r="E10" t="str">
-        <v>5160</v>
+        <v>9560</v>
       </c>
       <c r="F10" t="str">
         <v>Por peso</v>
@@ -601,19 +601,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>744019</v>
+        <v>742072</v>
       </c>
       <c r="B11" t="str">
-        <v>PASAS RUBIA KG FFVV</v>
+        <v>SANDIA PRIMERA PP KG</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>44019</v>
+        <v>42072</v>
       </c>
       <c r="E11" t="str">
-        <v>9960</v>
+        <v>490</v>
       </c>
       <c r="F11" t="str">
         <v>Por peso</v>
@@ -621,19 +621,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>744160</v>
+        <v>742031</v>
       </c>
       <c r="B12" t="str">
-        <v>YUCA KG FFVV</v>
+        <v>PLATANO KG</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12" t="str">
-        <v>44160</v>
+        <v>42031</v>
       </c>
       <c r="E12" t="str">
-        <v>3490</v>
+        <v>1690</v>
       </c>
       <c r="F12" t="str">
         <v>Por peso</v>
@@ -641,19 +641,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>744153</v>
+        <v>742025</v>
       </c>
       <c r="B13" t="str">
-        <v>TUNAS LIQUIDACION KG</v>
+        <v>POMELO KG</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13" t="str">
-        <v>44153</v>
+        <v>42025</v>
       </c>
       <c r="E13" t="str">
-        <v>9990</v>
+        <v>890</v>
       </c>
       <c r="F13" t="str">
         <v>Por peso</v>
@@ -661,19 +661,19 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>744146</v>
+        <v>742045</v>
       </c>
       <c r="B14" t="str">
-        <v>FLOR DE JAMAICA KG FFVV</v>
+        <v>PERA PACKHAM KG</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>44146</v>
+        <v>42045</v>
       </c>
       <c r="E14" t="str">
-        <v>27960</v>
+        <v>890</v>
       </c>
       <c r="F14" t="str">
         <v>Por peso</v>
@@ -681,19 +681,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>745147</v>
+        <v>742024</v>
       </c>
       <c r="B15" t="str">
-        <v>HUESILLOS KG FFVV</v>
+        <v>PERA WINTERNELLY KG</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>45147</v>
+        <v>42024</v>
       </c>
       <c r="E15" t="str">
-        <v>9560</v>
+        <v>890</v>
       </c>
       <c r="F15" t="str">
         <v>Por peso</v>
@@ -701,19 +701,19 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>742072</v>
+        <v>742082</v>
       </c>
       <c r="B16" t="str">
-        <v>SANDIA PRIMERA PP KG</v>
+        <v>PERA BERRY BOSC</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>42072</v>
+        <v>42082</v>
       </c>
       <c r="E16" t="str">
-        <v>490</v>
+        <v>890</v>
       </c>
       <c r="F16" t="str">
         <v>Por peso</v>
@@ -721,19 +721,19 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>742031</v>
+        <v>742081</v>
       </c>
       <c r="B17" t="str">
-        <v>PLATANO KG</v>
+        <v>PERA ASIATICA KG</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>42031</v>
+        <v>42081</v>
       </c>
       <c r="E17" t="str">
-        <v>1690</v>
+        <v>990</v>
       </c>
       <c r="F17" t="str">
         <v>Por peso</v>
@@ -741,19 +741,19 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>742025</v>
+        <v>742026</v>
       </c>
       <c r="B18" t="str">
-        <v>POMELO KG</v>
+        <v>PEPINO FRUTA KG</v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>42025</v>
+        <v>42026</v>
       </c>
       <c r="E18" t="str">
-        <v>890</v>
+        <v>1790</v>
       </c>
       <c r="F18" t="str">
         <v>Por peso</v>
@@ -761,19 +761,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>742045</v>
+        <v>742022</v>
       </c>
       <c r="B19" t="str">
-        <v>PERA PACKHAM KG</v>
+        <v>NUECES KG FFVV</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>42045</v>
+        <v>42022</v>
       </c>
       <c r="E19" t="str">
-        <v>890</v>
+        <v>14760</v>
       </c>
       <c r="F19" t="str">
         <v>Por peso</v>
@@ -781,19 +781,19 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>742024</v>
+        <v>742044</v>
       </c>
       <c r="B20" t="str">
-        <v>PERA WINTERNELLY KG</v>
+        <v>MEMBRILLO KG</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>42024</v>
+        <v>42044</v>
       </c>
       <c r="E20" t="str">
-        <v>890</v>
+        <v>990</v>
       </c>
       <c r="F20" t="str">
         <v>Por peso</v>
@@ -801,19 +801,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>742082</v>
+        <v>742015</v>
       </c>
       <c r="B21" t="str">
-        <v>PERA BERRY BOSC</v>
+        <v>MANZANA VERDE KG</v>
       </c>
       <c r="C21" t="str">
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>42082</v>
+        <v>42015</v>
       </c>
       <c r="E21" t="str">
-        <v>890</v>
+        <v>990</v>
       </c>
       <c r="F21" t="str">
         <v>Por peso</v>
@@ -821,16 +821,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>742081</v>
+        <v>742013</v>
       </c>
       <c r="B22" t="str">
-        <v>PERA ASIATICA KG</v>
+        <v>MANZANA ROJA KG</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22" t="str">
-        <v>42081</v>
+        <v>42013</v>
       </c>
       <c r="E22" t="str">
         <v>990</v>
@@ -841,19 +841,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>742026</v>
+        <v>742066</v>
       </c>
       <c r="B23" t="str">
-        <v>PEPINO FRUTA KG</v>
+        <v>MANZANA ROYAL GALA KG</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>42026</v>
+        <v>42066</v>
       </c>
       <c r="E23" t="str">
-        <v>1790</v>
+        <v>990</v>
       </c>
       <c r="F23" t="str">
         <v>Por peso</v>
@@ -861,19 +861,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>742022</v>
+        <v>742067</v>
       </c>
       <c r="B24" t="str">
-        <v>NUECES KG FFVV</v>
+        <v>MANZANA FUJI KG</v>
       </c>
       <c r="C24" t="str">
         <v/>
       </c>
       <c r="D24" t="str">
-        <v>42022</v>
+        <v>42067</v>
       </c>
       <c r="E24" t="str">
-        <v>14760</v>
+        <v>990</v>
       </c>
       <c r="F24" t="str">
         <v>Por peso</v>
@@ -881,19 +881,19 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>742044</v>
+        <v>742102</v>
       </c>
       <c r="B25" t="str">
-        <v>MEMBRILLO KG</v>
+        <v>MANGOS KG</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>42044</v>
+        <v>42102</v>
       </c>
       <c r="E25" t="str">
-        <v>990</v>
+        <v>2890</v>
       </c>
       <c r="F25" t="str">
         <v>Por peso</v>
@@ -901,19 +901,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>742015</v>
+        <v>742011</v>
       </c>
       <c r="B26" t="str">
-        <v>MANZANA VERDE KG</v>
+        <v>LIMON KG</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
       <c r="D26" t="str">
-        <v>42015</v>
+        <v>42011</v>
       </c>
       <c r="E26" t="str">
-        <v>990</v>
+        <v>1290</v>
       </c>
       <c r="F26" t="str">
         <v>Por peso</v>
@@ -921,19 +921,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>742013</v>
+        <v>742010</v>
       </c>
       <c r="B27" t="str">
-        <v>MANZANA ROJA KG</v>
+        <v>KIWI KG</v>
       </c>
       <c r="C27" t="str">
         <v/>
       </c>
       <c r="D27" t="str">
-        <v>42013</v>
+        <v>42010</v>
       </c>
       <c r="E27" t="str">
-        <v>990</v>
+        <v>1190</v>
       </c>
       <c r="F27" t="str">
         <v>Por peso</v>
@@ -941,19 +941,19 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>742066</v>
+        <v>742051</v>
       </c>
       <c r="B28" t="str">
-        <v>MANZANA ROYAL GALA KG</v>
+        <v>GRANADAS KG</v>
       </c>
       <c r="C28" t="str">
         <v/>
       </c>
       <c r="D28" t="str">
-        <v>42066</v>
+        <v>42051</v>
       </c>
       <c r="E28" t="str">
-        <v>990</v>
+        <v>1990</v>
       </c>
       <c r="F28" t="str">
         <v>Por peso</v>
@@ -961,19 +961,19 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>742067</v>
+        <v>742033</v>
       </c>
       <c r="B29" t="str">
-        <v>MANZANA FUJI KG</v>
+        <v>CIRUELA KG</v>
       </c>
       <c r="C29" t="str">
         <v/>
       </c>
       <c r="D29" t="str">
-        <v>42067</v>
+        <v>42033</v>
       </c>
       <c r="E29" t="str">
-        <v>990</v>
+        <v>690</v>
       </c>
       <c r="F29" t="str">
         <v>Por peso</v>
@@ -981,19 +981,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>742102</v>
+        <v>742042</v>
       </c>
       <c r="B30" t="str">
-        <v>MANGOS KG</v>
+        <v>UVA NEGRA KG</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30" t="str">
-        <v>42102</v>
+        <v>42042</v>
       </c>
       <c r="E30" t="str">
-        <v>2890</v>
+        <v>1190</v>
       </c>
       <c r="F30" t="str">
         <v>Por peso</v>
@@ -1001,19 +1001,19 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>742051</v>
+        <v>742041</v>
       </c>
       <c r="B31" t="str">
-        <v>GRANADAS KG</v>
+        <v>TOMATE LARGA VIDA KG</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31" t="str">
-        <v>42051</v>
+        <v>42041</v>
       </c>
       <c r="E31" t="str">
-        <v>1990</v>
+        <v>1490</v>
       </c>
       <c r="F31" t="str">
         <v>Por peso</v>
@@ -1021,19 +1021,19 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>742042</v>
+        <v>742006</v>
       </c>
       <c r="B32" t="str">
-        <v>UVA NEGRA KG</v>
+        <v>CEREZAS KILO</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>42042</v>
+        <v>42006</v>
       </c>
       <c r="E32" t="str">
-        <v>1190</v>
+        <v>1290</v>
       </c>
       <c r="F32" t="str">
         <v>Por peso</v>
@@ -1041,19 +1041,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>742006</v>
+        <v>742166</v>
       </c>
       <c r="B33" t="str">
-        <v>CEREZAS KILO</v>
+        <v>CACAO AMARGO KG FFVV</v>
       </c>
       <c r="C33" t="str">
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>42006</v>
+        <v>42166</v>
       </c>
       <c r="E33" t="str">
-        <v>1290</v>
+        <v>14760</v>
       </c>
       <c r="F33" t="str">
         <v>Por peso</v>
@@ -1061,19 +1061,19 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>742166</v>
+        <v>742135</v>
       </c>
       <c r="B34" t="str">
-        <v>CACAO AMARGO KG FFVV</v>
+        <v>SANDIA EXTRA PP KG</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>42166</v>
+        <v>42135</v>
       </c>
       <c r="E34" t="str">
-        <v>14760</v>
+        <v>490</v>
       </c>
       <c r="F34" t="str">
         <v>Por peso</v>
@@ -1081,19 +1081,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>742135</v>
+        <v>741835</v>
       </c>
       <c r="B35" t="str">
-        <v>SANDIA EXTRA PP KG</v>
+        <v>ANIS ESTRELLA KG FFVV</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>42135</v>
+        <v>41835</v>
       </c>
       <c r="E35" t="str">
-        <v>490</v>
+        <v>27160</v>
       </c>
       <c r="F35" t="str">
         <v>Por peso</v>
@@ -1101,19 +1101,19 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>741835</v>
+        <v>741828</v>
       </c>
       <c r="B36" t="str">
-        <v>ANIS ESTRELLA KG FFVV</v>
+        <v>PEPINO FRUTA LIQUIDACION</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>41835</v>
+        <v>41828</v>
       </c>
       <c r="E36" t="str">
-        <v>27160</v>
+        <v>9990</v>
       </c>
       <c r="F36" t="str">
         <v>Por peso</v>
@@ -1121,19 +1121,19 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>741828</v>
+        <v>741826</v>
       </c>
       <c r="B37" t="str">
-        <v>PEPINO FRUTA LIQUIDACION</v>
+        <v>TOMATE CHERRY KG FFVV</v>
       </c>
       <c r="C37" t="str">
         <v/>
       </c>
       <c r="D37" t="str">
-        <v>41828</v>
+        <v>41826</v>
       </c>
       <c r="E37" t="str">
-        <v>9990</v>
+        <v>4760</v>
       </c>
       <c r="F37" t="str">
         <v>Por peso</v>
@@ -1141,19 +1141,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>741826</v>
+        <v>741820</v>
       </c>
       <c r="B38" t="str">
-        <v>TOMATE CHERRY KG FFVV</v>
+        <v>MERKEN KG FFVV</v>
       </c>
       <c r="C38" t="str">
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>41826</v>
+        <v>41820</v>
       </c>
       <c r="E38" t="str">
-        <v>4760</v>
+        <v>12360</v>
       </c>
       <c r="F38" t="str">
         <v>Por peso</v>
@@ -1161,19 +1161,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>741820</v>
+        <v>745142</v>
       </c>
       <c r="B39" t="str">
-        <v>MERKEN KG FFVV</v>
+        <v>CEBOLLA MORADA KG</v>
       </c>
       <c r="C39" t="str">
         <v/>
       </c>
       <c r="D39" t="str">
-        <v>41820</v>
+        <v>45142</v>
       </c>
       <c r="E39" t="str">
-        <v>12360</v>
+        <v>790</v>
       </c>
       <c r="F39" t="str">
         <v>Por peso</v>
@@ -1181,19 +1181,19 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>745142</v>
+        <v>742075</v>
       </c>
       <c r="B40" t="str">
-        <v>CEBOLLA MORADA KG</v>
+        <v>PERA FORELLE KG</v>
       </c>
       <c r="C40" t="str">
         <v/>
       </c>
       <c r="D40" t="str">
-        <v>45142</v>
+        <v>42075</v>
       </c>
       <c r="E40" t="str">
-        <v>790</v>
+        <v>890</v>
       </c>
       <c r="F40" t="str">
         <v>Por peso</v>
@@ -1201,19 +1201,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>742075</v>
+        <v>742118</v>
       </c>
       <c r="B41" t="str">
-        <v>PERA FORELLE KG</v>
+        <v>CLEMENTINA MANDARINA KG</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
       <c r="D41" t="str">
-        <v>42075</v>
+        <v>42118</v>
       </c>
       <c r="E41" t="str">
-        <v>890</v>
+        <v>1490</v>
       </c>
       <c r="F41" t="str">
         <v>Por peso</v>
@@ -1221,19 +1221,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>742118</v>
+        <v>742016</v>
       </c>
       <c r="B42" t="str">
-        <v>CLEMENTINA MANDARINA KG</v>
+        <v>CASTANAS KILO FFVV</v>
       </c>
       <c r="C42" t="str">
         <v/>
       </c>
       <c r="D42" t="str">
-        <v>42118</v>
+        <v>42016</v>
       </c>
       <c r="E42" t="str">
-        <v>1490</v>
+        <v>1990</v>
       </c>
       <c r="F42" t="str">
         <v>Por peso</v>
@@ -1241,19 +1241,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>742016</v>
+        <v>742001</v>
       </c>
       <c r="B43" t="str">
-        <v>CASTANAS KILO FFVV</v>
+        <v>FRUTA CONFITADA KG FFVV</v>
       </c>
       <c r="C43" t="str">
         <v/>
       </c>
       <c r="D43" t="str">
-        <v>42016</v>
+        <v>42001</v>
       </c>
       <c r="E43" t="str">
-        <v>1990</v>
+        <v>5560</v>
       </c>
       <c r="F43" t="str">
         <v>Por peso</v>
@@ -1261,19 +1261,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>742001</v>
+        <v>742158</v>
       </c>
       <c r="B44" t="str">
-        <v>FRUTA CONFITADA KG FFVV</v>
+        <v>MANZANA CRISS PINK KG</v>
       </c>
       <c r="C44" t="str">
         <v/>
       </c>
       <c r="D44" t="str">
-        <v>42001</v>
+        <v>42158</v>
       </c>
       <c r="E44" t="str">
-        <v>5560</v>
+        <v>990</v>
       </c>
       <c r="F44" t="str">
         <v>Por peso</v>
@@ -1281,19 +1281,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>742158</v>
+        <v>741064</v>
       </c>
       <c r="B45" t="str">
-        <v>MANZANA CRISS PINK KG</v>
+        <v>ZAPALLO JAMBOREE SAMPSON PP KG</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45" t="str">
-        <v>42158</v>
+        <v>41064</v>
       </c>
       <c r="E45" t="str">
-        <v>990</v>
+        <v>790</v>
       </c>
       <c r="F45" t="str">
         <v>Por peso</v>
@@ -1301,16 +1301,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>741064</v>
+        <v>741039</v>
       </c>
       <c r="B46" t="str">
-        <v>ZAPALLO JAMBOREE SAMPSON PP KG</v>
+        <v>ZAPALLO CAMOTE KG</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46" t="str">
-        <v>41064</v>
+        <v>41039</v>
       </c>
       <c r="E46" t="str">
         <v>790</v>
@@ -1321,19 +1321,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>741039</v>
+        <v>741025</v>
       </c>
       <c r="B47" t="str">
-        <v>ZAPALLO CAMOTE KG</v>
+        <v>POROTO VERDE KG</v>
       </c>
       <c r="C47" t="str">
         <v/>
       </c>
       <c r="D47" t="str">
-        <v>41039</v>
+        <v>41025</v>
       </c>
       <c r="E47" t="str">
-        <v>790</v>
+        <v>2290</v>
       </c>
       <c r="F47" t="str">
         <v>Por peso</v>
@@ -1341,16 +1341,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>741025</v>
+        <v>741026</v>
       </c>
       <c r="B48" t="str">
-        <v>POROTO VERDE KG</v>
+        <v>POROTO GRANADO KG</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>41025</v>
+        <v>41026</v>
       </c>
       <c r="E48" t="str">
         <v>2290</v>
@@ -1361,19 +1361,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>741026</v>
+        <v>741051</v>
       </c>
       <c r="B49" t="str">
-        <v>POROTO GRANADO KG</v>
+        <v>PAPA LAVADA KG</v>
       </c>
       <c r="C49" t="str">
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>41026</v>
+        <v>41051</v>
       </c>
       <c r="E49" t="str">
-        <v>2290</v>
+        <v>890</v>
       </c>
       <c r="F49" t="str">
         <v>Por peso</v>
@@ -1381,19 +1381,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>741051</v>
+        <v>741002</v>
       </c>
       <c r="B50" t="str">
-        <v>PAPA LAVADA KG</v>
+        <v>AJI LIQUIDACION</v>
       </c>
       <c r="C50" t="str">
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>41051</v>
+        <v>41002</v>
       </c>
       <c r="E50" t="str">
-        <v>890</v>
+        <v>9990</v>
       </c>
       <c r="F50" t="str">
         <v>Por peso</v>
@@ -1401,19 +1401,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>741002</v>
+        <v>741021</v>
       </c>
       <c r="B51" t="str">
-        <v>AJI LIQUIDACION</v>
+        <v>MOTE KG</v>
       </c>
       <c r="C51" t="str">
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>41002</v>
+        <v>41021</v>
       </c>
       <c r="E51" t="str">
-        <v>9990</v>
+        <v>1290</v>
       </c>
       <c r="F51" t="str">
         <v>Por peso</v>
@@ -1421,19 +1421,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>741021</v>
+        <v>741014</v>
       </c>
       <c r="B52" t="str">
-        <v>MOTE KG</v>
+        <v>HABAS KG</v>
       </c>
       <c r="C52" t="str">
         <v/>
       </c>
       <c r="D52" t="str">
-        <v>41021</v>
+        <v>41014</v>
       </c>
       <c r="E52" t="str">
-        <v>1290</v>
+        <v>990</v>
       </c>
       <c r="F52" t="str">
         <v>Por peso</v>
@@ -1441,19 +1441,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>741014</v>
+        <v>741046</v>
       </c>
       <c r="B53" t="str">
-        <v>HABAS KG</v>
+        <v>AJI CACHO CABRA SECO KG</v>
       </c>
       <c r="C53" t="str">
         <v/>
       </c>
       <c r="D53" t="str">
-        <v>41014</v>
+        <v>41046</v>
       </c>
       <c r="E53" t="str">
-        <v>990</v>
+        <v>13160</v>
       </c>
       <c r="F53" t="str">
         <v>Por peso</v>
@@ -1461,19 +1461,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>741046</v>
+        <v>741079</v>
       </c>
       <c r="B54" t="str">
-        <v>AJI CACHO CABRA SECO KG</v>
+        <v>CEBOLLA BLANCA CRISTAL KG</v>
       </c>
       <c r="C54" t="str">
         <v/>
       </c>
       <c r="D54" t="str">
-        <v>41046</v>
+        <v>41079</v>
       </c>
       <c r="E54" t="str">
-        <v>13160</v>
+        <v>790</v>
       </c>
       <c r="F54" t="str">
         <v>Por peso</v>
@@ -1481,19 +1481,19 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>741079</v>
+        <v>741080</v>
       </c>
       <c r="B55" t="str">
-        <v>CEBOLLA BLANCA CRISTAL KG</v>
+        <v>CEBOLLA CUGAT PP KG</v>
       </c>
       <c r="C55" t="str">
         <v/>
       </c>
       <c r="D55" t="str">
-        <v>41079</v>
+        <v>41080</v>
       </c>
       <c r="E55" t="str">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="F55" t="str">
         <v>Por peso</v>
@@ -1501,19 +1501,19 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>741080</v>
+        <v>741055</v>
       </c>
       <c r="B56" t="str">
-        <v>CEBOLLA CUGAT PP KG</v>
+        <v>BRUSELAS KG</v>
       </c>
       <c r="C56" t="str">
         <v/>
       </c>
       <c r="D56" t="str">
-        <v>41080</v>
+        <v>41055</v>
       </c>
       <c r="E56" t="str">
-        <v>690</v>
+        <v>2590</v>
       </c>
       <c r="F56" t="str">
         <v>Por peso</v>
@@ -1521,19 +1521,19 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>741055</v>
+        <v>741129</v>
       </c>
       <c r="B57" t="str">
-        <v>BRUSELAS KG</v>
+        <v>PAPA SURENA KILO</v>
       </c>
       <c r="C57" t="str">
         <v/>
       </c>
       <c r="D57" t="str">
-        <v>41055</v>
+        <v>41129</v>
       </c>
       <c r="E57" t="str">
-        <v>2590</v>
+        <v>690</v>
       </c>
       <c r="F57" t="str">
         <v>Por peso</v>
@@ -1541,16 +1541,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>741129</v>
+        <v>741042</v>
       </c>
       <c r="B58" t="str">
-        <v>PAPA SURENA KILO</v>
+        <v>ZANAHORIA KG</v>
       </c>
       <c r="C58" t="str">
         <v/>
       </c>
       <c r="D58" t="str">
-        <v>41129</v>
+        <v>41042</v>
       </c>
       <c r="E58" t="str">
         <v>690</v>

--- a/MaestraPLU_FFVV.xlsx
+++ b/MaestraPLU_FFVV.xlsx
@@ -421,19 +421,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>741032</v>
+        <v>742031</v>
       </c>
       <c r="B2" t="str">
-        <v>JENGIBRE KG</v>
+        <v>PLATANO KG</v>
       </c>
       <c r="C2" t="str">
         <v/>
       </c>
       <c r="D2" t="str">
-        <v>51032</v>
+        <v>42031</v>
       </c>
       <c r="E2" t="str">
-        <v>3560</v>
+        <v>1299</v>
       </c>
       <c r="F2" t="str">
         <v>Por peso</v>
@@ -441,19 +441,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>745146</v>
+        <v>741032</v>
       </c>
       <c r="B3" t="str">
-        <v>ALMENDRA KG FFVV</v>
+        <v>JENGIBRE KG</v>
       </c>
       <c r="C3" t="str">
         <v/>
       </c>
       <c r="D3" t="str">
-        <v>45146</v>
+        <v>51032</v>
       </c>
       <c r="E3" t="str">
-        <v>16760</v>
+        <v>3560</v>
       </c>
       <c r="F3" t="str">
         <v>Por peso</v>
@@ -461,19 +461,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>744023</v>
+        <v>745146</v>
       </c>
       <c r="B4" t="str">
-        <v>CHUCHOCA MOLIDA KG FFVV</v>
+        <v>ALMENDRA KG FFVV</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
       <c r="D4" t="str">
-        <v>44023</v>
+        <v>45146</v>
       </c>
       <c r="E4" t="str">
-        <v>1960</v>
+        <v>16760</v>
       </c>
       <c r="F4" t="str">
         <v>Por peso</v>
@@ -481,19 +481,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>743024</v>
+        <v>744023</v>
       </c>
       <c r="B5" t="str">
-        <v>PASAS MORENAS KG FFVV</v>
+        <v>CHUCHOCA MOLIDA KG FFVV</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5" t="str">
-        <v>43024</v>
+        <v>44023</v>
       </c>
       <c r="E5" t="str">
-        <v>5160</v>
+        <v>1960</v>
       </c>
       <c r="F5" t="str">
         <v>Por peso</v>
@@ -501,19 +501,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>744019</v>
+        <v>743024</v>
       </c>
       <c r="B6" t="str">
-        <v>PASAS RUBIA KG FFVV</v>
+        <v>PASAS MORENAS KG FFVV</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
       <c r="D6" t="str">
-        <v>44019</v>
+        <v>43024</v>
       </c>
       <c r="E6" t="str">
-        <v>9960</v>
+        <v>5160</v>
       </c>
       <c r="F6" t="str">
         <v>Por peso</v>
@@ -521,19 +521,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>744160</v>
+        <v>744019</v>
       </c>
       <c r="B7" t="str">
-        <v>YUCA KG FFVV</v>
+        <v>PASAS RUBIA KG FFVV</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7" t="str">
-        <v>44160</v>
+        <v>44019</v>
       </c>
       <c r="E7" t="str">
-        <v>3490</v>
+        <v>9960</v>
       </c>
       <c r="F7" t="str">
         <v>Por peso</v>
@@ -541,19 +541,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>744153</v>
+        <v>744160</v>
       </c>
       <c r="B8" t="str">
-        <v>TUNAS LIQUIDACION KG</v>
+        <v>YUCA KG FFVV</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
       <c r="D8" t="str">
-        <v>44153</v>
+        <v>44160</v>
       </c>
       <c r="E8" t="str">
-        <v>9990</v>
+        <v>3490</v>
       </c>
       <c r="F8" t="str">
         <v>Por peso</v>
@@ -561,19 +561,19 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>744146</v>
+        <v>744153</v>
       </c>
       <c r="B9" t="str">
-        <v>FLOR DE JAMAICA KG FFVV</v>
+        <v>TUNAS LIQUIDACION KG</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9" t="str">
-        <v>44146</v>
+        <v>44153</v>
       </c>
       <c r="E9" t="str">
-        <v>27960</v>
+        <v>9990</v>
       </c>
       <c r="F9" t="str">
         <v>Por peso</v>
@@ -581,19 +581,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>745147</v>
+        <v>744146</v>
       </c>
       <c r="B10" t="str">
-        <v>HUESILLOS KG FFVV</v>
+        <v>FLOR DE JAMAICA KG FFVV</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>45147</v>
+        <v>44146</v>
       </c>
       <c r="E10" t="str">
-        <v>9560</v>
+        <v>27960</v>
       </c>
       <c r="F10" t="str">
         <v>Por peso</v>
@@ -601,19 +601,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>742072</v>
+        <v>745147</v>
       </c>
       <c r="B11" t="str">
-        <v>SANDIA PRIMERA PP KG</v>
+        <v>HUESILLOS KG FFVV</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>42072</v>
+        <v>45147</v>
       </c>
       <c r="E11" t="str">
-        <v>490</v>
+        <v>9560</v>
       </c>
       <c r="F11" t="str">
         <v>Por peso</v>
@@ -621,19 +621,19 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>742031</v>
+        <v>742072</v>
       </c>
       <c r="B12" t="str">
-        <v>PLATANO KG</v>
+        <v>SANDIA PRIMERA PP KG</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12" t="str">
-        <v>42031</v>
+        <v>42072</v>
       </c>
       <c r="E12" t="str">
-        <v>1690</v>
+        <v>490</v>
       </c>
       <c r="F12" t="str">
         <v>Por peso</v>
@@ -913,7 +913,7 @@
         <v>42011</v>
       </c>
       <c r="E26" t="str">
-        <v>1290</v>
+        <v>1190</v>
       </c>
       <c r="F26" t="str">
         <v>Por peso</v>
@@ -1313,7 +1313,7 @@
         <v>41039</v>
       </c>
       <c r="E46" t="str">
-        <v>790</v>
+        <v>890</v>
       </c>
       <c r="F46" t="str">
         <v>Por peso</v>
